--- a/reports/Selenium_Report.xlsx
+++ b/reports/Selenium_Report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="129">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -52,7 +52,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>0.67s</t>
+    <t>0.65s</t>
   </si>
   <si>
     <t>TC-SEL-02</t>
@@ -64,7 +64,7 @@
     <t>Error message: "Passwords do not match." displays on password verification mismatch</t>
   </si>
   <si>
-    <t>0.59s</t>
+    <t>0.62s</t>
   </si>
   <si>
     <t>TC-SEL-03</t>
@@ -76,21 +76,21 @@
     <t>Error message: "Password must be at least 8 characters." displays</t>
   </si>
   <si>
+    <t>0.52s</t>
+  </si>
+  <si>
+    <t>TC-SEL-04</t>
+  </si>
+  <si>
+    <t>Validate signup with duplicate email restriction</t>
+  </si>
+  <si>
+    <t>Error message: "Email address already registered." displays</t>
+  </si>
+  <si>
     <t>0.49s</t>
   </si>
   <si>
-    <t>TC-SEL-04</t>
-  </si>
-  <si>
-    <t>Validate signup with duplicate email restriction</t>
-  </si>
-  <si>
-    <t>Error message: "Email address already registered." displays</t>
-  </si>
-  <si>
-    <t>0.46s</t>
-  </si>
-  <si>
     <t>TC-SEL-05</t>
   </si>
   <si>
@@ -100,7 +100,7 @@
     <t>Registration succeeds, stores user session, and auto-routes to dashboard layout</t>
   </si>
   <si>
-    <t>0.66s</t>
+    <t>0.72s</t>
   </si>
   <si>
     <t>TC-SEL-06</t>
@@ -112,159 +112,159 @@
     <t>Form prevents submission or displays missing fields prompt</t>
   </si>
   <si>
+    <t>0.22s</t>
+  </si>
+  <si>
+    <t>TC-SEL-07</t>
+  </si>
+  <si>
+    <t>Validate login password length boundaries</t>
+  </si>
+  <si>
+    <t>0.34s</t>
+  </si>
+  <si>
+    <t>TC-SEL-08</t>
+  </si>
+  <si>
+    <t>Validate wrong password credential error boundary</t>
+  </si>
+  <si>
+    <t>Error message: "Invalid email or password credential." displays</t>
+  </si>
+  <si>
+    <t>0.38s</t>
+  </si>
+  <si>
+    <t>TC-SEL-09</t>
+  </si>
+  <si>
+    <t>Verify successful authentication for Admin Manager role</t>
+  </si>
+  <si>
+    <t>Login succeeds and redirects to dashboard with active sidebar</t>
+  </si>
+  <si>
+    <t>TC-SEL-10</t>
+  </si>
+  <si>
+    <t>Verify Remember Me session storage persistence behavior</t>
+  </si>
+  <si>
+    <t>Session remains cached in localStorage when remember check is checked</t>
+  </si>
+  <si>
+    <t>0.43s</t>
+  </si>
+  <si>
+    <t>TC-SEL-11</t>
+  </si>
+  <si>
+    <t>Verify dashboard panels load initial default budgeting summary cards</t>
+  </si>
+  <si>
+    <t>Total Balance, Total Income, and Total Expenses load correctly</t>
+  </si>
+  <si>
+    <t>0.03s</t>
+  </si>
+  <si>
+    <t>TC-SEL-12</t>
+  </si>
+  <si>
+    <t>Verify dashboard net balance math matches initial static transactions</t>
+  </si>
+  <si>
+    <t>Balance equals total income minus total expenses</t>
+  </si>
+  <si>
+    <t>0.06s</t>
+  </si>
+  <si>
+    <t>TC-SEL-13</t>
+  </si>
+  <si>
+    <t>Verify dashboard search bar resolves real-time query list matches</t>
+  </si>
+  <si>
+    <t>Typing transaction names filters matching rows dynamically</t>
+  </si>
+  <si>
+    <t>0.15s</t>
+  </si>
+  <si>
+    <t>TC-SEL-14</t>
+  </si>
+  <si>
+    <t>Verify add income inflow category transaction form submission flow</t>
+  </si>
+  <si>
+    <t>Inflow transaction added and net balance increases accordingly</t>
+  </si>
+  <si>
+    <t>0.58s</t>
+  </si>
+  <si>
+    <t>TC-SEL-15</t>
+  </si>
+  <si>
+    <t>Validate income forms empty constraints boundaries</t>
+  </si>
+  <si>
+    <t>Missing required inputs prevent transaction submission</t>
+  </si>
+  <si>
+    <t>0.14s</t>
+  </si>
+  <si>
+    <t>TC-SEL-16</t>
+  </si>
+  <si>
+    <t>Verify delete income transaction adjusts total calculations</t>
+  </si>
+  <si>
+    <t>Removing an income transaction successfully reduces total balance</t>
+  </si>
+  <si>
+    <t>0.23s</t>
+  </si>
+  <si>
+    <t>TC-SEL-17</t>
+  </si>
+  <si>
+    <t>Verify add expense outflow category transaction successfully updates calculations</t>
+  </si>
+  <si>
+    <t>Outflow transaction decreases net balance</t>
+  </si>
+  <si>
+    <t>0.54s</t>
+  </si>
+  <si>
+    <t>TC-SEL-18</t>
+  </si>
+  <si>
+    <t>Validate numeric constraints on amount inputs preventing non-numerical submission</t>
+  </si>
+  <si>
+    <t>Negative or text values in amount are rejected</t>
+  </si>
+  <si>
+    <t>0.07s</t>
+  </si>
+  <si>
+    <t>TC-SEL-19</t>
+  </si>
+  <si>
+    <t>Verify delete expense transaction adjustments</t>
+  </si>
+  <si>
+    <t>Deleting an expense successfully restores balance amount</t>
+  </si>
+  <si>
     <t>0.18s</t>
   </si>
   <si>
-    <t>TC-SEL-07</t>
-  </si>
-  <si>
-    <t>Validate login password length boundaries</t>
-  </si>
-  <si>
-    <t>0.28s</t>
-  </si>
-  <si>
-    <t>TC-SEL-08</t>
-  </si>
-  <si>
-    <t>Validate wrong password credential error boundary</t>
-  </si>
-  <si>
-    <t>Error message: "Invalid email or password credential." displays</t>
-  </si>
-  <si>
-    <t>TC-SEL-09</t>
-  </si>
-  <si>
-    <t>Verify successful authentication for Admin Manager role</t>
-  </si>
-  <si>
-    <t>Login succeeds and redirects to dashboard with active sidebar</t>
-  </si>
-  <si>
-    <t>0.27s</t>
-  </si>
-  <si>
-    <t>TC-SEL-10</t>
-  </si>
-  <si>
-    <t>Verify Remember Me session storage persistence behavior</t>
-  </si>
-  <si>
-    <t>Session remains cached in localStorage when remember check is checked</t>
-  </si>
-  <si>
-    <t>0.38s</t>
-  </si>
-  <si>
-    <t>TC-SEL-11</t>
-  </si>
-  <si>
-    <t>Verify dashboard panels load initial default budgeting summary cards</t>
-  </si>
-  <si>
-    <t>Total Balance, Total Income, and Total Expenses load correctly</t>
-  </si>
-  <si>
-    <t>0.02s</t>
-  </si>
-  <si>
-    <t>TC-SEL-12</t>
-  </si>
-  <si>
-    <t>Verify dashboard net balance math matches initial static transactions</t>
-  </si>
-  <si>
-    <t>Balance equals total income minus total expenses</t>
-  </si>
-  <si>
-    <t>0.05s</t>
-  </si>
-  <si>
-    <t>TC-SEL-13</t>
-  </si>
-  <si>
-    <t>Verify dashboard search bar resolves real-time query list matches</t>
-  </si>
-  <si>
-    <t>Typing transaction names filters matching rows dynamically</t>
-  </si>
-  <si>
-    <t>0.16s</t>
-  </si>
-  <si>
-    <t>TC-SEL-14</t>
-  </si>
-  <si>
-    <t>Verify add income inflow category transaction form submission flow</t>
-  </si>
-  <si>
-    <t>Inflow transaction added and net balance increases accordingly</t>
-  </si>
-  <si>
-    <t>0.77s</t>
-  </si>
-  <si>
-    <t>TC-SEL-15</t>
-  </si>
-  <si>
-    <t>Validate income forms empty constraints boundaries</t>
-  </si>
-  <si>
-    <t>Missing required inputs prevent transaction submission</t>
-  </si>
-  <si>
-    <t>0.13s</t>
-  </si>
-  <si>
-    <t>TC-SEL-16</t>
-  </si>
-  <si>
-    <t>Verify delete income transaction adjusts total calculations</t>
-  </si>
-  <si>
-    <t>Removing an income transaction successfully reduces total balance</t>
-  </si>
-  <si>
-    <t>0.24s</t>
-  </si>
-  <si>
-    <t>TC-SEL-17</t>
-  </si>
-  <si>
-    <t>Verify add expense outflow category transaction successfully updates calculations</t>
-  </si>
-  <si>
-    <t>Outflow transaction decreases net balance</t>
-  </si>
-  <si>
-    <t>0.52s</t>
-  </si>
-  <si>
-    <t>TC-SEL-18</t>
-  </si>
-  <si>
-    <t>Validate numeric constraints on amount inputs preventing non-numerical submission</t>
-  </si>
-  <si>
-    <t>Negative or text values in amount are rejected</t>
-  </si>
-  <si>
-    <t>0.07s</t>
-  </si>
-  <si>
-    <t>TC-SEL-19</t>
-  </si>
-  <si>
-    <t>Verify delete expense transaction adjustments</t>
-  </si>
-  <si>
-    <t>Deleting an expense successfully restores balance amount</t>
-  </si>
-  <si>
-    <t>0.15s</t>
-  </si>
-  <si>
     <t>TC-SEL-20</t>
   </si>
   <si>
@@ -274,9 +274,6 @@
     <t>Category caps limits are saved and progress bars render</t>
   </si>
   <si>
-    <t>0.37s</t>
-  </si>
-  <si>
     <t>TC-SEL-21</t>
   </si>
   <si>
@@ -286,7 +283,7 @@
     <t>Budget Cap overflow modal popup loads when transaction exceeds cap</t>
   </si>
   <si>
-    <t>0.72s</t>
+    <t>0.80s</t>
   </si>
   <si>
     <t>TC-SEL-22</t>
@@ -298,6 +295,9 @@
     <t>Updating limit increases budget cap and progress decreases</t>
   </si>
   <si>
+    <t>0.29s</t>
+  </si>
+  <si>
     <t>TC-SEL-23</t>
   </si>
   <si>
@@ -307,7 +307,7 @@
     <t>Monthly Balance Trend line container is visible on page</t>
   </si>
   <si>
-    <t>0.09s</t>
+    <t>0.10s</t>
   </si>
   <si>
     <t>TC-SEL-24</t>
@@ -328,42 +328,45 @@
     <t>Clicking export initializes simulated raw CSV download</t>
   </si>
   <si>
+    <t>0.12s</t>
+  </si>
+  <si>
+    <t>TC-SEL-26</t>
+  </si>
+  <si>
+    <t>Verify user profile metadata fields update successfully</t>
+  </si>
+  <si>
+    <t>Display name successfully updates and synchronizes with sidebar user block</t>
+  </si>
+  <si>
+    <t>0.40s</t>
+  </si>
+  <si>
+    <t>TC-SEL-27</t>
+  </si>
+  <si>
+    <t>Verify preferred default currency synchronization on profile updates</t>
+  </si>
+  <si>
+    <t>Changing currency symbol on profile alters dashboard symbols</t>
+  </si>
+  <si>
+    <t>0.39s</t>
+  </si>
+  <si>
+    <t>TC-SEL-28</t>
+  </si>
+  <si>
+    <t>Verify profile assigned application role is readonly configuration</t>
+  </si>
+  <si>
+    <t>Application role text box contains "readonly" property attribute</t>
+  </si>
+  <si>
     <t>0.11s</t>
   </si>
   <si>
-    <t>TC-SEL-26</t>
-  </si>
-  <si>
-    <t>Verify user profile metadata fields update successfully</t>
-  </si>
-  <si>
-    <t>Display name successfully updates and synchronizes with sidebar user block</t>
-  </si>
-  <si>
-    <t>0.36s</t>
-  </si>
-  <si>
-    <t>TC-SEL-27</t>
-  </si>
-  <si>
-    <t>Verify preferred default currency synchronization on profile updates</t>
-  </si>
-  <si>
-    <t>Changing currency symbol on profile alters dashboard symbols</t>
-  </si>
-  <si>
-    <t>TC-SEL-28</t>
-  </si>
-  <si>
-    <t>Verify profile assigned application role is readonly configuration</t>
-  </si>
-  <si>
-    <t>Application role text box contains "readonly" property attribute</t>
-  </si>
-  <si>
-    <t>0.10s</t>
-  </si>
-  <si>
     <t>TC-SEL-29</t>
   </si>
   <si>
@@ -379,7 +382,7 @@
     <t>FAIL</t>
   </si>
   <si>
-    <t>10.20s</t>
+    <t>10.21s</t>
   </si>
   <si>
     <t>TC-SEL-30</t>
@@ -1047,21 +1050,21 @@
         <v>12</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>11</v>
@@ -1070,7 +1073,7 @@
         <v>12</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1323,53 +1326,53 @@
         <v>12</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="4" t="s">
+      <c r="D22" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="E22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="E23" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1484,21 +1487,21 @@
         <v>12</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>87</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>11</v>
@@ -1507,53 +1510,53 @@
         <v>12</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Selenium_Report.xlsx
+++ b/reports/Selenium_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="271">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/16/2026, 4:44:07 AM</t>
+    <t>6/16/2026, 5:20:47 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>6.93s</t>
+    <t>10.48s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,7 +103,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>0.34s</t>
+    <t>0.80s</t>
   </si>
   <si>
     <t>TC-SEL-02</t>
@@ -115,7 +115,7 @@
     <t>Error message: "Passwords do not match." displays on password verification mismatch</t>
   </si>
   <si>
-    <t>0.38s</t>
+    <t>0.66s</t>
   </si>
   <si>
     <t>TC-SEL-03</t>
@@ -127,7 +127,7 @@
     <t>Error message: "Password must be at least 8 characters." displays</t>
   </si>
   <si>
-    <t>0.36s</t>
+    <t>0.49s</t>
   </si>
   <si>
     <t>TC-SEL-04</t>
@@ -139,264 +139,279 @@
     <t>Error message: "Email address already registered." displays</t>
   </si>
   <si>
+    <t>0.58s</t>
+  </si>
+  <si>
+    <t>TC-SEL-05</t>
+  </si>
+  <si>
+    <t>Verify successful user signup and redirect to main Dashboard view</t>
+  </si>
+  <si>
+    <t>Registration succeeds, stores user session, and auto-routes to dashboard layout</t>
+  </si>
+  <si>
+    <t>0.85s</t>
+  </si>
+  <si>
+    <t>TC-SEL-06</t>
+  </si>
+  <si>
+    <t>Validate login empty fields boundary rules</t>
+  </si>
+  <si>
+    <t>Form prevents submission or displays missing fields prompt</t>
+  </si>
+  <si>
+    <t>0.22s</t>
+  </si>
+  <si>
+    <t>TC-SEL-07</t>
+  </si>
+  <si>
+    <t>Validate login password length boundaries</t>
+  </si>
+  <si>
+    <t>0.31s</t>
+  </si>
+  <si>
+    <t>TC-SEL-08</t>
+  </si>
+  <si>
+    <t>Validate wrong password credential error boundary</t>
+  </si>
+  <si>
+    <t>Error message: "Invalid email or password credential." displays</t>
+  </si>
+  <si>
+    <t>0.28s</t>
+  </si>
+  <si>
+    <t>TC-SEL-09</t>
+  </si>
+  <si>
+    <t>Verify successful authentication for Admin Manager role</t>
+  </si>
+  <si>
+    <t>Login succeeds and redirects to dashboard with active sidebar</t>
+  </si>
+  <si>
+    <t>0.30s</t>
+  </si>
+  <si>
+    <t>TC-SEL-10</t>
+  </si>
+  <si>
+    <t>Verify Remember Me session storage persistence behavior</t>
+  </si>
+  <si>
+    <t>Session remains cached in localStorage when remember check is checked</t>
+  </si>
+  <si>
+    <t>0.43s</t>
+  </si>
+  <si>
+    <t>TC-SEL-11</t>
+  </si>
+  <si>
+    <t>Verify dashboard panels load initial default budgeting summary cards</t>
+  </si>
+  <si>
+    <t>Total Balance, Total Income, and Total Expenses load correctly</t>
+  </si>
+  <si>
+    <t>0.46s</t>
+  </si>
+  <si>
+    <t>TC-SEL-12</t>
+  </si>
+  <si>
+    <t>Verify dashboard net balance math matches initial static transactions</t>
+  </si>
+  <si>
+    <t>Balance equals total income minus total expenses</t>
+  </si>
+  <si>
+    <t>0.06s</t>
+  </si>
+  <si>
+    <t>TC-SEL-13</t>
+  </si>
+  <si>
+    <t>Verify dashboard search bar resolves real-time query list matches</t>
+  </si>
+  <si>
+    <t>Typing transaction names filters matching rows dynamically</t>
+  </si>
+  <si>
+    <t>0.15s</t>
+  </si>
+  <si>
+    <t>TC-SEL-14</t>
+  </si>
+  <si>
+    <t>Verify add income inflow category transaction form submission flow</t>
+  </si>
+  <si>
+    <t>Inflow transaction added and net balance increases accordingly</t>
+  </si>
+  <si>
+    <t>0.57s</t>
+  </si>
+  <si>
+    <t>TC-SEL-15</t>
+  </si>
+  <si>
+    <t>Validate income forms empty constraints boundaries</t>
+  </si>
+  <si>
+    <t>Missing required inputs prevent transaction submission</t>
+  </si>
+  <si>
+    <t>0.14s</t>
+  </si>
+  <si>
+    <t>TC-SEL-16</t>
+  </si>
+  <si>
+    <t>Verify delete income transaction adjusts total calculations</t>
+  </si>
+  <si>
+    <t>Removing an income transaction successfully reduces total balance</t>
+  </si>
+  <si>
+    <t>0.23s</t>
+  </si>
+  <si>
+    <t>TC-SEL-17</t>
+  </si>
+  <si>
+    <t>Verify add expense outflow category transaction successfully updates calculations</t>
+  </si>
+  <si>
+    <t>Outflow transaction decreases net balance</t>
+  </si>
+  <si>
+    <t>0.51s</t>
+  </si>
+  <si>
+    <t>TC-SEL-18</t>
+  </si>
+  <si>
+    <t>Validate numeric constraints on amount inputs preventing non-numerical submission</t>
+  </si>
+  <si>
+    <t>Negative or text values in amount are rejected</t>
+  </si>
+  <si>
+    <t>0.07s</t>
+  </si>
+  <si>
+    <t>TC-SEL-19</t>
+  </si>
+  <si>
+    <t>Verify delete expense transaction adjustments</t>
+  </si>
+  <si>
+    <t>Deleting an expense successfully restores balance amount</t>
+  </si>
+  <si>
+    <t>0.19s</t>
+  </si>
+  <si>
+    <t>TC-SEL-20</t>
+  </si>
+  <si>
+    <t>Verify category budget cap limit configuration successfully saves limiters</t>
+  </si>
+  <si>
+    <t>Category caps limits are saved and progress bars render</t>
+  </si>
+  <si>
     <t>0.37s</t>
   </si>
   <si>
-    <t>TC-SEL-05</t>
-  </si>
-  <si>
-    <t>Verify successful user signup and redirect to main Dashboard view</t>
-  </si>
-  <si>
-    <t>Registration succeeds, stores user session, and auto-routes to dashboard layout</t>
-  </si>
-  <si>
-    <t>0.44s</t>
-  </si>
-  <si>
-    <t>TC-SEL-06</t>
-  </si>
-  <si>
-    <t>Validate login empty fields boundary rules</t>
-  </si>
-  <si>
-    <t>Form prevents submission or displays missing fields prompt</t>
-  </si>
-  <si>
-    <t>0.14s</t>
-  </si>
-  <si>
-    <t>TC-SEL-07</t>
-  </si>
-  <si>
-    <t>Validate login password length boundaries</t>
-  </si>
-  <si>
-    <t>0.23s</t>
-  </si>
-  <si>
-    <t>TC-SEL-08</t>
-  </si>
-  <si>
-    <t>Validate wrong password credential error boundary</t>
-  </si>
-  <si>
-    <t>Error message: "Invalid email or password credential." displays</t>
-  </si>
-  <si>
-    <t>0.21s</t>
-  </si>
-  <si>
-    <t>TC-SEL-09</t>
-  </si>
-  <si>
-    <t>Verify successful authentication for Admin Manager role</t>
-  </si>
-  <si>
-    <t>Login succeeds and redirects to dashboard with active sidebar</t>
-  </si>
-  <si>
-    <t>TC-SEL-10</t>
-  </si>
-  <si>
-    <t>Verify Remember Me session storage persistence behavior</t>
-  </si>
-  <si>
-    <t>Session remains cached in localStorage when remember check is checked</t>
-  </si>
-  <si>
-    <t>0.32s</t>
-  </si>
-  <si>
-    <t>TC-SEL-11</t>
-  </si>
-  <si>
-    <t>Verify dashboard panels load initial default budgeting summary cards</t>
-  </si>
-  <si>
-    <t>Total Balance, Total Income, and Total Expenses load correctly</t>
-  </si>
-  <si>
-    <t>0.02s</t>
-  </si>
-  <si>
-    <t>TC-SEL-12</t>
-  </si>
-  <si>
-    <t>Verify dashboard net balance math matches initial static transactions</t>
-  </si>
-  <si>
-    <t>Balance equals total income minus total expenses</t>
-  </si>
-  <si>
-    <t>0.05s</t>
-  </si>
-  <si>
-    <t>TC-SEL-13</t>
-  </si>
-  <si>
-    <t>Verify dashboard search bar resolves real-time query list matches</t>
-  </si>
-  <si>
-    <t>Typing transaction names filters matching rows dynamically</t>
+    <t>TC-SEL-21</t>
+  </si>
+  <si>
+    <t>Verify category budget warning alert triggers when expense exceeds limit cap</t>
+  </si>
+  <si>
+    <t>Budget Cap overflow modal popup loads when transaction exceeds cap</t>
+  </si>
+  <si>
+    <t>0.79s</t>
+  </si>
+  <si>
+    <t>TC-SEL-22</t>
+  </si>
+  <si>
+    <t>Verify edit category budget limit increases active threshold</t>
+  </si>
+  <si>
+    <t>Updating limit increases budget cap and progress decreases</t>
+  </si>
+  <si>
+    <t>0.29s</t>
+  </si>
+  <si>
+    <t>TC-SEL-23</t>
+  </si>
+  <si>
+    <t>Verify reports dashboard trend chart elements rendering</t>
+  </si>
+  <si>
+    <t>Monthly Balance Trend line container is visible on page</t>
+  </si>
+  <si>
+    <t>0.10s</t>
+  </si>
+  <si>
+    <t>TC-SEL-24</t>
+  </si>
+  <si>
+    <t>Verify category distribution breakdown list aggregates metrics</t>
+  </si>
+  <si>
+    <t>Analytics categories breakdown table loads and sums values</t>
+  </si>
+  <si>
+    <t>TC-SEL-25</t>
+  </si>
+  <si>
+    <t>Verify raw data export reports CSV simulation download trigger</t>
+  </si>
+  <si>
+    <t>Clicking export initializes simulated raw CSV download</t>
   </si>
   <si>
     <t>0.11s</t>
   </si>
   <si>
-    <t>TC-SEL-14</t>
-  </si>
-  <si>
-    <t>Verify add income inflow category transaction form submission flow</t>
-  </si>
-  <si>
-    <t>Inflow transaction added and net balance increases accordingly</t>
-  </si>
-  <si>
-    <t>0.45s</t>
-  </si>
-  <si>
-    <t>TC-SEL-15</t>
-  </si>
-  <si>
-    <t>Validate income forms empty constraints boundaries</t>
-  </si>
-  <si>
-    <t>Missing required inputs prevent transaction submission</t>
-  </si>
-  <si>
-    <t>TC-SEL-16</t>
-  </si>
-  <si>
-    <t>Verify delete income transaction adjusts total calculations</t>
-  </si>
-  <si>
-    <t>Removing an income transaction successfully reduces total balance</t>
-  </si>
-  <si>
-    <t>0.16s</t>
-  </si>
-  <si>
-    <t>TC-SEL-17</t>
-  </si>
-  <si>
-    <t>Verify add expense outflow category transaction successfully updates calculations</t>
-  </si>
-  <si>
-    <t>Outflow transaction decreases net balance</t>
+    <t>TC-SEL-26</t>
+  </si>
+  <si>
+    <t>Verify user profile metadata fields update successfully</t>
+  </si>
+  <si>
+    <t>Display name successfully updates and synchronizes with sidebar user block</t>
+  </si>
+  <si>
+    <t>0.41s</t>
+  </si>
+  <si>
+    <t>TC-SEL-27</t>
+  </si>
+  <si>
+    <t>Verify preferred default currency synchronization on profile updates</t>
+  </si>
+  <si>
+    <t>Changing currency symbol on profile alters dashboard symbols</t>
   </si>
   <si>
     <t>0.42s</t>
   </si>
   <si>
-    <t>TC-SEL-18</t>
-  </si>
-  <si>
-    <t>Validate numeric constraints on amount inputs preventing non-numerical submission</t>
-  </si>
-  <si>
-    <t>Negative or text values in amount are rejected</t>
-  </si>
-  <si>
-    <t>0.06s</t>
-  </si>
-  <si>
-    <t>TC-SEL-19</t>
-  </si>
-  <si>
-    <t>Verify delete expense transaction adjustments</t>
-  </si>
-  <si>
-    <t>Deleting an expense successfully restores balance amount</t>
-  </si>
-  <si>
-    <t>TC-SEL-20</t>
-  </si>
-  <si>
-    <t>Verify category budget cap limit configuration successfully saves limiters</t>
-  </si>
-  <si>
-    <t>Category caps limits are saved and progress bars render</t>
-  </si>
-  <si>
-    <t>TC-SEL-21</t>
-  </si>
-  <si>
-    <t>Verify category budget warning alert triggers when expense exceeds limit cap</t>
-  </si>
-  <si>
-    <t>Budget Cap overflow modal popup loads when transaction exceeds cap</t>
-  </si>
-  <si>
-    <t>0.68s</t>
-  </si>
-  <si>
-    <t>TC-SEL-22</t>
-  </si>
-  <si>
-    <t>Verify edit category budget limit increases active threshold</t>
-  </si>
-  <si>
-    <t>Updating limit increases budget cap and progress decreases</t>
-  </si>
-  <si>
-    <t>0.22s</t>
-  </si>
-  <si>
-    <t>TC-SEL-23</t>
-  </si>
-  <si>
-    <t>Verify reports dashboard trend chart elements rendering</t>
-  </si>
-  <si>
-    <t>Monthly Balance Trend line container is visible on page</t>
-  </si>
-  <si>
-    <t>TC-SEL-24</t>
-  </si>
-  <si>
-    <t>Verify category distribution breakdown list aggregates metrics</t>
-  </si>
-  <si>
-    <t>Analytics categories breakdown table loads and sums values</t>
-  </si>
-  <si>
-    <t>0.08s</t>
-  </si>
-  <si>
-    <t>TC-SEL-25</t>
-  </si>
-  <si>
-    <t>Verify raw data export reports CSV simulation download trigger</t>
-  </si>
-  <si>
-    <t>Clicking export initializes simulated raw CSV download</t>
-  </si>
-  <si>
-    <t>0.07s</t>
-  </si>
-  <si>
-    <t>TC-SEL-26</t>
-  </si>
-  <si>
-    <t>Verify user profile metadata fields update successfully</t>
-  </si>
-  <si>
-    <t>Display name successfully updates and synchronizes with sidebar user block</t>
-  </si>
-  <si>
-    <t>0.40s</t>
-  </si>
-  <si>
-    <t>TC-SEL-27</t>
-  </si>
-  <si>
-    <t>Verify preferred default currency synchronization on profile updates</t>
-  </si>
-  <si>
-    <t>Changing currency symbol on profile alters dashboard symbols</t>
-  </si>
-  <si>
     <t>TC-SEL-28</t>
   </si>
   <si>
@@ -406,18 +421,21 @@
     <t>Application role text box contains "readonly" property attribute</t>
   </si>
   <si>
+    <t>0.13s</t>
+  </si>
+  <si>
+    <t>TC-SEL-29</t>
+  </si>
+  <si>
+    <t>Verify successful user logout redirects to authentication login view</t>
+  </si>
+  <si>
+    <t>Session clears and client redirects to login view immediately</t>
+  </si>
+  <si>
     <t>0.09s</t>
   </si>
   <si>
-    <t>TC-SEL-29</t>
-  </si>
-  <si>
-    <t>Verify successful user logout redirects to authentication login view</t>
-  </si>
-  <si>
-    <t>Session clears and client redirects to login view immediately</t>
-  </si>
-  <si>
     <t>TC-SEL-30</t>
   </si>
   <si>
@@ -427,9 +445,6 @@
     <t>Inactivity trigger automatically destroys token and redirects to login view</t>
   </si>
   <si>
-    <t>0.00s</t>
-  </si>
-  <si>
     <t>Failure Message</t>
   </si>
   <si>
@@ -454,7 +469,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>6/16/2026, 4:44:00 AM</t>
+    <t>6/16/2026, 5:20:36 AM</t>
   </si>
   <si>
     <t>LoginPage</t>
@@ -508,7 +523,7 @@
     <t>Entered: SecurePass123!</t>
   </si>
   <si>
-    <t>6/16/2026, 4:44:01 AM</t>
+    <t>6/16/2026, 5:20:37 AM</t>
   </si>
   <si>
     <t>Entered: WrongPass123!</t>
@@ -535,18 +550,21 @@
     <t>Entered: admin@budget.com</t>
   </si>
   <si>
+    <t>6/16/2026, 5:20:38 AM</t>
+  </si>
+  <si>
     <t>Entered: SmartBudgetPass123!</t>
   </si>
   <si>
     <t>Text found: "Email address already registered."</t>
   </si>
   <si>
-    <t>6/16/2026, 4:44:02 AM</t>
-  </si>
-  <si>
     <t>Entered: SarahPass123!</t>
   </si>
   <si>
+    <t>6/16/2026, 5:20:39 AM</t>
+  </si>
+  <si>
     <t>DashboardPage</t>
   </si>
   <si>
@@ -583,7 +601,7 @@
     <t>Text found: "Invalid email or password credential."</t>
   </si>
   <si>
-    <t>6/16/2026, 4:44:03 AM</t>
+    <t>6/16/2026, 5:20:40 AM</t>
   </si>
   <si>
     <t>Check Remember Me option</t>
@@ -619,6 +637,9 @@
     <t>Navigate to tab: nav-income</t>
   </si>
   <si>
+    <t>6/16/2026, 5:20:41 AM</t>
+  </si>
+  <si>
     <t>Select income category: Salary</t>
   </si>
   <si>
@@ -637,9 +658,6 @@
     <t>Entered: Part-time consultancy paycheck</t>
   </si>
   <si>
-    <t>6/16/2026, 4:44:04 AM</t>
-  </si>
-  <si>
     <t>Click Log Income Submit button</t>
   </si>
   <si>
@@ -667,6 +685,9 @@
     <t>Entered: Food</t>
   </si>
   <si>
+    <t>6/16/2026, 5:20:42 AM</t>
+  </si>
+  <si>
     <t>Enter expense amount: 120</t>
   </si>
   <si>
@@ -689,9 +710,6 @@
   </si>
   <si>
     <t>Text found: "$1,990.00"</t>
-  </si>
-  <si>
-    <t>6/16/2026, 4:44:05 AM</t>
   </si>
   <si>
     <t>Navigate to tab: nav-budget</t>
@@ -724,6 +742,9 @@
 $0.00 / $1500.00 (0%)"</t>
   </si>
   <si>
+    <t>6/16/2026, 5:20:43 AM</t>
+  </si>
+  <si>
     <t>Select budget segment: Shopping</t>
   </si>
   <si>
@@ -754,13 +775,13 @@
     <t>Acknowledge budget cap warning dialog</t>
   </si>
   <si>
-    <t>6/16/2026, 4:44:06 AM</t>
-  </si>
-  <si>
     <t>Enter budget cap limit: 1000</t>
   </si>
   <si>
     <t>Entered: 1000</t>
+  </si>
+  <si>
+    <t>6/16/2026, 5:20:44 AM</t>
   </si>
   <si>
     <t>Check updated Food cap</t>
@@ -823,6 +844,9 @@
   </si>
   <si>
     <t>Entered: €</t>
+  </si>
+  <si>
+    <t>6/16/2026, 5:20:45 AM</t>
   </si>
   <si>
     <t>Text found: "€1,740.00"</t>
@@ -1598,21 +1622,21 @@
         <v>28</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
@@ -1621,21 +1645,21 @@
         <v>28</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>27</v>
@@ -1644,21 +1668,21 @@
         <v>28</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>27</v>
@@ -1667,21 +1691,21 @@
         <v>28</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
@@ -1690,21 +1714,21 @@
         <v>28</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>27</v>
@@ -1713,21 +1737,21 @@
         <v>28</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>27</v>
@@ -1736,21 +1760,21 @@
         <v>28</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>27</v>
@@ -1759,21 +1783,21 @@
         <v>28</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>27</v>
@@ -1782,21 +1806,21 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -1805,21 +1829,21 @@
         <v>28</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>27</v>
@@ -1828,21 +1852,21 @@
         <v>28</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>27</v>
@@ -1851,21 +1875,21 @@
         <v>28</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>37</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>27</v>
@@ -1874,21 +1898,21 @@
         <v>28</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>27</v>
@@ -1897,21 +1921,21 @@
         <v>28</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>27</v>
@@ -1920,21 +1944,21 @@
         <v>28</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>27</v>
@@ -1943,21 +1967,21 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -1966,21 +1990,21 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>27</v>
@@ -1989,21 +2013,21 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
@@ -2012,21 +2036,21 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>29</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>27</v>
@@ -2035,21 +2059,21 @@
         <v>28</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>27</v>
@@ -2058,21 +2082,21 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>27</v>
@@ -2081,7 +2105,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>137</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -2113,10 +2137,10 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2127,10 +2151,10 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>7</v>
@@ -2156,143 +2180,143 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>24</v>
@@ -2309,109 +2333,109 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
@@ -2428,109 +2452,109 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>159</v>
-      </c>
       <c r="D17" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>24</v>
@@ -2547,109 +2571,109 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
@@ -2666,109 +2690,109 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>159</v>
-      </c>
       <c r="D31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>24</v>
@@ -2785,75 +2809,75 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>24</v>
@@ -2870,75 +2894,75 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>24</v>
@@ -2955,75 +2979,75 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>24</v>
@@ -3040,58 +3064,58 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>24</v>
@@ -3108,98 +3132,98 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>28</v>
@@ -3210,30 +3234,30 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>28</v>
@@ -3244,64 +3268,64 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>28</v>
@@ -3312,47 +3336,47 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>28</v>
@@ -3363,87 +3387,87 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -3451,16 +3475,16 @@
         <v>207</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -3468,16 +3492,16 @@
         <v>207</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -3488,7 +3512,7 @@
         <v>24</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>28</v>
@@ -3502,16 +3526,16 @@
         <v>207</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -3519,16 +3543,16 @@
         <v>207</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -3539,7 +3563,7 @@
         <v>24</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>28</v>
@@ -3553,16 +3577,16 @@
         <v>207</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -3570,16 +3594,16 @@
         <v>207</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -3587,16 +3611,16 @@
         <v>207</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -3604,16 +3628,16 @@
         <v>207</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -3624,7 +3648,7 @@
         <v>24</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>28</v>
@@ -3638,16 +3662,16 @@
         <v>207</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -3655,16 +3679,16 @@
         <v>207</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D89" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -3672,95 +3696,95 @@
         <v>207</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D95" s="6" t="s">
         <v>28</v>
@@ -3771,30 +3795,30 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D96" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D97" s="6" t="s">
         <v>28</v>
@@ -3805,81 +3829,81 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D101" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D102" s="6" t="s">
         <v>28</v>
@@ -3890,98 +3914,98 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D103" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="D104" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D105" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D106" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D107" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D108" s="6" t="s">
         <v>28</v>
@@ -3992,183 +4016,183 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D113" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D119" s="6" t="s">
         <v>28</v>
@@ -4179,98 +4203,98 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="D121" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D122" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D123" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D125" s="6" t="s">
         <v>28</v>
@@ -4281,30 +4305,30 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D127" s="6" t="s">
         <v>28</v>
@@ -4315,47 +4339,47 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="D128" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="D129" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>28</v>
@@ -4366,30 +4390,30 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="D131" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>28</v>
@@ -4400,98 +4424,98 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="D133" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="D135" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="D137" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D138" s="6" t="s">
         <v>28</v>
@@ -4502,115 +4526,115 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="D139" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="D141" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
-        <v>3</v>
+        <v>269</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="D142" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
-        <v>3</v>
+        <v>269</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D143" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="5" t="s">
-        <v>3</v>
+        <v>269</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D144" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
-        <v>3</v>
+        <v>269</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D145" s="6" t="s">
         <v>28</v>
@@ -4621,30 +4645,30 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="5" t="s">
-        <v>3</v>
+        <v>269</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="D146" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
-        <v>3</v>
+        <v>269</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D147" s="6" t="s">
         <v>28</v>
@@ -4655,30 +4679,30 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="5" t="s">
-        <v>3</v>
+        <v>269</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D148" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
-        <v>3</v>
+        <v>269</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D149" s="6" t="s">
         <v>28</v>
@@ -4689,13 +4713,13 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="5" t="s">
-        <v>3</v>
+        <v>269</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D150" s="6" t="s">
         <v>28</v>

--- a/reports/Selenium_Report.xlsx
+++ b/reports/Selenium_Report.xlsx
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/16/2026, 5:20:47 AM</t>
+    <t>6/16/2026, 5:29:22 AM</t>
   </si>
   <si>
     <t>Device Name</t>

--- a/reports/Selenium_Report.xlsx
+++ b/reports/Selenium_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="271">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>16/6/2026, 11:30:00 am</t>
+    <t>6/16/2026, 6:02:18 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>11.94s</t>
+    <t>10.36s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,327 +103,339 @@
     <t>PASS</t>
   </si>
   <si>
+    <t>0.91s</t>
+  </si>
+  <si>
+    <t>TC-SEL-02</t>
+  </si>
+  <si>
+    <t>Validate password mismatch constraint</t>
+  </si>
+  <si>
+    <t>Error message: "Passwords do not match." displays on password verification mismatch</t>
+  </si>
+  <si>
+    <t>0.74s</t>
+  </si>
+  <si>
+    <t>TC-SEL-03</t>
+  </si>
+  <si>
+    <t>Validate password minimum length validation constraint</t>
+  </si>
+  <si>
+    <t>Error message: "Password must be at least 8 characters." displays</t>
+  </si>
+  <si>
+    <t>0.49s</t>
+  </si>
+  <si>
+    <t>TC-SEL-04</t>
+  </si>
+  <si>
+    <t>Validate signup with duplicate email restriction</t>
+  </si>
+  <si>
+    <t>Error message: "Email address already registered." displays</t>
+  </si>
+  <si>
+    <t>0.60s</t>
+  </si>
+  <si>
+    <t>TC-SEL-05</t>
+  </si>
+  <si>
+    <t>Verify successful user signup and redirect to main Dashboard view</t>
+  </si>
+  <si>
+    <t>Registration succeeds, stores user session, and auto-routes to dashboard layout</t>
+  </si>
+  <si>
+    <t>0.82s</t>
+  </si>
+  <si>
+    <t>TC-SEL-06</t>
+  </si>
+  <si>
+    <t>Validate login empty fields boundary rules</t>
+  </si>
+  <si>
+    <t>Form prevents submission or displays missing fields prompt</t>
+  </si>
+  <si>
+    <t>0.20s</t>
+  </si>
+  <si>
+    <t>TC-SEL-07</t>
+  </si>
+  <si>
+    <t>Validate login password length boundaries</t>
+  </si>
+  <si>
+    <t>0.33s</t>
+  </si>
+  <si>
+    <t>TC-SEL-08</t>
+  </si>
+  <si>
+    <t>Validate wrong password credential error boundary</t>
+  </si>
+  <si>
+    <t>Error message: "Invalid email or password credential." displays</t>
+  </si>
+  <si>
+    <t>0.29s</t>
+  </si>
+  <si>
+    <t>TC-SEL-09</t>
+  </si>
+  <si>
+    <t>Verify successful authentication for Admin Manager role</t>
+  </si>
+  <si>
+    <t>Login succeeds and redirects to dashboard with active sidebar</t>
+  </si>
+  <si>
+    <t>0.31s</t>
+  </si>
+  <si>
+    <t>TC-SEL-10</t>
+  </si>
+  <si>
+    <t>Verify Remember Me session storage persistence behavior</t>
+  </si>
+  <si>
+    <t>Session remains cached in localStorage when remember check is checked</t>
+  </si>
+  <si>
+    <t>0.42s</t>
+  </si>
+  <si>
+    <t>TC-SEL-11</t>
+  </si>
+  <si>
+    <t>Verify dashboard panels load initial default budgeting summary cards</t>
+  </si>
+  <si>
+    <t>Total Balance, Total Income, and Total Expenses load correctly</t>
+  </si>
+  <si>
+    <t>0.24s</t>
+  </si>
+  <si>
+    <t>TC-SEL-12</t>
+  </si>
+  <si>
+    <t>Verify dashboard net balance math matches initial static transactions</t>
+  </si>
+  <si>
+    <t>Balance equals total income minus total expenses</t>
+  </si>
+  <si>
+    <t>0.06s</t>
+  </si>
+  <si>
+    <t>TC-SEL-13</t>
+  </si>
+  <si>
+    <t>Verify dashboard search bar resolves real-time query list matches</t>
+  </si>
+  <si>
+    <t>Typing transaction names filters matching rows dynamically</t>
+  </si>
+  <si>
+    <t>0.15s</t>
+  </si>
+  <si>
+    <t>TC-SEL-14</t>
+  </si>
+  <si>
+    <t>Verify add income inflow category transaction form submission flow</t>
+  </si>
+  <si>
+    <t>Inflow transaction added and net balance increases accordingly</t>
+  </si>
+  <si>
+    <t>0.57s</t>
+  </si>
+  <si>
+    <t>TC-SEL-15</t>
+  </si>
+  <si>
+    <t>Validate income forms empty constraints boundaries</t>
+  </si>
+  <si>
+    <t>Missing required inputs prevent transaction submission</t>
+  </si>
+  <si>
+    <t>0.14s</t>
+  </si>
+  <si>
+    <t>TC-SEL-16</t>
+  </si>
+  <si>
+    <t>Verify delete income transaction adjusts total calculations</t>
+  </si>
+  <si>
+    <t>Removing an income transaction successfully reduces total balance</t>
+  </si>
+  <si>
+    <t>0.22s</t>
+  </si>
+  <si>
+    <t>TC-SEL-17</t>
+  </si>
+  <si>
+    <t>Verify add expense outflow category transaction successfully updates calculations</t>
+  </si>
+  <si>
+    <t>Outflow transaction decreases net balance</t>
+  </si>
+  <si>
     <t>0.54s</t>
   </si>
   <si>
-    <t>TC-SEL-02</t>
-  </si>
-  <si>
-    <t>Validate password mismatch constraint</t>
-  </si>
-  <si>
-    <t>Error message: "Passwords do not match." displays on password verification mismatch</t>
-  </si>
-  <si>
-    <t>0.56s</t>
-  </si>
-  <si>
-    <t>TC-SEL-03</t>
-  </si>
-  <si>
-    <t>Validate password minimum length validation constraint</t>
-  </si>
-  <si>
-    <t>Error message: "Password must be at least 8 characters." displays</t>
-  </si>
-  <si>
-    <t>0.53s</t>
-  </si>
-  <si>
-    <t>TC-SEL-04</t>
-  </si>
-  <si>
-    <t>Validate signup with duplicate email restriction</t>
-  </si>
-  <si>
-    <t>Error message: "Email address already registered." displays</t>
-  </si>
-  <si>
-    <t>TC-SEL-05</t>
-  </si>
-  <si>
-    <t>Verify successful user signup and redirect to main Dashboard view</t>
-  </si>
-  <si>
-    <t>Registration succeeds, stores user session, and auto-routes to dashboard layout</t>
-  </si>
-  <si>
-    <t>0.71s</t>
-  </si>
-  <si>
-    <t>TC-SEL-06</t>
-  </si>
-  <si>
-    <t>Validate login empty fields boundary rules</t>
-  </si>
-  <si>
-    <t>Form prevents submission or displays missing fields prompt</t>
-  </si>
-  <si>
-    <t>0.22s</t>
-  </si>
-  <si>
-    <t>TC-SEL-07</t>
-  </si>
-  <si>
-    <t>Validate login password length boundaries</t>
-  </si>
-  <si>
-    <t>0.35s</t>
-  </si>
-  <si>
-    <t>TC-SEL-08</t>
-  </si>
-  <si>
-    <t>Validate wrong password credential error boundary</t>
-  </si>
-  <si>
-    <t>Error message: "Invalid email or password credential." displays</t>
-  </si>
-  <si>
-    <t>0.32s</t>
-  </si>
-  <si>
-    <t>TC-SEL-09</t>
-  </si>
-  <si>
-    <t>Verify successful authentication for Admin Manager role</t>
-  </si>
-  <si>
-    <t>Login succeeds and redirects to dashboard with active sidebar</t>
-  </si>
-  <si>
-    <t>0.33s</t>
-  </si>
-  <si>
-    <t>TC-SEL-10</t>
-  </si>
-  <si>
-    <t>Verify Remember Me session storage persistence behavior</t>
-  </si>
-  <si>
-    <t>Session remains cached in localStorage when remember check is checked</t>
-  </si>
-  <si>
-    <t>0.46s</t>
-  </si>
-  <si>
-    <t>TC-SEL-11</t>
-  </si>
-  <si>
-    <t>Verify dashboard panels load initial default budgeting summary cards</t>
-  </si>
-  <si>
-    <t>Total Balance, Total Income, and Total Expenses load correctly</t>
-  </si>
-  <si>
-    <t>0.28s</t>
-  </si>
-  <si>
-    <t>TC-SEL-12</t>
-  </si>
-  <si>
-    <t>Verify dashboard net balance math matches initial static transactions</t>
-  </si>
-  <si>
-    <t>Balance equals total income minus total expenses</t>
+    <t>TC-SEL-18</t>
+  </si>
+  <si>
+    <t>Validate numeric constraints on amount inputs preventing non-numerical submission</t>
+  </si>
+  <si>
+    <t>Negative or text values in amount are rejected</t>
   </si>
   <si>
     <t>0.07s</t>
   </si>
   <si>
-    <t>TC-SEL-13</t>
-  </si>
-  <si>
-    <t>Verify dashboard search bar resolves real-time query list matches</t>
-  </si>
-  <si>
-    <t>Typing transaction names filters matching rows dynamically</t>
-  </si>
-  <si>
-    <t>0.19s</t>
-  </si>
-  <si>
-    <t>TC-SEL-14</t>
-  </si>
-  <si>
-    <t>Verify add income inflow category transaction form submission flow</t>
-  </si>
-  <si>
-    <t>Inflow transaction added and net balance increases accordingly</t>
-  </si>
-  <si>
-    <t>0.74s</t>
-  </si>
-  <si>
-    <t>TC-SEL-15</t>
-  </si>
-  <si>
-    <t>Validate income forms empty constraints boundaries</t>
-  </si>
-  <si>
-    <t>Missing required inputs prevent transaction submission</t>
+    <t>TC-SEL-19</t>
+  </si>
+  <si>
+    <t>Verify delete expense transaction adjustments</t>
+  </si>
+  <si>
+    <t>Deleting an expense successfully restores balance amount</t>
+  </si>
+  <si>
+    <t>0.23s</t>
+  </si>
+  <si>
+    <t>TC-SEL-20</t>
+  </si>
+  <si>
+    <t>Verify category budget cap limit configuration successfully saves limiters</t>
+  </si>
+  <si>
+    <t>Category caps limits are saved and progress bars render</t>
+  </si>
+  <si>
+    <t>0.38s</t>
+  </si>
+  <si>
+    <t>TC-SEL-21</t>
+  </si>
+  <si>
+    <t>Verify category budget warning alert triggers when expense exceeds limit cap</t>
+  </si>
+  <si>
+    <t>Budget Cap overflow modal popup loads when transaction exceeds cap</t>
+  </si>
+  <si>
+    <t>0.84s</t>
+  </si>
+  <si>
+    <t>TC-SEL-22</t>
+  </si>
+  <si>
+    <t>Verify edit category budget limit increases active threshold</t>
+  </si>
+  <si>
+    <t>Updating limit increases budget cap and progress decreases</t>
+  </si>
+  <si>
+    <t>0.30s</t>
+  </si>
+  <si>
+    <t>TC-SEL-23</t>
+  </si>
+  <si>
+    <t>Verify reports dashboard trend chart elements rendering</t>
+  </si>
+  <si>
+    <t>Monthly Balance Trend line container is visible on page</t>
+  </si>
+  <si>
+    <t>0.11s</t>
+  </si>
+  <si>
+    <t>TC-SEL-24</t>
+  </si>
+  <si>
+    <t>Verify category distribution breakdown list aggregates metrics</t>
+  </si>
+  <si>
+    <t>Analytics categories breakdown table loads and sums values</t>
+  </si>
+  <si>
+    <t>TC-SEL-25</t>
+  </si>
+  <si>
+    <t>Verify raw data export reports CSV simulation download trigger</t>
+  </si>
+  <si>
+    <t>Clicking export initializes simulated raw CSV download</t>
+  </si>
+  <si>
+    <t>0.12s</t>
+  </si>
+  <si>
+    <t>TC-SEL-26</t>
+  </si>
+  <si>
+    <t>Verify user profile metadata fields update successfully</t>
+  </si>
+  <si>
+    <t>Display name successfully updates and synchronizes with sidebar user block</t>
   </si>
   <si>
     <t>0.39s</t>
   </si>
   <si>
-    <t>TC-SEL-16</t>
-  </si>
-  <si>
-    <t>Verify delete income transaction adjusts total calculations</t>
-  </si>
-  <si>
-    <t>Removing an income transaction successfully reduces total balance</t>
-  </si>
-  <si>
-    <t>0.26s</t>
-  </si>
-  <si>
-    <t>TC-SEL-17</t>
-  </si>
-  <si>
-    <t>Verify add expense outflow category transaction successfully updates calculations</t>
-  </si>
-  <si>
-    <t>Outflow transaction decreases net balance</t>
-  </si>
-  <si>
-    <t>0.73s</t>
-  </si>
-  <si>
-    <t>TC-SEL-18</t>
-  </si>
-  <si>
-    <t>Validate numeric constraints on amount inputs preventing non-numerical submission</t>
-  </si>
-  <si>
-    <t>Negative or text values in amount are rejected</t>
+    <t>TC-SEL-27</t>
+  </si>
+  <si>
+    <t>Verify preferred default currency synchronization on profile updates</t>
+  </si>
+  <si>
+    <t>Changing currency symbol on profile alters dashboard symbols</t>
+  </si>
+  <si>
+    <t>0.44s</t>
+  </si>
+  <si>
+    <t>TC-SEL-28</t>
+  </si>
+  <si>
+    <t>Verify profile assigned application role is readonly configuration</t>
+  </si>
+  <si>
+    <t>Application role text box contains "readonly" property attribute</t>
+  </si>
+  <si>
+    <t>0.10s</t>
+  </si>
+  <si>
+    <t>TC-SEL-29</t>
+  </si>
+  <si>
+    <t>Verify successful user logout redirects to authentication login view</t>
+  </si>
+  <si>
+    <t>Session clears and client redirects to login view immediately</t>
   </si>
   <si>
     <t>0.09s</t>
   </si>
   <si>
-    <t>TC-SEL-19</t>
-  </si>
-  <si>
-    <t>Verify delete expense transaction adjustments</t>
-  </si>
-  <si>
-    <t>Deleting an expense successfully restores balance amount</t>
-  </si>
-  <si>
-    <t>0.29s</t>
-  </si>
-  <si>
-    <t>TC-SEL-20</t>
-  </si>
-  <si>
-    <t>Verify category budget cap limit configuration successfully saves limiters</t>
-  </si>
-  <si>
-    <t>Category caps limits are saved and progress bars render</t>
-  </si>
-  <si>
-    <t>0.47s</t>
-  </si>
-  <si>
-    <t>TC-SEL-21</t>
-  </si>
-  <si>
-    <t>Verify category budget warning alert triggers when expense exceeds limit cap</t>
-  </si>
-  <si>
-    <t>Budget Cap overflow modal popup loads when transaction exceeds cap</t>
-  </si>
-  <si>
-    <t>1.23s</t>
-  </si>
-  <si>
-    <t>TC-SEL-22</t>
-  </si>
-  <si>
-    <t>Verify edit category budget limit increases active threshold</t>
-  </si>
-  <si>
-    <t>Updating limit increases budget cap and progress decreases</t>
-  </si>
-  <si>
-    <t>0.45s</t>
-  </si>
-  <si>
-    <t>TC-SEL-23</t>
-  </si>
-  <si>
-    <t>Verify reports dashboard trend chart elements rendering</t>
-  </si>
-  <si>
-    <t>Monthly Balance Trend line container is visible on page</t>
-  </si>
-  <si>
-    <t>0.12s</t>
-  </si>
-  <si>
-    <t>TC-SEL-24</t>
-  </si>
-  <si>
-    <t>Verify category distribution breakdown list aggregates metrics</t>
-  </si>
-  <si>
-    <t>Analytics categories breakdown table loads and sums values</t>
-  </si>
-  <si>
-    <t>TC-SEL-25</t>
-  </si>
-  <si>
-    <t>Verify raw data export reports CSV simulation download trigger</t>
-  </si>
-  <si>
-    <t>Clicking export initializes simulated raw CSV download</t>
-  </si>
-  <si>
-    <t>TC-SEL-26</t>
-  </si>
-  <si>
-    <t>Verify user profile metadata fields update successfully</t>
-  </si>
-  <si>
-    <t>Display name successfully updates and synchronizes with sidebar user block</t>
-  </si>
-  <si>
-    <t>TC-SEL-27</t>
-  </si>
-  <si>
-    <t>Verify preferred default currency synchronization on profile updates</t>
-  </si>
-  <si>
-    <t>Changing currency symbol on profile alters dashboard symbols</t>
-  </si>
-  <si>
-    <t>0.43s</t>
-  </si>
-  <si>
-    <t>TC-SEL-28</t>
-  </si>
-  <si>
-    <t>Verify profile assigned application role is readonly configuration</t>
-  </si>
-  <si>
-    <t>Application role text box contains "readonly" property attribute</t>
-  </si>
-  <si>
-    <t>0.31s</t>
-  </si>
-  <si>
-    <t>TC-SEL-29</t>
-  </si>
-  <si>
-    <t>Verify successful user logout redirects to authentication login view</t>
-  </si>
-  <si>
-    <t>Session clears and client redirects to login view immediately</t>
-  </si>
-  <si>
     <t>TC-SEL-30</t>
   </si>
   <si>
@@ -433,9 +445,6 @@
     <t>Inactivity trigger automatically destroys token and redirects to login view</t>
   </si>
   <si>
-    <t>0.41s</t>
-  </si>
-  <si>
     <t>Failure Message</t>
   </si>
   <si>
@@ -460,7 +469,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>16/6/2026, 11:29:49 am</t>
+    <t>6/16/2026, 6:02:08 AM</t>
   </si>
   <si>
     <t>LoginPage</t>
@@ -499,6 +508,9 @@
     <t>Text found: "All fields are required for registration."</t>
   </si>
   <si>
+    <t>6/16/2026, 6:02:09 AM</t>
+  </si>
+  <si>
     <t>Enter register name: Sarah Connor</t>
   </si>
   <si>
@@ -514,9 +526,6 @@
     <t>Entered: SecurePass123!</t>
   </si>
   <si>
-    <t>16/6/2026, 11:29:50 am</t>
-  </si>
-  <si>
     <t>Entered: WrongPass123!</t>
   </si>
   <si>
@@ -526,6 +535,9 @@
     <t>Entered: 12345</t>
   </si>
   <si>
+    <t>6/16/2026, 6:02:10 AM</t>
+  </si>
+  <si>
     <t>Text found: "Password must be at least 8 characters."</t>
   </si>
   <si>
@@ -544,12 +556,12 @@
     <t>Entered: SmartBudgetPass123!</t>
   </si>
   <si>
-    <t>16/6/2026, 11:29:51 am</t>
-  </si>
-  <si>
     <t>Text found: "Email address already registered."</t>
   </si>
   <si>
+    <t>6/16/2026, 6:02:11 AM</t>
+  </si>
+  <si>
     <t>Entered: SarahPass123!</t>
   </si>
   <si>
@@ -562,9 +574,6 @@
     <t xml:space="preserve">Enter login email: </t>
   </si>
   <si>
-    <t>16/6/2026, 11:29:52 am</t>
-  </si>
-  <si>
     <t>Enter login password</t>
   </si>
   <si>
@@ -583,6 +592,9 @@
     <t>Entered: user@budget.com</t>
   </si>
   <si>
+    <t>6/16/2026, 6:02:12 AM</t>
+  </si>
+  <si>
     <t>Entered: 123</t>
   </si>
   <si>
@@ -592,7 +604,7 @@
     <t>Text found: "Invalid email or password credential."</t>
   </si>
   <si>
-    <t>16/6/2026, 11:29:53 am</t>
+    <t>6/16/2026, 6:02:13 AM</t>
   </si>
   <si>
     <t>Check Remember Me option</t>
@@ -628,9 +640,6 @@
     <t>Navigate to tab: nav-income</t>
   </si>
   <si>
-    <t>16/6/2026, 11:29:54 am</t>
-  </si>
-  <si>
     <t>Select income category: Salary</t>
   </si>
   <si>
@@ -655,12 +664,12 @@
     <t>Text found: "$5,910.00"</t>
   </si>
   <si>
+    <t>6/16/2026, 6:02:14 AM</t>
+  </si>
+  <si>
     <t>Click submit button on empty form</t>
   </si>
   <si>
-    <t>16/6/2026, 11:29:55 am</t>
-  </si>
-  <si>
     <t>Navigate to tab: nav-dashboard</t>
   </si>
   <si>
@@ -697,7 +706,7 @@
     <t>Text found: "$790.00"</t>
   </si>
   <si>
-    <t>16/6/2026, 11:29:56 am</t>
+    <t>6/16/2026, 6:02:15 AM</t>
   </si>
   <si>
     <t>Delete first expense transaction</t>
@@ -736,9 +745,6 @@
 $0.00 / $1500.00 (0%)"</t>
   </si>
   <si>
-    <t>16/6/2026, 11:29:57 am</t>
-  </si>
-  <si>
     <t>Select budget segment: Shopping</t>
   </si>
   <si>
@@ -754,6 +760,9 @@
     <t>Select expense category: Shopping</t>
   </si>
   <si>
+    <t>6/16/2026, 6:02:16 AM</t>
+  </si>
+  <si>
     <t>Enter expense amount: 250</t>
   </si>
   <si>
@@ -764,9 +773,6 @@
   </si>
   <si>
     <t>Entered: Designer sneakers</t>
-  </si>
-  <si>
-    <t>16/6/2026, 11:29:58 am</t>
   </si>
   <si>
     <t>Acknowledge budget cap warning dialog</t>
@@ -807,10 +813,10 @@
 $250.00 (33%)"</t>
   </si>
   <si>
+    <t>6/16/2026, 6:02:17 AM</t>
+  </si>
+  <si>
     <t>Click Export Raw Data button</t>
-  </si>
-  <si>
-    <t>16/6/2026, 11:29:59 am</t>
   </si>
   <si>
     <t>Navigate to tab: nav-profile</t>
@@ -1501,21 +1507,21 @@
         <v>28</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>27</v>
@@ -1524,21 +1530,21 @@
         <v>28</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>27</v>
@@ -1547,18 +1553,18 @@
         <v>28</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>36</v>
@@ -1570,21 +1576,21 @@
         <v>28</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1593,21 +1599,21 @@
         <v>28</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>27</v>
@@ -1616,21 +1622,21 @@
         <v>28</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
@@ -1639,21 +1645,21 @@
         <v>28</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>27</v>
@@ -1662,21 +1668,21 @@
         <v>28</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>27</v>
@@ -1685,21 +1691,21 @@
         <v>28</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
@@ -1708,21 +1714,21 @@
         <v>28</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>27</v>
@@ -1731,21 +1737,21 @@
         <v>28</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>27</v>
@@ -1754,21 +1760,21 @@
         <v>28</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>27</v>
@@ -1777,21 +1783,21 @@
         <v>28</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>27</v>
@@ -1800,21 +1806,21 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -1823,21 +1829,21 @@
         <v>28</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>27</v>
@@ -1846,21 +1852,21 @@
         <v>28</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>27</v>
@@ -1869,21 +1875,21 @@
         <v>28</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>27</v>
@@ -1892,21 +1898,21 @@
         <v>28</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>27</v>
@@ -1915,21 +1921,21 @@
         <v>28</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>27</v>
@@ -1938,21 +1944,21 @@
         <v>28</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>27</v>
@@ -1961,21 +1967,21 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -1984,21 +1990,21 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>27</v>
@@ -2007,21 +2013,21 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>37</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
@@ -2030,21 +2036,21 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>27</v>
@@ -2053,21 +2059,21 @@
         <v>28</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>27</v>
@@ -2076,21 +2082,21 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>27</v>
@@ -2099,7 +2105,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>139</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2131,10 +2137,10 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2145,10 +2151,10 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>7</v>
@@ -2174,143 +2180,143 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>24</v>
@@ -2327,109 +2333,109 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
@@ -2446,109 +2452,109 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>24</v>
@@ -2565,109 +2571,109 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
@@ -2684,115 +2690,115 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>28</v>
@@ -2803,81 +2809,81 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>28</v>
@@ -2888,81 +2894,81 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>28</v>
@@ -2973,81 +2979,81 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>28</v>
@@ -3058,19 +3064,19 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -3078,16 +3084,16 @@
         <v>192</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -3095,16 +3101,16 @@
         <v>192</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -3115,7 +3121,7 @@
         <v>24</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>28</v>
@@ -3129,16 +3135,16 @@
         <v>192</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -3146,16 +3152,16 @@
         <v>192</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -3163,61 +3169,61 @@
         <v>192</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>28</v>
@@ -3228,30 +3234,30 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>28</v>
@@ -3262,64 +3268,64 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>28</v>
@@ -3330,47 +3336,47 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>28</v>
@@ -3381,132 +3387,132 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>28</v>
@@ -3517,47 +3523,47 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>28</v>
@@ -3568,81 +3574,81 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>28</v>
@@ -3653,132 +3659,132 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D89" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D95" s="6" t="s">
         <v>28</v>
@@ -3789,30 +3795,30 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D96" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D97" s="6" t="s">
         <v>28</v>
@@ -3823,81 +3829,81 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D101" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D102" s="6" t="s">
         <v>28</v>
@@ -3908,98 +3914,98 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D103" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D104" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D105" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D106" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D107" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D108" s="6" t="s">
         <v>28</v>
@@ -4010,183 +4016,183 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C112" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B112" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>234</v>
-      </c>
       <c r="D112" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D113" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D119" s="6" t="s">
         <v>28</v>
@@ -4197,98 +4203,98 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D121" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D122" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D123" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D125" s="6" t="s">
         <v>28</v>
@@ -4299,30 +4305,30 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D127" s="6" t="s">
         <v>28</v>
@@ -4333,47 +4339,47 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D128" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D129" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>28</v>
@@ -4384,30 +4390,30 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D131" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>28</v>
@@ -4418,98 +4424,98 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D133" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D135" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D137" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D138" s="6" t="s">
         <v>28</v>
@@ -4520,115 +4526,115 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D139" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D141" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D142" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D143" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D144" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D145" s="6" t="s">
         <v>28</v>
@@ -4639,30 +4645,30 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="5" t="s">
-        <v>3</v>
+        <v>258</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D146" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
-        <v>3</v>
+        <v>258</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D147" s="6" t="s">
         <v>28</v>
@@ -4676,16 +4682,16 @@
         <v>3</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D148" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -4696,7 +4702,7 @@
         <v>24</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D149" s="6" t="s">
         <v>28</v>
@@ -4713,7 +4719,7 @@
         <v>24</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D150" s="6" t="s">
         <v>28</v>

--- a/reports/Selenium_Report.xlsx
+++ b/reports/Selenium_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="266">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/16/2026, 7:21:07 AM</t>
+    <t>6/16/2026, 7:31:07 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>9.95s</t>
+    <t>10.54s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,7 +103,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>0.72s</t>
+    <t>0.73s</t>
   </si>
   <si>
     <t>TC-SEL-02</t>
@@ -115,7 +115,7 @@
     <t>Error message: "Passwords do not match." displays on password verification mismatch</t>
   </si>
   <si>
-    <t>0.63s</t>
+    <t>0.66s</t>
   </si>
   <si>
     <t>TC-SEL-03</t>
@@ -127,7 +127,7 @@
     <t>Error message: "Password must be at least 8 characters." displays</t>
   </si>
   <si>
-    <t>0.48s</t>
+    <t>0.52s</t>
   </si>
   <si>
     <t>TC-SEL-04</t>
@@ -151,7 +151,7 @@
     <t>Registration succeeds, stores user session, and auto-routes to dashboard layout</t>
   </si>
   <si>
-    <t>0.73s</t>
+    <t>0.75s</t>
   </si>
   <si>
     <t>TC-SEL-06</t>
@@ -163,156 +163,156 @@
     <t>Form prevents submission or displays missing fields prompt</t>
   </si>
   <si>
+    <t>0.21s</t>
+  </si>
+  <si>
+    <t>TC-SEL-07</t>
+  </si>
+  <si>
+    <t>Validate login password length boundaries</t>
+  </si>
+  <si>
+    <t>0.34s</t>
+  </si>
+  <si>
+    <t>TC-SEL-08</t>
+  </si>
+  <si>
+    <t>Validate wrong password credential error boundary</t>
+  </si>
+  <si>
+    <t>Error message: "Invalid email or password credential." displays</t>
+  </si>
+  <si>
+    <t>0.31s</t>
+  </si>
+  <si>
+    <t>TC-SEL-09</t>
+  </si>
+  <si>
+    <t>Verify successful authentication for Admin Manager role</t>
+  </si>
+  <si>
+    <t>Login succeeds and redirects to dashboard with active sidebar</t>
+  </si>
+  <si>
+    <t>TC-SEL-10</t>
+  </si>
+  <si>
+    <t>Verify Remember Me session storage persistence behavior</t>
+  </si>
+  <si>
+    <t>Session remains cached in localStorage when remember check is checked</t>
+  </si>
+  <si>
+    <t>0.46s</t>
+  </si>
+  <si>
+    <t>TC-SEL-11</t>
+  </si>
+  <si>
+    <t>Verify dashboard panels load initial default budgeting summary cards</t>
+  </si>
+  <si>
+    <t>Total Balance, Total Income, and Total Expenses load correctly</t>
+  </si>
+  <si>
+    <t>0.18s</t>
+  </si>
+  <si>
+    <t>TC-SEL-12</t>
+  </si>
+  <si>
+    <t>Verify dashboard net balance math matches initial static transactions</t>
+  </si>
+  <si>
+    <t>Balance equals total income minus total expenses</t>
+  </si>
+  <si>
+    <t>0.06s</t>
+  </si>
+  <si>
+    <t>TC-SEL-13</t>
+  </si>
+  <si>
+    <t>Verify dashboard search bar resolves real-time query list matches</t>
+  </si>
+  <si>
+    <t>Typing transaction names filters matching rows dynamically</t>
+  </si>
+  <si>
+    <t>0.16s</t>
+  </si>
+  <si>
+    <t>TC-SEL-14</t>
+  </si>
+  <si>
+    <t>Verify add income inflow category transaction form submission flow</t>
+  </si>
+  <si>
+    <t>Inflow transaction added and net balance increases accordingly</t>
+  </si>
+  <si>
+    <t>TC-SEL-15</t>
+  </si>
+  <si>
+    <t>Validate income forms empty constraints boundaries</t>
+  </si>
+  <si>
+    <t>Missing required inputs prevent transaction submission</t>
+  </si>
+  <si>
+    <t>0.14s</t>
+  </si>
+  <si>
+    <t>TC-SEL-16</t>
+  </si>
+  <si>
+    <t>Verify delete income transaction adjusts total calculations</t>
+  </si>
+  <si>
+    <t>Removing an income transaction successfully reduces total balance</t>
+  </si>
+  <si>
+    <t>0.24s</t>
+  </si>
+  <si>
+    <t>TC-SEL-17</t>
+  </si>
+  <si>
+    <t>Verify add expense outflow category transaction successfully updates calculations</t>
+  </si>
+  <si>
+    <t>Outflow transaction decreases net balance</t>
+  </si>
+  <si>
+    <t>0.56s</t>
+  </si>
+  <si>
+    <t>TC-SEL-18</t>
+  </si>
+  <si>
+    <t>Validate numeric constraints on amount inputs preventing non-numerical submission</t>
+  </si>
+  <si>
+    <t>Negative or text values in amount are rejected</t>
+  </si>
+  <si>
+    <t>0.09s</t>
+  </si>
+  <si>
+    <t>TC-SEL-19</t>
+  </si>
+  <si>
+    <t>Verify delete expense transaction adjustments</t>
+  </si>
+  <si>
+    <t>Deleting an expense successfully restores balance amount</t>
+  </si>
+  <si>
     <t>0.20s</t>
   </si>
   <si>
-    <t>TC-SEL-07</t>
-  </si>
-  <si>
-    <t>Validate login password length boundaries</t>
-  </si>
-  <si>
-    <t>0.30s</t>
-  </si>
-  <si>
-    <t>TC-SEL-08</t>
-  </si>
-  <si>
-    <t>Validate wrong password credential error boundary</t>
-  </si>
-  <si>
-    <t>Error message: "Invalid email or password credential." displays</t>
-  </si>
-  <si>
-    <t>0.29s</t>
-  </si>
-  <si>
-    <t>TC-SEL-09</t>
-  </si>
-  <si>
-    <t>Verify successful authentication for Admin Manager role</t>
-  </si>
-  <si>
-    <t>Login succeeds and redirects to dashboard with active sidebar</t>
-  </si>
-  <si>
-    <t>TC-SEL-10</t>
-  </si>
-  <si>
-    <t>Verify Remember Me session storage persistence behavior</t>
-  </si>
-  <si>
-    <t>Session remains cached in localStorage when remember check is checked</t>
-  </si>
-  <si>
-    <t>0.46s</t>
-  </si>
-  <si>
-    <t>TC-SEL-11</t>
-  </si>
-  <si>
-    <t>Verify dashboard panels load initial default budgeting summary cards</t>
-  </si>
-  <si>
-    <t>Total Balance, Total Income, and Total Expenses load correctly</t>
-  </si>
-  <si>
-    <t>0.32s</t>
-  </si>
-  <si>
-    <t>TC-SEL-12</t>
-  </si>
-  <si>
-    <t>Verify dashboard net balance math matches initial static transactions</t>
-  </si>
-  <si>
-    <t>Balance equals total income minus total expenses</t>
-  </si>
-  <si>
-    <t>0.06s</t>
-  </si>
-  <si>
-    <t>TC-SEL-13</t>
-  </si>
-  <si>
-    <t>Verify dashboard search bar resolves real-time query list matches</t>
-  </si>
-  <si>
-    <t>Typing transaction names filters matching rows dynamically</t>
-  </si>
-  <si>
-    <t>0.15s</t>
-  </si>
-  <si>
-    <t>TC-SEL-14</t>
-  </si>
-  <si>
-    <t>Verify add income inflow category transaction form submission flow</t>
-  </si>
-  <si>
-    <t>Inflow transaction added and net balance increases accordingly</t>
-  </si>
-  <si>
-    <t>TC-SEL-15</t>
-  </si>
-  <si>
-    <t>Validate income forms empty constraints boundaries</t>
-  </si>
-  <si>
-    <t>Missing required inputs prevent transaction submission</t>
-  </si>
-  <si>
-    <t>0.14s</t>
-  </si>
-  <si>
-    <t>TC-SEL-16</t>
-  </si>
-  <si>
-    <t>Verify delete income transaction adjusts total calculations</t>
-  </si>
-  <si>
-    <t>Removing an income transaction successfully reduces total balance</t>
-  </si>
-  <si>
-    <t>0.21s</t>
-  </si>
-  <si>
-    <t>TC-SEL-17</t>
-  </si>
-  <si>
-    <t>Verify add expense outflow category transaction successfully updates calculations</t>
-  </si>
-  <si>
-    <t>Outflow transaction decreases net balance</t>
-  </si>
-  <si>
-    <t>0.53s</t>
-  </si>
-  <si>
-    <t>TC-SEL-18</t>
-  </si>
-  <si>
-    <t>Validate numeric constraints on amount inputs preventing non-numerical submission</t>
-  </si>
-  <si>
-    <t>Negative or text values in amount are rejected</t>
-  </si>
-  <si>
-    <t>0.07s</t>
-  </si>
-  <si>
-    <t>TC-SEL-19</t>
-  </si>
-  <si>
-    <t>Verify delete expense transaction adjustments</t>
-  </si>
-  <si>
-    <t>Deleting an expense successfully restores balance amount</t>
-  </si>
-  <si>
-    <t>0.17s</t>
-  </si>
-  <si>
     <t>TC-SEL-20</t>
   </si>
   <si>
@@ -322,7 +322,7 @@
     <t>Category caps limits are saved and progress bars render</t>
   </si>
   <si>
-    <t>0.35s</t>
+    <t>0.41s</t>
   </si>
   <si>
     <t>TC-SEL-21</t>
@@ -334,7 +334,7 @@
     <t>Budget Cap overflow modal popup loads when transaction exceeds cap</t>
   </si>
   <si>
-    <t>0.77s</t>
+    <t>0.87s</t>
   </si>
   <si>
     <t>TC-SEL-22</t>
@@ -355,7 +355,7 @@
     <t>Monthly Balance Trend line container is visible on page</t>
   </si>
   <si>
-    <t>0.10s</t>
+    <t>0.12s</t>
   </si>
   <si>
     <t>TC-SEL-24</t>
@@ -367,18 +367,18 @@
     <t>Analytics categories breakdown table loads and sums values</t>
   </si>
   <si>
+    <t>TC-SEL-25</t>
+  </si>
+  <si>
+    <t>Verify raw data export reports CSV simulation download trigger</t>
+  </si>
+  <si>
+    <t>Clicking export initializes simulated raw CSV download</t>
+  </si>
+  <si>
     <t>0.11s</t>
   </si>
   <si>
-    <t>TC-SEL-25</t>
-  </si>
-  <si>
-    <t>Verify raw data export reports CSV simulation download trigger</t>
-  </si>
-  <si>
-    <t>Clicking export initializes simulated raw CSV download</t>
-  </si>
-  <si>
     <t>TC-SEL-26</t>
   </si>
   <si>
@@ -388,9 +388,6 @@
     <t>Display name successfully updates and synchronizes with sidebar user block</t>
   </si>
   <si>
-    <t>0.40s</t>
-  </si>
-  <si>
     <t>TC-SEL-27</t>
   </si>
   <si>
@@ -400,6 +397,9 @@
     <t>Changing currency symbol on profile alters dashboard symbols</t>
   </si>
   <si>
+    <t>0.42s</t>
+  </si>
+  <si>
     <t>TC-SEL-28</t>
   </si>
   <si>
@@ -421,9 +421,6 @@
     <t>Session clears and client redirects to login view immediately</t>
   </si>
   <si>
-    <t>0.09s</t>
-  </si>
-  <si>
     <t>TC-SEL-30</t>
   </si>
   <si>
@@ -433,7 +430,7 @@
     <t>Inactivity trigger automatically destroys token and redirects to login view</t>
   </si>
   <si>
-    <t>0.26s</t>
+    <t>0.39s</t>
   </si>
   <si>
     <t>Failure Message</t>
@@ -460,7 +457,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>6/16/2026, 7:20:58 AM</t>
+    <t>6/16/2026, 7:30:58 AM</t>
   </si>
   <si>
     <t>LoginPage</t>
@@ -493,9 +490,6 @@
     <t>Click Sign Up Button</t>
   </si>
   <si>
-    <t>6/16/2026, 7:20:59 AM</t>
-  </si>
-  <si>
     <t>Get registration error message</t>
   </si>
   <si>
@@ -517,6 +511,9 @@
     <t>Entered: SecurePass123!</t>
   </si>
   <si>
+    <t>6/16/2026, 7:30:59 AM</t>
+  </si>
+  <si>
     <t>Entered: WrongPass123!</t>
   </si>
   <si>
@@ -526,9 +523,6 @@
     <t>Entered: 12345</t>
   </si>
   <si>
-    <t>6/16/2026, 7:21:00 AM</t>
-  </si>
-  <si>
     <t>Text found: "Password must be at least 8 characters."</t>
   </si>
   <si>
@@ -544,6 +538,9 @@
     <t>Entered: admin@budget.com</t>
   </si>
   <si>
+    <t>6/16/2026, 7:31:00 AM</t>
+  </si>
+  <si>
     <t>Entered: SmartBudgetPass123!</t>
   </si>
   <si>
@@ -553,15 +550,15 @@
     <t>Entered: SarahPass123!</t>
   </si>
   <si>
-    <t>6/16/2026, 7:21:01 AM</t>
-  </si>
-  <si>
     <t>DashboardPage</t>
   </si>
   <si>
     <t>Click Logout Button</t>
   </si>
   <si>
+    <t>6/16/2026, 7:31:01 AM</t>
+  </si>
+  <si>
     <t xml:space="preserve">Enter login email: </t>
   </si>
   <si>
@@ -586,21 +583,18 @@
     <t>Entered: 123</t>
   </si>
   <si>
-    <t>6/16/2026, 7:21:02 AM</t>
-  </si>
-  <si>
     <t>Enter login email: admin@budget.com</t>
   </si>
   <si>
     <t>Text found: "Invalid email or password credential."</t>
   </si>
   <si>
+    <t>6/16/2026, 7:31:02 AM</t>
+  </si>
+  <si>
     <t>Check Remember Me option</t>
   </si>
   <si>
-    <t>6/16/2026, 7:21:03 AM</t>
-  </si>
-  <si>
     <t>Read total balance statistic</t>
   </si>
   <si>
@@ -628,6 +622,9 @@
     <t>Clear query</t>
   </si>
   <si>
+    <t>6/16/2026, 7:31:03 AM</t>
+  </si>
+  <si>
     <t>Navigate to tab: nav-income</t>
   </si>
   <si>
@@ -658,9 +655,6 @@
     <t>Click submit button on empty form</t>
   </si>
   <si>
-    <t>6/16/2026, 7:21:04 AM</t>
-  </si>
-  <si>
     <t>Navigate to tab: nav-dashboard</t>
   </si>
   <si>
@@ -673,6 +667,9 @@
     <t>Navigate to tab: nav-expense</t>
   </si>
   <si>
+    <t>6/16/2026, 7:31:04 AM</t>
+  </si>
+  <si>
     <t>Select expense category: Food</t>
   </si>
   <si>
@@ -703,9 +700,6 @@
     <t>Text found: "$1,990.00"</t>
   </si>
   <si>
-    <t>6/16/2026, 7:21:05 AM</t>
-  </si>
-  <si>
     <t>Navigate to tab: nav-budget</t>
   </si>
   <si>
@@ -716,6 +710,9 @@
   </si>
   <si>
     <t>Entered: 600</t>
+  </si>
+  <si>
+    <t>6/16/2026, 7:31:05 AM</t>
   </si>
   <si>
     <t>Click Save Budget Allocation button</t>
@@ -763,10 +760,10 @@
     <t>Entered: Designer sneakers</t>
   </si>
   <si>
-    <t>6/16/2026, 7:21:06 AM</t>
-  </si>
-  <si>
     <t>Acknowledge budget cap warning dialog</t>
+  </si>
+  <si>
+    <t>6/16/2026, 7:31:06 AM</t>
   </si>
   <si>
     <t>Enter budget cap limit: 1000</t>
@@ -1909,7 +1906,7 @@
         <v>28</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1955,21 +1952,21 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -1978,7 +1975,7 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2001,21 +1998,21 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
@@ -2024,7 +2021,7 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2070,21 +2067,21 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C31" s="3" t="s">
+      <c r="D31" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>27</v>
@@ -2093,7 +2090,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -2125,10 +2122,10 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2139,10 +2136,10 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>7</v>
@@ -2168,143 +2165,143 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>146</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>159</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>24</v>
@@ -2321,109 +2318,109 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
@@ -2440,109 +2437,109 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>24</v>
@@ -2559,109 +2556,109 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>172</v>
-      </c>
       <c r="D24" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
@@ -2678,109 +2675,109 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="D36" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>24</v>
@@ -2797,75 +2794,75 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C41" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E41" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>24</v>
@@ -2882,75 +2879,75 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C43" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E43" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>24</v>
@@ -2967,75 +2964,75 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>24</v>
@@ -3052,58 +3049,58 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>24</v>
@@ -3120,92 +3117,92 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>24</v>
@@ -3222,24 +3219,24 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E63" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>24</v>
@@ -3256,58 +3253,58 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E65" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>24</v>
@@ -3324,41 +3321,41 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>24</v>
@@ -3375,126 +3372,126 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C74" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E74" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="D74" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C75" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E75" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="D75" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C76" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E76" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>24</v>
@@ -3511,41 +3508,41 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>24</v>
@@ -3562,75 +3559,75 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B85" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>216</v>
-      </c>
       <c r="D85" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>24</v>
@@ -3647,126 +3644,126 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D89" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C90" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E90" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="D90" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C91" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E91" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C92" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E92" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="D92" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>24</v>
@@ -3783,24 +3780,24 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D96" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>24</v>
@@ -3817,75 +3814,75 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D101" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>24</v>
@@ -3902,92 +3899,92 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D103" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C104" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B104" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>231</v>
-      </c>
       <c r="D104" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D105" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D106" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C107" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E107" s="3" t="s">
         <v>235</v>
-      </c>
-      <c r="D107" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E107" s="3" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>24</v>
@@ -4004,177 +4001,177 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C110" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E110" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="D110" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C111" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E111" s="3" t="s">
         <v>239</v>
-      </c>
-      <c r="D111" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D113" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C115" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E115" s="3" t="s">
         <v>242</v>
-      </c>
-      <c r="D115" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C116" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E116" s="3" t="s">
         <v>244</v>
-      </c>
-      <c r="D116" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>24</v>
@@ -4194,16 +4191,16 @@
         <v>246</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -4211,16 +4208,16 @@
         <v>246</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D121" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -4228,16 +4225,16 @@
         <v>246</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C122" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D122" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E122" s="3" t="s">
         <v>248</v>
-      </c>
-      <c r="D122" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
@@ -4245,16 +4242,16 @@
         <v>246</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D123" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
@@ -4262,16 +4259,16 @@
         <v>246</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C124" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D124" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E124" s="3" t="s">
         <v>250</v>
-      </c>
-      <c r="D124" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E124" s="3" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
@@ -4296,16 +4293,16 @@
         <v>246</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
@@ -4330,16 +4327,16 @@
         <v>246</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D128" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
@@ -4347,16 +4344,16 @@
         <v>246</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C129" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E129" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="D129" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E129" s="3" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
@@ -4381,16 +4378,16 @@
         <v>246</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D131" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -4401,7 +4398,7 @@
         <v>24</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>28</v>
@@ -4415,16 +4412,16 @@
         <v>246</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D133" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -4432,16 +4429,16 @@
         <v>246</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C134" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E134" s="3" t="s">
         <v>257</v>
-      </c>
-      <c r="D134" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E134" s="3" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
@@ -4449,16 +4446,16 @@
         <v>246</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C135" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="D135" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E135" s="3" t="s">
         <v>259</v>
-      </c>
-      <c r="D135" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E135" s="3" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -4466,16 +4463,16 @@
         <v>3</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -4483,16 +4480,16 @@
         <v>3</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C137" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="D137" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E137" s="3" t="s">
         <v>262</v>
-      </c>
-      <c r="D137" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E137" s="3" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
@@ -4517,16 +4514,16 @@
         <v>3</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D139" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -4534,16 +4531,16 @@
         <v>3</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C140" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D140" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E140" s="3" t="s">
         <v>257</v>
-      </c>
-      <c r="D140" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E140" s="3" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
@@ -4551,16 +4548,16 @@
         <v>3</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C141" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E141" s="3" t="s">
         <v>264</v>
-      </c>
-      <c r="D141" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E141" s="3" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -4568,16 +4565,16 @@
         <v>3</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D142" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
@@ -4585,16 +4582,16 @@
         <v>3</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D143" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -4602,16 +4599,16 @@
         <v>3</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D144" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -4622,7 +4619,7 @@
         <v>24</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D145" s="6" t="s">
         <v>28</v>
@@ -4636,16 +4633,16 @@
         <v>3</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D146" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
@@ -4670,16 +4667,16 @@
         <v>3</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D148" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -4707,7 +4704,7 @@
         <v>24</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D150" s="6" t="s">
         <v>28</v>

--- a/reports/Selenium_Report.xlsx
+++ b/reports/Selenium_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="267">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/16/2026, 7:31:07 AM</t>
+    <t>6/16/2026, 7:34:51 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>10.54s</t>
+    <t>10.85s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,7 +103,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>0.73s</t>
+    <t>0.97s</t>
   </si>
   <si>
     <t>TC-SEL-02</t>
@@ -115,7 +115,7 @@
     <t>Error message: "Passwords do not match." displays on password verification mismatch</t>
   </si>
   <si>
-    <t>0.66s</t>
+    <t>0.81s</t>
   </si>
   <si>
     <t>TC-SEL-03</t>
@@ -127,7 +127,7 @@
     <t>Error message: "Password must be at least 8 characters." displays</t>
   </si>
   <si>
-    <t>0.52s</t>
+    <t>0.51s</t>
   </si>
   <si>
     <t>TC-SEL-04</t>
@@ -139,9 +139,6 @@
     <t>Error message: "Email address already registered." displays</t>
   </si>
   <si>
-    <t>0.59s</t>
-  </si>
-  <si>
     <t>TC-SEL-05</t>
   </si>
   <si>
@@ -151,7 +148,7 @@
     <t>Registration succeeds, stores user session, and auto-routes to dashboard layout</t>
   </si>
   <si>
-    <t>0.75s</t>
+    <t>0.80s</t>
   </si>
   <si>
     <t>TC-SEL-06</t>
@@ -172,54 +169,57 @@
     <t>Validate login password length boundaries</t>
   </si>
   <si>
+    <t>0.32s</t>
+  </si>
+  <si>
+    <t>TC-SEL-08</t>
+  </si>
+  <si>
+    <t>Validate wrong password credential error boundary</t>
+  </si>
+  <si>
+    <t>Error message: "Invalid email or password credential." displays</t>
+  </si>
+  <si>
+    <t>0.29s</t>
+  </si>
+  <si>
+    <t>TC-SEL-09</t>
+  </si>
+  <si>
+    <t>Verify successful authentication for Admin Manager role</t>
+  </si>
+  <si>
+    <t>Login succeeds and redirects to dashboard with active sidebar</t>
+  </si>
+  <si>
+    <t>0.30s</t>
+  </si>
+  <si>
+    <t>TC-SEL-10</t>
+  </si>
+  <si>
+    <t>Verify Remember Me session storage persistence behavior</t>
+  </si>
+  <si>
+    <t>Session remains cached in localStorage when remember check is checked</t>
+  </si>
+  <si>
+    <t>0.43s</t>
+  </si>
+  <si>
+    <t>TC-SEL-11</t>
+  </si>
+  <si>
+    <t>Verify dashboard panels load initial default budgeting summary cards</t>
+  </si>
+  <si>
+    <t>Total Balance, Total Income, and Total Expenses load correctly</t>
+  </si>
+  <si>
     <t>0.34s</t>
   </si>
   <si>
-    <t>TC-SEL-08</t>
-  </si>
-  <si>
-    <t>Validate wrong password credential error boundary</t>
-  </si>
-  <si>
-    <t>Error message: "Invalid email or password credential." displays</t>
-  </si>
-  <si>
-    <t>0.31s</t>
-  </si>
-  <si>
-    <t>TC-SEL-09</t>
-  </si>
-  <si>
-    <t>Verify successful authentication for Admin Manager role</t>
-  </si>
-  <si>
-    <t>Login succeeds and redirects to dashboard with active sidebar</t>
-  </si>
-  <si>
-    <t>TC-SEL-10</t>
-  </si>
-  <si>
-    <t>Verify Remember Me session storage persistence behavior</t>
-  </si>
-  <si>
-    <t>Session remains cached in localStorage when remember check is checked</t>
-  </si>
-  <si>
-    <t>0.46s</t>
-  </si>
-  <si>
-    <t>TC-SEL-11</t>
-  </si>
-  <si>
-    <t>Verify dashboard panels load initial default budgeting summary cards</t>
-  </si>
-  <si>
-    <t>Total Balance, Total Income, and Total Expenses load correctly</t>
-  </si>
-  <si>
-    <t>0.18s</t>
-  </si>
-  <si>
     <t>TC-SEL-12</t>
   </si>
   <si>
@@ -253,6 +253,9 @@
     <t>Inflow transaction added and net balance increases accordingly</t>
   </si>
   <si>
+    <t>0.58s</t>
+  </si>
+  <si>
     <t>TC-SEL-15</t>
   </si>
   <si>
@@ -286,9 +289,6 @@
     <t>Outflow transaction decreases net balance</t>
   </si>
   <si>
-    <t>0.56s</t>
-  </si>
-  <si>
     <t>TC-SEL-18</t>
   </si>
   <si>
@@ -298,129 +298,132 @@
     <t>Negative or text values in amount are rejected</t>
   </si>
   <si>
+    <t>0.08s</t>
+  </si>
+  <si>
+    <t>TC-SEL-19</t>
+  </si>
+  <si>
+    <t>Verify delete expense transaction adjustments</t>
+  </si>
+  <si>
+    <t>Deleting an expense successfully restores balance amount</t>
+  </si>
+  <si>
+    <t>0.19s</t>
+  </si>
+  <si>
+    <t>TC-SEL-20</t>
+  </si>
+  <si>
+    <t>Verify category budget cap limit configuration successfully saves limiters</t>
+  </si>
+  <si>
+    <t>Category caps limits are saved and progress bars render</t>
+  </si>
+  <si>
+    <t>0.39s</t>
+  </si>
+  <si>
+    <t>TC-SEL-21</t>
+  </si>
+  <si>
+    <t>Verify category budget warning alert triggers when expense exceeds limit cap</t>
+  </si>
+  <si>
+    <t>Budget Cap overflow modal popup loads when transaction exceeds cap</t>
+  </si>
+  <si>
+    <t>0.87s</t>
+  </si>
+  <si>
+    <t>TC-SEL-22</t>
+  </si>
+  <si>
+    <t>Verify edit category budget limit increases active threshold</t>
+  </si>
+  <si>
+    <t>Updating limit increases budget cap and progress decreases</t>
+  </si>
+  <si>
+    <t>TC-SEL-23</t>
+  </si>
+  <si>
+    <t>Verify reports dashboard trend chart elements rendering</t>
+  </si>
+  <si>
+    <t>Monthly Balance Trend line container is visible on page</t>
+  </si>
+  <si>
+    <t>0.11s</t>
+  </si>
+  <si>
+    <t>TC-SEL-24</t>
+  </si>
+  <si>
+    <t>Verify category distribution breakdown list aggregates metrics</t>
+  </si>
+  <si>
+    <t>Analytics categories breakdown table loads and sums values</t>
+  </si>
+  <si>
+    <t>0.12s</t>
+  </si>
+  <si>
+    <t>TC-SEL-25</t>
+  </si>
+  <si>
+    <t>Verify raw data export reports CSV simulation download trigger</t>
+  </si>
+  <si>
+    <t>Clicking export initializes simulated raw CSV download</t>
+  </si>
+  <si>
+    <t>TC-SEL-26</t>
+  </si>
+  <si>
+    <t>Verify user profile metadata fields update successfully</t>
+  </si>
+  <si>
+    <t>Display name successfully updates and synchronizes with sidebar user block</t>
+  </si>
+  <si>
+    <t>0.40s</t>
+  </si>
+  <si>
+    <t>TC-SEL-27</t>
+  </si>
+  <si>
+    <t>Verify preferred default currency synchronization on profile updates</t>
+  </si>
+  <si>
+    <t>Changing currency symbol on profile alters dashboard symbols</t>
+  </si>
+  <si>
+    <t>TC-SEL-28</t>
+  </si>
+  <si>
+    <t>Verify profile assigned application role is readonly configuration</t>
+  </si>
+  <si>
+    <t>Application role text box contains "readonly" property attribute</t>
+  </si>
+  <si>
+    <t>0.13s</t>
+  </si>
+  <si>
+    <t>TC-SEL-29</t>
+  </si>
+  <si>
+    <t>Verify successful user logout redirects to authentication login view</t>
+  </si>
+  <si>
+    <t>Session clears and client redirects to login view immediately</t>
+  </si>
+  <si>
     <t>0.09s</t>
   </si>
   <si>
-    <t>TC-SEL-19</t>
-  </si>
-  <si>
-    <t>Verify delete expense transaction adjustments</t>
-  </si>
-  <si>
-    <t>Deleting an expense successfully restores balance amount</t>
-  </si>
-  <si>
-    <t>0.20s</t>
-  </si>
-  <si>
-    <t>TC-SEL-20</t>
-  </si>
-  <si>
-    <t>Verify category budget cap limit configuration successfully saves limiters</t>
-  </si>
-  <si>
-    <t>Category caps limits are saved and progress bars render</t>
-  </si>
-  <si>
-    <t>0.41s</t>
-  </si>
-  <si>
-    <t>TC-SEL-21</t>
-  </si>
-  <si>
-    <t>Verify category budget warning alert triggers when expense exceeds limit cap</t>
-  </si>
-  <si>
-    <t>Budget Cap overflow modal popup loads when transaction exceeds cap</t>
-  </si>
-  <si>
-    <t>0.87s</t>
-  </si>
-  <si>
-    <t>TC-SEL-22</t>
-  </si>
-  <si>
-    <t>Verify edit category budget limit increases active threshold</t>
-  </si>
-  <si>
-    <t>Updating limit increases budget cap and progress decreases</t>
-  </si>
-  <si>
-    <t>TC-SEL-23</t>
-  </si>
-  <si>
-    <t>Verify reports dashboard trend chart elements rendering</t>
-  </si>
-  <si>
-    <t>Monthly Balance Trend line container is visible on page</t>
-  </si>
-  <si>
-    <t>0.12s</t>
-  </si>
-  <si>
-    <t>TC-SEL-24</t>
-  </si>
-  <si>
-    <t>Verify category distribution breakdown list aggregates metrics</t>
-  </si>
-  <si>
-    <t>Analytics categories breakdown table loads and sums values</t>
-  </si>
-  <si>
-    <t>TC-SEL-25</t>
-  </si>
-  <si>
-    <t>Verify raw data export reports CSV simulation download trigger</t>
-  </si>
-  <si>
-    <t>Clicking export initializes simulated raw CSV download</t>
-  </si>
-  <si>
-    <t>0.11s</t>
-  </si>
-  <si>
-    <t>TC-SEL-26</t>
-  </si>
-  <si>
-    <t>Verify user profile metadata fields update successfully</t>
-  </si>
-  <si>
-    <t>Display name successfully updates and synchronizes with sidebar user block</t>
-  </si>
-  <si>
-    <t>TC-SEL-27</t>
-  </si>
-  <si>
-    <t>Verify preferred default currency synchronization on profile updates</t>
-  </si>
-  <si>
-    <t>Changing currency symbol on profile alters dashboard symbols</t>
-  </si>
-  <si>
-    <t>0.42s</t>
-  </si>
-  <si>
-    <t>TC-SEL-28</t>
-  </si>
-  <si>
-    <t>Verify profile assigned application role is readonly configuration</t>
-  </si>
-  <si>
-    <t>Application role text box contains "readonly" property attribute</t>
-  </si>
-  <si>
-    <t>0.13s</t>
-  </si>
-  <si>
-    <t>TC-SEL-29</t>
-  </si>
-  <si>
-    <t>Verify successful user logout redirects to authentication login view</t>
-  </si>
-  <si>
-    <t>Session clears and client redirects to login view immediately</t>
-  </si>
-  <si>
     <t>TC-SEL-30</t>
   </si>
   <si>
@@ -430,9 +433,6 @@
     <t>Inactivity trigger automatically destroys token and redirects to login view</t>
   </si>
   <si>
-    <t>0.39s</t>
-  </si>
-  <si>
     <t>Failure Message</t>
   </si>
   <si>
@@ -457,7 +457,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>6/16/2026, 7:30:58 AM</t>
+    <t>6/16/2026, 7:34:41 AM</t>
   </si>
   <si>
     <t>LoginPage</t>
@@ -496,6 +496,9 @@
     <t>Text found: "All fields are required for registration."</t>
   </si>
   <si>
+    <t>6/16/2026, 7:34:42 AM</t>
+  </si>
+  <si>
     <t>Enter register name: Sarah Connor</t>
   </si>
   <si>
@@ -511,9 +514,6 @@
     <t>Entered: SecurePass123!</t>
   </si>
   <si>
-    <t>6/16/2026, 7:30:59 AM</t>
-  </si>
-  <si>
     <t>Entered: WrongPass123!</t>
   </si>
   <si>
@@ -523,6 +523,9 @@
     <t>Entered: 12345</t>
   </si>
   <si>
+    <t>6/16/2026, 7:34:43 AM</t>
+  </si>
+  <si>
     <t>Text found: "Password must be at least 8 characters."</t>
   </si>
   <si>
@@ -538,15 +541,15 @@
     <t>Entered: admin@budget.com</t>
   </si>
   <si>
-    <t>6/16/2026, 7:31:00 AM</t>
-  </si>
-  <si>
     <t>Entered: SmartBudgetPass123!</t>
   </si>
   <si>
     <t>Text found: "Email address already registered."</t>
   </si>
   <si>
+    <t>6/16/2026, 7:34:44 AM</t>
+  </si>
+  <si>
     <t>Entered: SarahPass123!</t>
   </si>
   <si>
@@ -556,9 +559,6 @@
     <t>Click Logout Button</t>
   </si>
   <si>
-    <t>6/16/2026, 7:31:01 AM</t>
-  </si>
-  <si>
     <t xml:space="preserve">Enter login email: </t>
   </si>
   <si>
@@ -574,6 +574,9 @@
     <t>Text found: ""</t>
   </si>
   <si>
+    <t>6/16/2026, 7:34:45 AM</t>
+  </si>
+  <si>
     <t>Enter login email: user@budget.com</t>
   </si>
   <si>
@@ -589,7 +592,7 @@
     <t>Text found: "Invalid email or password credential."</t>
   </si>
   <si>
-    <t>6/16/2026, 7:31:02 AM</t>
+    <t>6/16/2026, 7:34:46 AM</t>
   </si>
   <si>
     <t>Check Remember Me option</t>
@@ -622,9 +625,6 @@
     <t>Clear query</t>
   </si>
   <si>
-    <t>6/16/2026, 7:31:03 AM</t>
-  </si>
-  <si>
     <t>Navigate to tab: nav-income</t>
   </si>
   <si>
@@ -640,6 +640,9 @@
     <t>Entered: 2500</t>
   </si>
   <si>
+    <t>6/16/2026, 7:34:47 AM</t>
+  </si>
+  <si>
     <t>Enter income description: Part-time consultancy paycheck</t>
   </si>
   <si>
@@ -667,9 +670,6 @@
     <t>Navigate to tab: nav-expense</t>
   </si>
   <si>
-    <t>6/16/2026, 7:31:04 AM</t>
-  </si>
-  <si>
     <t>Select expense category: Food</t>
   </si>
   <si>
@@ -688,6 +688,9 @@
     <t>Entered: Weekly grocery run</t>
   </si>
   <si>
+    <t>6/16/2026, 7:34:48 AM</t>
+  </si>
+  <si>
     <t>Click Log Expense Submit button</t>
   </si>
   <si>
@@ -710,9 +713,6 @@
   </si>
   <si>
     <t>Entered: 600</t>
-  </si>
-  <si>
-    <t>6/16/2026, 7:31:05 AM</t>
   </si>
   <si>
     <t>Click Save Budget Allocation button</t>
@@ -745,6 +745,9 @@
     <t>Entered: 200</t>
   </si>
   <si>
+    <t>6/16/2026, 7:34:49 AM</t>
+  </si>
+  <si>
     <t>Select expense category: Shopping</t>
   </si>
   <si>
@@ -761,9 +764,6 @@
   </si>
   <si>
     <t>Acknowledge budget cap warning dialog</t>
-  </si>
-  <si>
-    <t>6/16/2026, 7:31:06 AM</t>
   </si>
   <si>
     <t>Enter budget cap limit: 1000</t>
@@ -788,6 +788,9 @@
   </si>
   <si>
     <t>Navigate to tab: nav-reports</t>
+  </si>
+  <si>
+    <t>6/16/2026, 7:34:50 AM</t>
   </si>
   <si>
     <t>Read category distribution list</t>
@@ -1492,21 +1495,21 @@
         <v>28</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>27</v>
@@ -1515,21 +1518,21 @@
         <v>28</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>27</v>
@@ -1538,18 +1541,18 @@
         <v>28</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>36</v>
@@ -1561,21 +1564,21 @@
         <v>28</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1584,21 +1587,21 @@
         <v>28</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>27</v>
@@ -1607,7 +1610,7 @@
         <v>28</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1722,21 +1725,21 @@
         <v>28</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>27</v>
@@ -1745,21 +1748,21 @@
         <v>28</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>27</v>
@@ -1768,21 +1771,21 @@
         <v>28</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>27</v>
@@ -1791,7 +1794,7 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>90</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1906,7 +1909,7 @@
         <v>28</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1952,21 +1955,21 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -1975,7 +1978,7 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1998,21 +2001,21 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
@@ -2021,7 +2024,7 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>127</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2067,21 +2070,21 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>27</v>
@@ -2090,7 +2093,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -2318,41 +2321,41 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>151</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>151</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>151</v>
@@ -2364,12 +2367,12 @@
         <v>28</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>151</v>
@@ -2386,7 +2389,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>151</v>
@@ -2403,7 +2406,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>151</v>
@@ -2420,7 +2423,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
@@ -2437,41 +2440,41 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>151</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>151</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>151</v>
@@ -2488,7 +2491,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>151</v>
@@ -2505,7 +2508,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>151</v>
@@ -2522,7 +2525,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>151</v>
@@ -2534,12 +2537,12 @@
         <v>28</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>24</v>
@@ -2556,41 +2559,41 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>151</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>151</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>151</v>
@@ -2607,7 +2610,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>151</v>
@@ -2624,7 +2627,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>151</v>
@@ -2641,7 +2644,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>151</v>
@@ -2658,7 +2661,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
@@ -2675,41 +2678,41 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>151</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>151</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>151</v>
@@ -2721,12 +2724,12 @@
         <v>28</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>151</v>
@@ -2738,12 +2741,12 @@
         <v>28</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>151</v>
@@ -2760,13 +2763,13 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>28</v>
@@ -2777,13 +2780,13 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>28</v>
@@ -2794,7 +2797,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>148</v>
@@ -2811,7 +2814,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>148</v>
@@ -2828,7 +2831,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>148</v>
@@ -2845,7 +2848,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>148</v>
@@ -2862,13 +2865,13 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>28</v>
@@ -2879,24 +2882,24 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>148</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>148</v>
@@ -2908,12 +2911,12 @@
         <v>28</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>148</v>
@@ -2930,7 +2933,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>148</v>
@@ -2942,18 +2945,18 @@
         <v>28</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>28</v>
@@ -2964,24 +2967,24 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>148</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>148</v>
@@ -2998,7 +3001,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>148</v>
@@ -3015,7 +3018,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>148</v>
@@ -3027,18 +3030,18 @@
         <v>28</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>28</v>
@@ -3049,24 +3052,24 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>148</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>148</v>
@@ -3083,7 +3086,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>148</v>
@@ -3100,13 +3103,13 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>28</v>
@@ -3117,13 +3120,13 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>28</v>
@@ -3134,24 +3137,24 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>148</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>148</v>
@@ -3168,13 +3171,13 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>148</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>28</v>
@@ -3185,7 +3188,7 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>148</v>
@@ -3202,7 +3205,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>24</v>
@@ -3219,24 +3222,24 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>24</v>
@@ -3253,58 +3256,58 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>24</v>
@@ -3321,30 +3324,30 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>28</v>
@@ -3355,7 +3358,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>24</v>
@@ -3372,27 +3375,27 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>203</v>
@@ -3406,10 +3409,10 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>204</v>
@@ -3423,10 +3426,10 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>206</v>
@@ -3440,30 +3443,30 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>28</v>
@@ -3474,24 +3477,24 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>24</v>
@@ -3508,10 +3511,10 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>203</v>
@@ -3525,13 +3528,13 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>28</v>
@@ -3542,13 +3545,13 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>28</v>
@@ -3559,13 +3562,13 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>28</v>
@@ -3576,30 +3579,30 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>28</v>
@@ -3610,30 +3613,30 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>28</v>
@@ -3644,30 +3647,30 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D89" s="6" t="s">
         <v>28</v>
@@ -3678,10 +3681,10 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>218</v>
@@ -3695,10 +3698,10 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>220</v>
@@ -3712,10 +3715,10 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>222</v>
@@ -3729,13 +3732,13 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>28</v>
@@ -3746,30 +3749,30 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D95" s="6" t="s">
         <v>28</v>
@@ -3780,13 +3783,13 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>216</v>
       </c>
       <c r="D96" s="6" t="s">
         <v>28</v>
@@ -3797,7 +3800,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>24</v>
@@ -3814,13 +3817,13 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>28</v>
@@ -3831,30 +3834,30 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>28</v>
@@ -3865,24 +3868,24 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D101" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>24</v>
@@ -3899,13 +3902,13 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D103" s="6" t="s">
         <v>28</v>
@@ -3916,13 +3919,13 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D104" s="6" t="s">
         <v>28</v>
@@ -3933,27 +3936,27 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D105" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>233</v>
@@ -3967,10 +3970,10 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>234</v>
@@ -3984,7 +3987,7 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>24</v>
@@ -4001,13 +4004,13 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>28</v>
@@ -4018,10 +4021,10 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>236</v>
@@ -4035,10 +4038,10 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>238</v>
@@ -4052,10 +4055,10 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>233</v>
@@ -4069,13 +4072,13 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D113" s="6" t="s">
         <v>28</v>
@@ -4086,13 +4089,13 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>28</v>
@@ -4103,47 +4106,47 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>28</v>
@@ -4154,13 +4157,13 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>28</v>
@@ -4171,7 +4174,7 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>24</v>
@@ -4188,13 +4191,13 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>28</v>
@@ -4205,13 +4208,13 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D121" s="6" t="s">
         <v>28</v>
@@ -4222,10 +4225,10 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>247</v>
@@ -4239,10 +4242,10 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>233</v>
@@ -4256,10 +4259,10 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>249</v>
@@ -4273,7 +4276,7 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>24</v>
@@ -4290,10 +4293,10 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>251</v>
@@ -4307,7 +4310,7 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>24</v>
@@ -4324,10 +4327,10 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C128" s="3" t="s">
         <v>251</v>
@@ -4341,24 +4344,24 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D129" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>24</v>
@@ -4375,13 +4378,13 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D131" s="6" t="s">
         <v>28</v>
@@ -4392,13 +4395,13 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>28</v>
@@ -4409,13 +4412,13 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D133" s="6" t="s">
         <v>28</v>
@@ -4426,47 +4429,47 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D135" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
-        <v>3</v>
+        <v>252</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>28</v>
@@ -4477,24 +4480,24 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
-        <v>3</v>
+        <v>252</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D137" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
-        <v>3</v>
+        <v>252</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>24</v>
@@ -4511,13 +4514,13 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
-        <v>3</v>
+        <v>252</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D139" s="6" t="s">
         <v>28</v>
@@ -4528,47 +4531,47 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
-        <v>3</v>
+        <v>252</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
-        <v>3</v>
+        <v>252</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D141" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
-        <v>3</v>
+        <v>252</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D142" s="6" t="s">
         <v>28</v>
@@ -4582,10 +4585,10 @@
         <v>3</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D143" s="6" t="s">
         <v>28</v>
@@ -4599,16 +4602,16 @@
         <v>3</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D144" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -4619,7 +4622,7 @@
         <v>24</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D145" s="6" t="s">
         <v>28</v>
@@ -4633,10 +4636,10 @@
         <v>3</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D146" s="6" t="s">
         <v>28</v>
@@ -4667,10 +4670,10 @@
         <v>3</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D148" s="6" t="s">
         <v>28</v>
@@ -4704,7 +4707,7 @@
         <v>24</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D150" s="6" t="s">
         <v>28</v>

--- a/reports/Selenium_Report.xlsx
+++ b/reports/Selenium_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="267">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/16/2026, 7:31:07 AM</t>
+    <t>6/18/2026, 4:42:35 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>10.54s</t>
+    <t>9.91s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,7 +103,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>0.73s</t>
+    <t>0.51s</t>
   </si>
   <si>
     <t>TC-SEL-02</t>
@@ -115,7 +115,7 @@
     <t>Error message: "Passwords do not match." displays on password verification mismatch</t>
   </si>
   <si>
-    <t>0.66s</t>
+    <t>0.56s</t>
   </si>
   <si>
     <t>TC-SEL-03</t>
@@ -127,7 +127,7 @@
     <t>Error message: "Password must be at least 8 characters." displays</t>
   </si>
   <si>
-    <t>0.52s</t>
+    <t>0.49s</t>
   </si>
   <si>
     <t>TC-SEL-04</t>
@@ -139,7 +139,7 @@
     <t>Error message: "Email address already registered." displays</t>
   </si>
   <si>
-    <t>0.59s</t>
+    <t>0.54s</t>
   </si>
   <si>
     <t>TC-SEL-05</t>
@@ -151,7 +151,7 @@
     <t>Registration succeeds, stores user session, and auto-routes to dashboard layout</t>
   </si>
   <si>
-    <t>0.75s</t>
+    <t>0.65s</t>
   </si>
   <si>
     <t>TC-SEL-06</t>
@@ -163,7 +163,7 @@
     <t>Form prevents submission or displays missing fields prompt</t>
   </si>
   <si>
-    <t>0.21s</t>
+    <t>0.20s</t>
   </si>
   <si>
     <t>TC-SEL-07</t>
@@ -172,7 +172,7 @@
     <t>Validate login password length boundaries</t>
   </si>
   <si>
-    <t>0.34s</t>
+    <t>0.31s</t>
   </si>
   <si>
     <t>TC-SEL-08</t>
@@ -184,7 +184,7 @@
     <t>Error message: "Invalid email or password credential." displays</t>
   </si>
   <si>
-    <t>0.31s</t>
+    <t>0.28s</t>
   </si>
   <si>
     <t>TC-SEL-09</t>
@@ -196,6 +196,9 @@
     <t>Login succeeds and redirects to dashboard with active sidebar</t>
   </si>
   <si>
+    <t>0.30s</t>
+  </si>
+  <si>
     <t>TC-SEL-10</t>
   </si>
   <si>
@@ -205,7 +208,7 @@
     <t>Session remains cached in localStorage when remember check is checked</t>
   </si>
   <si>
-    <t>0.46s</t>
+    <t>0.43s</t>
   </si>
   <si>
     <t>TC-SEL-11</t>
@@ -217,222 +220,222 @@
     <t>Total Balance, Total Income, and Total Expenses load correctly</t>
   </si>
   <si>
+    <t>0.32s</t>
+  </si>
+  <si>
+    <t>TC-SEL-12</t>
+  </si>
+  <si>
+    <t>Verify dashboard net balance math matches initial static transactions</t>
+  </si>
+  <si>
+    <t>Balance equals total income minus total expenses</t>
+  </si>
+  <si>
+    <t>0.07s</t>
+  </si>
+  <si>
+    <t>TC-SEL-13</t>
+  </si>
+  <si>
+    <t>Verify dashboard search bar resolves real-time query list matches</t>
+  </si>
+  <si>
+    <t>Typing transaction names filters matching rows dynamically</t>
+  </si>
+  <si>
+    <t>0.15s</t>
+  </si>
+  <si>
+    <t>TC-SEL-14</t>
+  </si>
+  <si>
+    <t>Verify add income inflow category transaction form submission flow</t>
+  </si>
+  <si>
+    <t>Inflow transaction added and net balance increases accordingly</t>
+  </si>
+  <si>
+    <t>0.58s</t>
+  </si>
+  <si>
+    <t>TC-SEL-15</t>
+  </si>
+  <si>
+    <t>Validate income forms empty constraints boundaries</t>
+  </si>
+  <si>
+    <t>Missing required inputs prevent transaction submission</t>
+  </si>
+  <si>
+    <t>TC-SEL-16</t>
+  </si>
+  <si>
+    <t>Verify delete income transaction adjusts total calculations</t>
+  </si>
+  <si>
+    <t>Removing an income transaction successfully reduces total balance</t>
+  </si>
+  <si>
+    <t>0.22s</t>
+  </si>
+  <si>
+    <t>TC-SEL-17</t>
+  </si>
+  <si>
+    <t>Verify add expense outflow category transaction successfully updates calculations</t>
+  </si>
+  <si>
+    <t>Outflow transaction decreases net balance</t>
+  </si>
+  <si>
+    <t>0.55s</t>
+  </si>
+  <si>
+    <t>TC-SEL-18</t>
+  </si>
+  <si>
+    <t>Validate numeric constraints on amount inputs preventing non-numerical submission</t>
+  </si>
+  <si>
+    <t>Negative or text values in amount are rejected</t>
+  </si>
+  <si>
+    <t>TC-SEL-19</t>
+  </si>
+  <si>
+    <t>Verify delete expense transaction adjustments</t>
+  </si>
+  <si>
+    <t>Deleting an expense successfully restores balance amount</t>
+  </si>
+  <si>
     <t>0.18s</t>
   </si>
   <si>
-    <t>TC-SEL-12</t>
-  </si>
-  <si>
-    <t>Verify dashboard net balance math matches initial static transactions</t>
-  </si>
-  <si>
-    <t>Balance equals total income minus total expenses</t>
-  </si>
-  <si>
-    <t>0.06s</t>
-  </si>
-  <si>
-    <t>TC-SEL-13</t>
-  </si>
-  <si>
-    <t>Verify dashboard search bar resolves real-time query list matches</t>
-  </si>
-  <si>
-    <t>Typing transaction names filters matching rows dynamically</t>
-  </si>
-  <si>
-    <t>0.16s</t>
-  </si>
-  <si>
-    <t>TC-SEL-14</t>
-  </si>
-  <si>
-    <t>Verify add income inflow category transaction form submission flow</t>
-  </si>
-  <si>
-    <t>Inflow transaction added and net balance increases accordingly</t>
-  </si>
-  <si>
-    <t>TC-SEL-15</t>
-  </si>
-  <si>
-    <t>Validate income forms empty constraints boundaries</t>
-  </si>
-  <si>
-    <t>Missing required inputs prevent transaction submission</t>
-  </si>
-  <si>
-    <t>0.14s</t>
-  </si>
-  <si>
-    <t>TC-SEL-16</t>
-  </si>
-  <si>
-    <t>Verify delete income transaction adjusts total calculations</t>
-  </si>
-  <si>
-    <t>Removing an income transaction successfully reduces total balance</t>
-  </si>
-  <si>
-    <t>0.24s</t>
-  </si>
-  <si>
-    <t>TC-SEL-17</t>
-  </si>
-  <si>
-    <t>Verify add expense outflow category transaction successfully updates calculations</t>
-  </si>
-  <si>
-    <t>Outflow transaction decreases net balance</t>
-  </si>
-  <si>
-    <t>0.56s</t>
-  </si>
-  <si>
-    <t>TC-SEL-18</t>
-  </si>
-  <si>
-    <t>Validate numeric constraints on amount inputs preventing non-numerical submission</t>
-  </si>
-  <si>
-    <t>Negative or text values in amount are rejected</t>
+    <t>TC-SEL-20</t>
+  </si>
+  <si>
+    <t>Verify category budget cap limit configuration successfully saves limiters</t>
+  </si>
+  <si>
+    <t>Category caps limits are saved and progress bars render</t>
+  </si>
+  <si>
+    <t>0.42s</t>
+  </si>
+  <si>
+    <t>TC-SEL-21</t>
+  </si>
+  <si>
+    <t>Verify category budget warning alert triggers when expense exceeds limit cap</t>
+  </si>
+  <si>
+    <t>Budget Cap overflow modal popup loads when transaction exceeds cap</t>
+  </si>
+  <si>
+    <t>0.83s</t>
+  </si>
+  <si>
+    <t>TC-SEL-22</t>
+  </si>
+  <si>
+    <t>Verify edit category budget limit increases active threshold</t>
+  </si>
+  <si>
+    <t>Updating limit increases budget cap and progress decreases</t>
+  </si>
+  <si>
+    <t>TC-SEL-23</t>
+  </si>
+  <si>
+    <t>Verify reports dashboard trend chart elements rendering</t>
+  </si>
+  <si>
+    <t>Monthly Balance Trend line container is visible on page</t>
+  </si>
+  <si>
+    <t>0.11s</t>
+  </si>
+  <si>
+    <t>TC-SEL-24</t>
+  </si>
+  <si>
+    <t>Verify category distribution breakdown list aggregates metrics</t>
+  </si>
+  <si>
+    <t>Analytics categories breakdown table loads and sums values</t>
+  </si>
+  <si>
+    <t>0.10s</t>
+  </si>
+  <si>
+    <t>TC-SEL-25</t>
+  </si>
+  <si>
+    <t>Verify raw data export reports CSV simulation download trigger</t>
+  </si>
+  <si>
+    <t>Clicking export initializes simulated raw CSV download</t>
+  </si>
+  <si>
+    <t>TC-SEL-26</t>
+  </si>
+  <si>
+    <t>Verify user profile metadata fields update successfully</t>
+  </si>
+  <si>
+    <t>Display name successfully updates and synchronizes with sidebar user block</t>
+  </si>
+  <si>
+    <t>0.44s</t>
+  </si>
+  <si>
+    <t>TC-SEL-27</t>
+  </si>
+  <si>
+    <t>Verify preferred default currency synchronization on profile updates</t>
+  </si>
+  <si>
+    <t>Changing currency symbol on profile alters dashboard symbols</t>
+  </si>
+  <si>
+    <t>TC-SEL-28</t>
+  </si>
+  <si>
+    <t>Verify profile assigned application role is readonly configuration</t>
+  </si>
+  <si>
+    <t>Application role text box contains "readonly" property attribute</t>
+  </si>
+  <si>
+    <t>0.13s</t>
+  </si>
+  <si>
+    <t>TC-SEL-29</t>
+  </si>
+  <si>
+    <t>Verify successful user logout redirects to authentication login view</t>
+  </si>
+  <si>
+    <t>Session clears and client redirects to login view immediately</t>
   </si>
   <si>
     <t>0.09s</t>
   </si>
   <si>
-    <t>TC-SEL-19</t>
-  </si>
-  <si>
-    <t>Verify delete expense transaction adjustments</t>
-  </si>
-  <si>
-    <t>Deleting an expense successfully restores balance amount</t>
-  </si>
-  <si>
-    <t>0.20s</t>
-  </si>
-  <si>
-    <t>TC-SEL-20</t>
-  </si>
-  <si>
-    <t>Verify category budget cap limit configuration successfully saves limiters</t>
-  </si>
-  <si>
-    <t>Category caps limits are saved and progress bars render</t>
+    <t>TC-SEL-30</t>
+  </si>
+  <si>
+    <t>Verify inactive session security timeout auto-redirect functionality</t>
+  </si>
+  <si>
+    <t>Inactivity trigger automatically destroys token and redirects to login view</t>
   </si>
   <si>
     <t>0.41s</t>
   </si>
   <si>
-    <t>TC-SEL-21</t>
-  </si>
-  <si>
-    <t>Verify category budget warning alert triggers when expense exceeds limit cap</t>
-  </si>
-  <si>
-    <t>Budget Cap overflow modal popup loads when transaction exceeds cap</t>
-  </si>
-  <si>
-    <t>0.87s</t>
-  </si>
-  <si>
-    <t>TC-SEL-22</t>
-  </si>
-  <si>
-    <t>Verify edit category budget limit increases active threshold</t>
-  </si>
-  <si>
-    <t>Updating limit increases budget cap and progress decreases</t>
-  </si>
-  <si>
-    <t>TC-SEL-23</t>
-  </si>
-  <si>
-    <t>Verify reports dashboard trend chart elements rendering</t>
-  </si>
-  <si>
-    <t>Monthly Balance Trend line container is visible on page</t>
-  </si>
-  <si>
-    <t>0.12s</t>
-  </si>
-  <si>
-    <t>TC-SEL-24</t>
-  </si>
-  <si>
-    <t>Verify category distribution breakdown list aggregates metrics</t>
-  </si>
-  <si>
-    <t>Analytics categories breakdown table loads and sums values</t>
-  </si>
-  <si>
-    <t>TC-SEL-25</t>
-  </si>
-  <si>
-    <t>Verify raw data export reports CSV simulation download trigger</t>
-  </si>
-  <si>
-    <t>Clicking export initializes simulated raw CSV download</t>
-  </si>
-  <si>
-    <t>0.11s</t>
-  </si>
-  <si>
-    <t>TC-SEL-26</t>
-  </si>
-  <si>
-    <t>Verify user profile metadata fields update successfully</t>
-  </si>
-  <si>
-    <t>Display name successfully updates and synchronizes with sidebar user block</t>
-  </si>
-  <si>
-    <t>TC-SEL-27</t>
-  </si>
-  <si>
-    <t>Verify preferred default currency synchronization on profile updates</t>
-  </si>
-  <si>
-    <t>Changing currency symbol on profile alters dashboard symbols</t>
-  </si>
-  <si>
-    <t>0.42s</t>
-  </si>
-  <si>
-    <t>TC-SEL-28</t>
-  </si>
-  <si>
-    <t>Verify profile assigned application role is readonly configuration</t>
-  </si>
-  <si>
-    <t>Application role text box contains "readonly" property attribute</t>
-  </si>
-  <si>
-    <t>0.13s</t>
-  </si>
-  <si>
-    <t>TC-SEL-29</t>
-  </si>
-  <si>
-    <t>Verify successful user logout redirects to authentication login view</t>
-  </si>
-  <si>
-    <t>Session clears and client redirects to login view immediately</t>
-  </si>
-  <si>
-    <t>TC-SEL-30</t>
-  </si>
-  <si>
-    <t>Verify inactive session security timeout auto-redirect functionality</t>
-  </si>
-  <si>
-    <t>Inactivity trigger automatically destroys token and redirects to login view</t>
-  </si>
-  <si>
-    <t>0.39s</t>
-  </si>
-  <si>
     <t>Failure Message</t>
   </si>
   <si>
@@ -457,7 +460,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>6/16/2026, 7:30:58 AM</t>
+    <t>6/18/2026, 4:42:26 AM</t>
   </si>
   <si>
     <t>LoginPage</t>
@@ -508,12 +511,12 @@
     <t>Entered: sarah@budget.com</t>
   </si>
   <si>
+    <t>6/18/2026, 4:42:27 AM</t>
+  </si>
+  <si>
     <t>Entered: SecurePass123!</t>
   </si>
   <si>
-    <t>6/16/2026, 7:30:59 AM</t>
-  </si>
-  <si>
     <t>Entered: WrongPass123!</t>
   </si>
   <si>
@@ -532,15 +535,15 @@
     <t>Entered: Admin User</t>
   </si>
   <si>
+    <t>6/18/2026, 4:42:28 AM</t>
+  </si>
+  <si>
     <t>Enter register email: admin@budget.com</t>
   </si>
   <si>
     <t>Entered: admin@budget.com</t>
   </si>
   <si>
-    <t>6/16/2026, 7:31:00 AM</t>
-  </si>
-  <si>
     <t>Entered: SmartBudgetPass123!</t>
   </si>
   <si>
@@ -556,7 +559,7 @@
     <t>Click Logout Button</t>
   </si>
   <si>
-    <t>6/16/2026, 7:31:01 AM</t>
+    <t>6/18/2026, 4:42:29 AM</t>
   </si>
   <si>
     <t xml:space="preserve">Enter login email: </t>
@@ -589,7 +592,7 @@
     <t>Text found: "Invalid email or password credential."</t>
   </si>
   <si>
-    <t>6/16/2026, 7:31:02 AM</t>
+    <t>6/18/2026, 4:42:30 AM</t>
   </si>
   <si>
     <t>Check Remember Me option</t>
@@ -622,9 +625,6 @@
     <t>Clear query</t>
   </si>
   <si>
-    <t>6/16/2026, 7:31:03 AM</t>
-  </si>
-  <si>
     <t>Navigate to tab: nav-income</t>
   </si>
   <si>
@@ -634,6 +634,9 @@
     <t>Entered: Salary</t>
   </si>
   <si>
+    <t>6/18/2026, 4:42:31 AM</t>
+  </si>
+  <si>
     <t>Enter income amount: 2500</t>
   </si>
   <si>
@@ -667,9 +670,6 @@
     <t>Navigate to tab: nav-expense</t>
   </si>
   <si>
-    <t>6/16/2026, 7:31:04 AM</t>
-  </si>
-  <si>
     <t>Select expense category: Food</t>
   </si>
   <si>
@@ -682,6 +682,9 @@
     <t>Entered: 120</t>
   </si>
   <si>
+    <t>6/18/2026, 4:42:32 AM</t>
+  </si>
+  <si>
     <t>Enter expense description: Weekly grocery run</t>
   </si>
   <si>
@@ -710,9 +713,6 @@
   </si>
   <si>
     <t>Entered: 600</t>
-  </si>
-  <si>
-    <t>6/16/2026, 7:31:05 AM</t>
   </si>
   <si>
     <t>Click Save Budget Allocation button</t>
@@ -733,6 +733,9 @@
 $0.00 / $1500.00 (0%)"</t>
   </si>
   <si>
+    <t>6/18/2026, 4:42:33 AM</t>
+  </si>
+  <si>
     <t>Select budget segment: Shopping</t>
   </si>
   <si>
@@ -763,13 +766,13 @@
     <t>Acknowledge budget cap warning dialog</t>
   </si>
   <si>
-    <t>6/16/2026, 7:31:06 AM</t>
-  </si>
-  <si>
     <t>Enter budget cap limit: 1000</t>
   </si>
   <si>
     <t>Entered: 1000</t>
+  </si>
+  <si>
+    <t>6/18/2026, 4:42:34 AM</t>
   </si>
   <si>
     <t>Check updated Food cap</t>
@@ -1607,21 +1610,21 @@
         <v>28</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
@@ -1630,21 +1633,21 @@
         <v>28</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>27</v>
@@ -1653,21 +1656,21 @@
         <v>28</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>27</v>
@@ -1676,21 +1679,21 @@
         <v>28</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
@@ -1699,21 +1702,21 @@
         <v>28</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>27</v>
@@ -1722,21 +1725,21 @@
         <v>28</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>27</v>
@@ -1745,21 +1748,21 @@
         <v>28</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>27</v>
@@ -1768,21 +1771,21 @@
         <v>28</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>27</v>
@@ -1791,21 +1794,21 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -1814,7 +1817,7 @@
         <v>28</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1906,7 +1909,7 @@
         <v>28</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1952,21 +1955,21 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -1975,7 +1978,7 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1998,21 +2001,21 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
@@ -2021,7 +2024,7 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2067,21 +2070,21 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>27</v>
@@ -2090,7 +2093,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2122,10 +2125,10 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2136,10 +2139,10 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>7</v>
@@ -2165,143 +2168,143 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>24</v>
@@ -2318,53 +2321,53 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2372,16 +2375,16 @@
         <v>165</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2389,16 +2392,16 @@
         <v>165</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2406,16 +2409,16 @@
         <v>165</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2440,16 +2443,16 @@
         <v>165</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -2457,16 +2460,16 @@
         <v>165</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -2474,16 +2477,16 @@
         <v>165</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2491,16 +2494,16 @@
         <v>165</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -2508,16 +2511,16 @@
         <v>165</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -2525,16 +2528,16 @@
         <v>165</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -2559,106 +2562,106 @@
         <v>165</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
@@ -2675,109 +2678,109 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>24</v>
@@ -2794,75 +2797,75 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>24</v>
@@ -2879,75 +2882,75 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>24</v>
@@ -2964,75 +2967,75 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>24</v>
@@ -3049,58 +3052,58 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>24</v>
@@ -3117,98 +3120,98 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>28</v>
@@ -3219,30 +3222,30 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>28</v>
@@ -3253,64 +3256,64 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>28</v>
@@ -3321,47 +3324,47 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>28</v>
@@ -3372,27 +3375,27 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>203</v>
@@ -3401,15 +3404,15 @@
         <v>28</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>204</v>
@@ -3423,81 +3426,81 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>28</v>
@@ -3508,10 +3511,10 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>203</v>
@@ -3520,35 +3523,35 @@
         <v>28</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>28</v>
@@ -3559,81 +3562,81 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>28</v>
@@ -3644,44 +3647,44 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D89" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>218</v>
@@ -3695,10 +3698,10 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>220</v>
@@ -3712,64 +3715,64 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D95" s="6" t="s">
         <v>28</v>
@@ -3780,30 +3783,30 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="B96" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>216</v>
-      </c>
       <c r="D96" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D97" s="6" t="s">
         <v>28</v>
@@ -3814,75 +3817,75 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D101" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>24</v>
@@ -3899,30 +3902,30 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D103" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D104" s="6" t="s">
         <v>28</v>
@@ -3933,27 +3936,27 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D105" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>233</v>
@@ -3962,15 +3965,15 @@
         <v>28</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>234</v>
@@ -3984,7 +3987,7 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>24</v>
@@ -4001,61 +4004,61 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>233</v>
@@ -4064,114 +4067,114 @@
         <v>28</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D113" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>24</v>
@@ -4188,30 +4191,30 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D121" s="6" t="s">
         <v>28</v>
@@ -4222,10 +4225,10 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>247</v>
@@ -4239,10 +4242,10 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>233</v>
@@ -4251,29 +4254,29 @@
         <v>28</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>24</v>
@@ -4290,24 +4293,24 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>24</v>
@@ -4324,41 +4327,41 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D128" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D129" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>24</v>
@@ -4375,30 +4378,30 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D131" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>28</v>
@@ -4409,92 +4412,92 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D133" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D135" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D137" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>24</v>
@@ -4511,36 +4514,36 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D139" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
@@ -4548,16 +4551,16 @@
         <v>3</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D141" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -4565,16 +4568,16 @@
         <v>3</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D142" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
@@ -4582,16 +4585,16 @@
         <v>3</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D143" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -4599,16 +4602,16 @@
         <v>3</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D144" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -4619,7 +4622,7 @@
         <v>24</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D145" s="6" t="s">
         <v>28</v>
@@ -4633,16 +4636,16 @@
         <v>3</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D146" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
@@ -4667,16 +4670,16 @@
         <v>3</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D148" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -4704,7 +4707,7 @@
         <v>24</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D150" s="6" t="s">
         <v>28</v>

--- a/reports/Selenium_Report.xlsx
+++ b/reports/Selenium_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="268">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/18/2026, 4:42:35 AM</t>
+    <t>6/18/2026, 5:58:23 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>9.91s</t>
+    <t>10.04s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,7 +103,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>0.51s</t>
+    <t>0.48s</t>
   </si>
   <si>
     <t>TC-SEL-02</t>
@@ -115,7 +115,7 @@
     <t>Error message: "Passwords do not match." displays on password verification mismatch</t>
   </si>
   <si>
-    <t>0.56s</t>
+    <t>0.71s</t>
   </si>
   <si>
     <t>TC-SEL-03</t>
@@ -127,7 +127,7 @@
     <t>Error message: "Password must be at least 8 characters." displays</t>
   </si>
   <si>
-    <t>0.49s</t>
+    <t>0.59s</t>
   </si>
   <si>
     <t>TC-SEL-04</t>
@@ -139,7 +139,7 @@
     <t>Error message: "Email address already registered." displays</t>
   </si>
   <si>
-    <t>0.54s</t>
+    <t>0.53s</t>
   </si>
   <si>
     <t>TC-SEL-05</t>
@@ -151,7 +151,7 @@
     <t>Registration succeeds, stores user session, and auto-routes to dashboard layout</t>
   </si>
   <si>
-    <t>0.65s</t>
+    <t>0.67s</t>
   </si>
   <si>
     <t>TC-SEL-06</t>
@@ -172,180 +172,183 @@
     <t>Validate login password length boundaries</t>
   </si>
   <si>
+    <t>0.29s</t>
+  </si>
+  <si>
+    <t>TC-SEL-08</t>
+  </si>
+  <si>
+    <t>Validate wrong password credential error boundary</t>
+  </si>
+  <si>
+    <t>Error message: "Invalid email or password credential." displays</t>
+  </si>
+  <si>
+    <t>0.30s</t>
+  </si>
+  <si>
+    <t>TC-SEL-09</t>
+  </si>
+  <si>
+    <t>Verify successful authentication for Admin Manager role</t>
+  </si>
+  <si>
+    <t>Login succeeds and redirects to dashboard with active sidebar</t>
+  </si>
+  <si>
+    <t>TC-SEL-10</t>
+  </si>
+  <si>
+    <t>Verify Remember Me session storage persistence behavior</t>
+  </si>
+  <si>
+    <t>Session remains cached in localStorage when remember check is checked</t>
+  </si>
+  <si>
+    <t>0.43s</t>
+  </si>
+  <si>
+    <t>TC-SEL-11</t>
+  </si>
+  <si>
+    <t>Verify dashboard panels load initial default budgeting summary cards</t>
+  </si>
+  <si>
+    <t>Total Balance, Total Income, and Total Expenses load correctly</t>
+  </si>
+  <si>
+    <t>0.27s</t>
+  </si>
+  <si>
+    <t>TC-SEL-12</t>
+  </si>
+  <si>
+    <t>Verify dashboard net balance math matches initial static transactions</t>
+  </si>
+  <si>
+    <t>Balance equals total income minus total expenses</t>
+  </si>
+  <si>
+    <t>0.06s</t>
+  </si>
+  <si>
+    <t>TC-SEL-13</t>
+  </si>
+  <si>
+    <t>Verify dashboard search bar resolves real-time query list matches</t>
+  </si>
+  <si>
+    <t>Typing transaction names filters matching rows dynamically</t>
+  </si>
+  <si>
+    <t>0.16s</t>
+  </si>
+  <si>
+    <t>TC-SEL-14</t>
+  </si>
+  <si>
+    <t>Verify add income inflow category transaction form submission flow</t>
+  </si>
+  <si>
+    <t>Inflow transaction added and net balance increases accordingly</t>
+  </si>
+  <si>
+    <t>0.57s</t>
+  </si>
+  <si>
+    <t>TC-SEL-15</t>
+  </si>
+  <si>
+    <t>Validate income forms empty constraints boundaries</t>
+  </si>
+  <si>
+    <t>Missing required inputs prevent transaction submission</t>
+  </si>
+  <si>
+    <t>0.14s</t>
+  </si>
+  <si>
+    <t>TC-SEL-16</t>
+  </si>
+  <si>
+    <t>Verify delete income transaction adjusts total calculations</t>
+  </si>
+  <si>
+    <t>Removing an income transaction successfully reduces total balance</t>
+  </si>
+  <si>
+    <t>0.23s</t>
+  </si>
+  <si>
+    <t>TC-SEL-17</t>
+  </si>
+  <si>
+    <t>Verify add expense outflow category transaction successfully updates calculations</t>
+  </si>
+  <si>
+    <t>Outflow transaction decreases net balance</t>
+  </si>
+  <si>
+    <t>TC-SEL-18</t>
+  </si>
+  <si>
+    <t>Validate numeric constraints on amount inputs preventing non-numerical submission</t>
+  </si>
+  <si>
+    <t>Negative or text values in amount are rejected</t>
+  </si>
+  <si>
+    <t>0.08s</t>
+  </si>
+  <si>
+    <t>TC-SEL-19</t>
+  </si>
+  <si>
+    <t>Verify delete expense transaction adjustments</t>
+  </si>
+  <si>
+    <t>Deleting an expense successfully restores balance amount</t>
+  </si>
+  <si>
+    <t>0.21s</t>
+  </si>
+  <si>
+    <t>TC-SEL-20</t>
+  </si>
+  <si>
+    <t>Verify category budget cap limit configuration successfully saves limiters</t>
+  </si>
+  <si>
+    <t>Category caps limits are saved and progress bars render</t>
+  </si>
+  <si>
+    <t>0.39s</t>
+  </si>
+  <si>
+    <t>TC-SEL-21</t>
+  </si>
+  <si>
+    <t>Verify category budget warning alert triggers when expense exceeds limit cap</t>
+  </si>
+  <si>
+    <t>Budget Cap overflow modal popup loads when transaction exceeds cap</t>
+  </si>
+  <si>
+    <t>0.81s</t>
+  </si>
+  <si>
+    <t>TC-SEL-22</t>
+  </si>
+  <si>
+    <t>Verify edit category budget limit increases active threshold</t>
+  </si>
+  <si>
+    <t>Updating limit increases budget cap and progress decreases</t>
+  </si>
+  <si>
     <t>0.31s</t>
   </si>
   <si>
-    <t>TC-SEL-08</t>
-  </si>
-  <si>
-    <t>Validate wrong password credential error boundary</t>
-  </si>
-  <si>
-    <t>Error message: "Invalid email or password credential." displays</t>
-  </si>
-  <si>
-    <t>0.28s</t>
-  </si>
-  <si>
-    <t>TC-SEL-09</t>
-  </si>
-  <si>
-    <t>Verify successful authentication for Admin Manager role</t>
-  </si>
-  <si>
-    <t>Login succeeds and redirects to dashboard with active sidebar</t>
-  </si>
-  <si>
-    <t>0.30s</t>
-  </si>
-  <si>
-    <t>TC-SEL-10</t>
-  </si>
-  <si>
-    <t>Verify Remember Me session storage persistence behavior</t>
-  </si>
-  <si>
-    <t>Session remains cached in localStorage when remember check is checked</t>
-  </si>
-  <si>
-    <t>0.43s</t>
-  </si>
-  <si>
-    <t>TC-SEL-11</t>
-  </si>
-  <si>
-    <t>Verify dashboard panels load initial default budgeting summary cards</t>
-  </si>
-  <si>
-    <t>Total Balance, Total Income, and Total Expenses load correctly</t>
-  </si>
-  <si>
-    <t>0.32s</t>
-  </si>
-  <si>
-    <t>TC-SEL-12</t>
-  </si>
-  <si>
-    <t>Verify dashboard net balance math matches initial static transactions</t>
-  </si>
-  <si>
-    <t>Balance equals total income minus total expenses</t>
-  </si>
-  <si>
-    <t>0.07s</t>
-  </si>
-  <si>
-    <t>TC-SEL-13</t>
-  </si>
-  <si>
-    <t>Verify dashboard search bar resolves real-time query list matches</t>
-  </si>
-  <si>
-    <t>Typing transaction names filters matching rows dynamically</t>
-  </si>
-  <si>
-    <t>0.15s</t>
-  </si>
-  <si>
-    <t>TC-SEL-14</t>
-  </si>
-  <si>
-    <t>Verify add income inflow category transaction form submission flow</t>
-  </si>
-  <si>
-    <t>Inflow transaction added and net balance increases accordingly</t>
-  </si>
-  <si>
-    <t>0.58s</t>
-  </si>
-  <si>
-    <t>TC-SEL-15</t>
-  </si>
-  <si>
-    <t>Validate income forms empty constraints boundaries</t>
-  </si>
-  <si>
-    <t>Missing required inputs prevent transaction submission</t>
-  </si>
-  <si>
-    <t>TC-SEL-16</t>
-  </si>
-  <si>
-    <t>Verify delete income transaction adjusts total calculations</t>
-  </si>
-  <si>
-    <t>Removing an income transaction successfully reduces total balance</t>
-  </si>
-  <si>
-    <t>0.22s</t>
-  </si>
-  <si>
-    <t>TC-SEL-17</t>
-  </si>
-  <si>
-    <t>Verify add expense outflow category transaction successfully updates calculations</t>
-  </si>
-  <si>
-    <t>Outflow transaction decreases net balance</t>
-  </si>
-  <si>
-    <t>0.55s</t>
-  </si>
-  <si>
-    <t>TC-SEL-18</t>
-  </si>
-  <si>
-    <t>Validate numeric constraints on amount inputs preventing non-numerical submission</t>
-  </si>
-  <si>
-    <t>Negative or text values in amount are rejected</t>
-  </si>
-  <si>
-    <t>TC-SEL-19</t>
-  </si>
-  <si>
-    <t>Verify delete expense transaction adjustments</t>
-  </si>
-  <si>
-    <t>Deleting an expense successfully restores balance amount</t>
-  </si>
-  <si>
-    <t>0.18s</t>
-  </si>
-  <si>
-    <t>TC-SEL-20</t>
-  </si>
-  <si>
-    <t>Verify category budget cap limit configuration successfully saves limiters</t>
-  </si>
-  <si>
-    <t>Category caps limits are saved and progress bars render</t>
-  </si>
-  <si>
-    <t>0.42s</t>
-  </si>
-  <si>
-    <t>TC-SEL-21</t>
-  </si>
-  <si>
-    <t>Verify category budget warning alert triggers when expense exceeds limit cap</t>
-  </si>
-  <si>
-    <t>Budget Cap overflow modal popup loads when transaction exceeds cap</t>
-  </si>
-  <si>
-    <t>0.83s</t>
-  </si>
-  <si>
-    <t>TC-SEL-22</t>
-  </si>
-  <si>
-    <t>Verify edit category budget limit increases active threshold</t>
-  </si>
-  <si>
-    <t>Updating limit increases budget cap and progress decreases</t>
-  </si>
-  <si>
     <t>TC-SEL-23</t>
   </si>
   <si>
@@ -355,30 +358,33 @@
     <t>Monthly Balance Trend line container is visible on page</t>
   </si>
   <si>
+    <t>0.09s</t>
+  </si>
+  <si>
+    <t>TC-SEL-24</t>
+  </si>
+  <si>
+    <t>Verify category distribution breakdown list aggregates metrics</t>
+  </si>
+  <si>
+    <t>Analytics categories breakdown table loads and sums values</t>
+  </si>
+  <si>
     <t>0.11s</t>
   </si>
   <si>
-    <t>TC-SEL-24</t>
-  </si>
-  <si>
-    <t>Verify category distribution breakdown list aggregates metrics</t>
-  </si>
-  <si>
-    <t>Analytics categories breakdown table loads and sums values</t>
+    <t>TC-SEL-25</t>
+  </si>
+  <si>
+    <t>Verify raw data export reports CSV simulation download trigger</t>
+  </si>
+  <si>
+    <t>Clicking export initializes simulated raw CSV download</t>
   </si>
   <si>
     <t>0.10s</t>
   </si>
   <si>
-    <t>TC-SEL-25</t>
-  </si>
-  <si>
-    <t>Verify raw data export reports CSV simulation download trigger</t>
-  </si>
-  <si>
-    <t>Clicking export initializes simulated raw CSV download</t>
-  </si>
-  <si>
     <t>TC-SEL-26</t>
   </si>
   <si>
@@ -388,7 +394,7 @@
     <t>Display name successfully updates and synchronizes with sidebar user block</t>
   </si>
   <si>
-    <t>0.44s</t>
+    <t>0.41s</t>
   </si>
   <si>
     <t>TC-SEL-27</t>
@@ -400,6 +406,9 @@
     <t>Changing currency symbol on profile alters dashboard symbols</t>
   </si>
   <si>
+    <t>0.40s</t>
+  </si>
+  <si>
     <t>TC-SEL-28</t>
   </si>
   <si>
@@ -409,9 +418,6 @@
     <t>Application role text box contains "readonly" property attribute</t>
   </si>
   <si>
-    <t>0.13s</t>
-  </si>
-  <si>
     <t>TC-SEL-29</t>
   </si>
   <si>
@@ -421,9 +427,6 @@
     <t>Session clears and client redirects to login view immediately</t>
   </si>
   <si>
-    <t>0.09s</t>
-  </si>
-  <si>
     <t>TC-SEL-30</t>
   </si>
   <si>
@@ -433,7 +436,7 @@
     <t>Inactivity trigger automatically destroys token and redirects to login view</t>
   </si>
   <si>
-    <t>0.41s</t>
+    <t>0.47s</t>
   </si>
   <si>
     <t>Failure Message</t>
@@ -460,7 +463,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>6/18/2026, 4:42:26 AM</t>
+    <t>6/18/2026, 5:58:14 AM</t>
   </si>
   <si>
     <t>LoginPage</t>
@@ -499,6 +502,9 @@
     <t>Text found: "All fields are required for registration."</t>
   </si>
   <si>
+    <t>6/18/2026, 5:58:15 AM</t>
+  </si>
+  <si>
     <t>Enter register name: Sarah Connor</t>
   </si>
   <si>
@@ -511,9 +517,6 @@
     <t>Entered: sarah@budget.com</t>
   </si>
   <si>
-    <t>6/18/2026, 4:42:27 AM</t>
-  </si>
-  <si>
     <t>Entered: SecurePass123!</t>
   </si>
   <si>
@@ -523,6 +526,9 @@
     <t>Text found: "Passwords do not match."</t>
   </si>
   <si>
+    <t>6/18/2026, 5:58:16 AM</t>
+  </si>
+  <si>
     <t>Entered: 12345</t>
   </si>
   <si>
@@ -535,9 +541,6 @@
     <t>Entered: Admin User</t>
   </si>
   <si>
-    <t>6/18/2026, 4:42:28 AM</t>
-  </si>
-  <si>
     <t>Enter register email: admin@budget.com</t>
   </si>
   <si>
@@ -550,6 +553,9 @@
     <t>Text found: "Email address already registered."</t>
   </si>
   <si>
+    <t>6/18/2026, 5:58:17 AM</t>
+  </si>
+  <si>
     <t>Entered: SarahPass123!</t>
   </si>
   <si>
@@ -559,9 +565,6 @@
     <t>Click Logout Button</t>
   </si>
   <si>
-    <t>6/18/2026, 4:42:29 AM</t>
-  </si>
-  <si>
     <t xml:space="preserve">Enter login email: </t>
   </si>
   <si>
@@ -586,15 +589,15 @@
     <t>Entered: 123</t>
   </si>
   <si>
+    <t>6/18/2026, 5:58:18 AM</t>
+  </si>
+  <si>
     <t>Enter login email: admin@budget.com</t>
   </si>
   <si>
     <t>Text found: "Invalid email or password credential."</t>
   </si>
   <si>
-    <t>6/18/2026, 4:42:30 AM</t>
-  </si>
-  <si>
     <t>Check Remember Me option</t>
   </si>
   <si>
@@ -604,6 +607,9 @@
     <t>Text found: "$3,410.00"</t>
   </si>
   <si>
+    <t>6/18/2026, 5:58:19 AM</t>
+  </si>
+  <si>
     <t>Read total income statistic</t>
   </si>
   <si>
@@ -634,9 +640,6 @@
     <t>Entered: Salary</t>
   </si>
   <si>
-    <t>6/18/2026, 4:42:31 AM</t>
-  </si>
-  <si>
     <t>Enter income amount: 2500</t>
   </si>
   <si>
@@ -658,6 +661,9 @@
     <t>Click submit button on empty form</t>
   </si>
   <si>
+    <t>6/18/2026, 5:58:20 AM</t>
+  </si>
+  <si>
     <t>Navigate to tab: nav-dashboard</t>
   </si>
   <si>
@@ -682,9 +688,6 @@
     <t>Entered: 120</t>
   </si>
   <si>
-    <t>6/18/2026, 4:42:32 AM</t>
-  </si>
-  <si>
     <t>Enter expense description: Weekly grocery run</t>
   </si>
   <si>
@@ -701,6 +704,9 @@
   </si>
   <si>
     <t>Text found: "$1,990.00"</t>
+  </si>
+  <si>
+    <t>6/18/2026, 5:58:21 AM</t>
   </si>
   <si>
     <t>Navigate to tab: nav-budget</t>
@@ -733,9 +739,6 @@
 $0.00 / $1500.00 (0%)"</t>
   </si>
   <si>
-    <t>6/18/2026, 4:42:33 AM</t>
-  </si>
-  <si>
     <t>Select budget segment: Shopping</t>
   </si>
   <si>
@@ -757,6 +760,9 @@
     <t>Entered: 250</t>
   </si>
   <si>
+    <t>6/18/2026, 5:58:22 AM</t>
+  </si>
+  <si>
     <t>Enter expense description: Designer sneakers</t>
   </si>
   <si>
@@ -770,9 +776,6 @@
   </si>
   <si>
     <t>Entered: 1000</t>
-  </si>
-  <si>
-    <t>6/18/2026, 4:42:34 AM</t>
   </si>
   <si>
     <t>Check updated Food cap</t>
@@ -1610,21 +1613,21 @@
         <v>28</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
@@ -1633,21 +1636,21 @@
         <v>28</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>27</v>
@@ -1656,21 +1659,21 @@
         <v>28</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>27</v>
@@ -1679,21 +1682,21 @@
         <v>28</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
@@ -1702,21 +1705,21 @@
         <v>28</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>27</v>
@@ -1725,21 +1728,21 @@
         <v>28</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>27</v>
@@ -1748,7 +1751,7 @@
         <v>28</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1794,21 +1797,21 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -1817,7 +1820,7 @@
         <v>28</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1909,21 +1912,21 @@
         <v>28</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>27</v>
@@ -1932,21 +1935,21 @@
         <v>28</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>27</v>
@@ -1955,21 +1958,21 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -1978,21 +1981,21 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>27</v>
@@ -2001,21 +2004,21 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
@@ -2024,21 +2027,21 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>27</v>
@@ -2047,21 +2050,21 @@
         <v>28</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>27</v>
@@ -2070,21 +2073,21 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>27</v>
@@ -2093,7 +2096,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2125,10 +2128,10 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2139,10 +2142,10 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>7</v>
@@ -2168,143 +2171,143 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>24</v>
@@ -2321,109 +2324,109 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
@@ -2440,109 +2443,109 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>163</v>
-      </c>
       <c r="D18" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>24</v>
@@ -2559,109 +2562,109 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
@@ -2678,109 +2681,109 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>24</v>
@@ -2797,75 +2800,75 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>24</v>
@@ -2882,75 +2885,75 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>24</v>
@@ -2967,75 +2970,75 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>24</v>
@@ -3052,58 +3055,58 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>24</v>
@@ -3120,98 +3123,98 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>190</v>
-      </c>
       <c r="D58" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>28</v>
@@ -3222,30 +3225,30 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>28</v>
@@ -3256,64 +3259,64 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>28</v>
@@ -3324,47 +3327,47 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>28</v>
@@ -3375,132 +3378,132 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>28</v>
@@ -3511,47 +3514,47 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>28</v>
@@ -3562,75 +3565,75 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>24</v>
@@ -3647,126 +3650,126 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D89" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>24</v>
@@ -3783,30 +3786,30 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D96" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D97" s="6" t="s">
         <v>28</v>
@@ -3817,75 +3820,75 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D101" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>24</v>
@@ -3902,92 +3905,92 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D103" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D104" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D105" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D106" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D107" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>24</v>
@@ -4004,177 +4007,177 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D113" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>24</v>
@@ -4191,92 +4194,92 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D121" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D122" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D123" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>24</v>
@@ -4293,30 +4296,30 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D127" s="6" t="s">
         <v>28</v>
@@ -4327,47 +4330,47 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D128" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D129" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>28</v>
@@ -4378,30 +4381,30 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D131" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>28</v>
@@ -4412,98 +4415,98 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D133" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D135" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D137" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D138" s="6" t="s">
         <v>28</v>
@@ -4514,36 +4517,36 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D139" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
@@ -4551,16 +4554,16 @@
         <v>3</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D141" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -4568,16 +4571,16 @@
         <v>3</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D142" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
@@ -4585,16 +4588,16 @@
         <v>3</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D143" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -4602,16 +4605,16 @@
         <v>3</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D144" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -4622,7 +4625,7 @@
         <v>24</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D145" s="6" t="s">
         <v>28</v>
@@ -4636,16 +4639,16 @@
         <v>3</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D146" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
@@ -4656,7 +4659,7 @@
         <v>24</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D147" s="6" t="s">
         <v>28</v>
@@ -4670,16 +4673,16 @@
         <v>3</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D148" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -4690,7 +4693,7 @@
         <v>24</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D149" s="6" t="s">
         <v>28</v>
@@ -4707,7 +4710,7 @@
         <v>24</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D150" s="6" t="s">
         <v>28</v>

--- a/reports/Selenium_Report.xlsx
+++ b/reports/Selenium_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="269">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/18/2026, 5:58:23 AM</t>
+    <t>6/18/2026, 6:12:02 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>10.04s</t>
+    <t>11.04s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,7 +103,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>0.48s</t>
+    <t>1.24s</t>
   </si>
   <si>
     <t>TC-SEL-02</t>
@@ -115,33 +115,33 @@
     <t>Error message: "Passwords do not match." displays on password verification mismatch</t>
   </si>
   <si>
+    <t>0.76s</t>
+  </si>
+  <si>
+    <t>TC-SEL-03</t>
+  </si>
+  <si>
+    <t>Validate password minimum length validation constraint</t>
+  </si>
+  <si>
+    <t>Error message: "Password must be at least 8 characters." displays</t>
+  </si>
+  <si>
+    <t>0.51s</t>
+  </si>
+  <si>
+    <t>TC-SEL-04</t>
+  </si>
+  <si>
+    <t>Validate signup with duplicate email restriction</t>
+  </si>
+  <si>
+    <t>Error message: "Email address already registered." displays</t>
+  </si>
+  <si>
     <t>0.71s</t>
   </si>
   <si>
-    <t>TC-SEL-03</t>
-  </si>
-  <si>
-    <t>Validate password minimum length validation constraint</t>
-  </si>
-  <si>
-    <t>Error message: "Password must be at least 8 characters." displays</t>
-  </si>
-  <si>
-    <t>0.59s</t>
-  </si>
-  <si>
-    <t>TC-SEL-04</t>
-  </si>
-  <si>
-    <t>Validate signup with duplicate email restriction</t>
-  </si>
-  <si>
-    <t>Error message: "Email address already registered." displays</t>
-  </si>
-  <si>
-    <t>0.53s</t>
-  </si>
-  <si>
     <t>TC-SEL-05</t>
   </si>
   <si>
@@ -151,7 +151,7 @@
     <t>Registration succeeds, stores user session, and auto-routes to dashboard layout</t>
   </si>
   <si>
-    <t>0.67s</t>
+    <t>0.82s</t>
   </si>
   <si>
     <t>TC-SEL-06</t>
@@ -163,123 +163,123 @@
     <t>Form prevents submission or displays missing fields prompt</t>
   </si>
   <si>
+    <t>0.21s</t>
+  </si>
+  <si>
+    <t>TC-SEL-07</t>
+  </si>
+  <si>
+    <t>Validate login password length boundaries</t>
+  </si>
+  <si>
+    <t>0.35s</t>
+  </si>
+  <si>
+    <t>TC-SEL-08</t>
+  </si>
+  <si>
+    <t>Validate wrong password credential error boundary</t>
+  </si>
+  <si>
+    <t>Error message: "Invalid email or password credential." displays</t>
+  </si>
+  <si>
+    <t>0.29s</t>
+  </si>
+  <si>
+    <t>TC-SEL-09</t>
+  </si>
+  <si>
+    <t>Verify successful authentication for Admin Manager role</t>
+  </si>
+  <si>
+    <t>Login succeeds and redirects to dashboard with active sidebar</t>
+  </si>
+  <si>
+    <t>0.30s</t>
+  </si>
+  <si>
+    <t>TC-SEL-10</t>
+  </si>
+  <si>
+    <t>Verify Remember Me session storage persistence behavior</t>
+  </si>
+  <si>
+    <t>Session remains cached in localStorage when remember check is checked</t>
+  </si>
+  <si>
+    <t>0.45s</t>
+  </si>
+  <si>
+    <t>TC-SEL-11</t>
+  </si>
+  <si>
+    <t>Verify dashboard panels load initial default budgeting summary cards</t>
+  </si>
+  <si>
+    <t>Total Balance, Total Income, and Total Expenses load correctly</t>
+  </si>
+  <si>
+    <t>TC-SEL-12</t>
+  </si>
+  <si>
+    <t>Verify dashboard net balance math matches initial static transactions</t>
+  </si>
+  <si>
+    <t>Balance equals total income minus total expenses</t>
+  </si>
+  <si>
+    <t>0.06s</t>
+  </si>
+  <si>
+    <t>TC-SEL-13</t>
+  </si>
+  <si>
+    <t>Verify dashboard search bar resolves real-time query list matches</t>
+  </si>
+  <si>
+    <t>Typing transaction names filters matching rows dynamically</t>
+  </si>
+  <si>
+    <t>0.15s</t>
+  </si>
+  <si>
+    <t>TC-SEL-14</t>
+  </si>
+  <si>
+    <t>Verify add income inflow category transaction form submission flow</t>
+  </si>
+  <si>
+    <t>Inflow transaction added and net balance increases accordingly</t>
+  </si>
+  <si>
+    <t>0.65s</t>
+  </si>
+  <si>
+    <t>TC-SEL-15</t>
+  </si>
+  <si>
+    <t>Validate income forms empty constraints boundaries</t>
+  </si>
+  <si>
+    <t>Missing required inputs prevent transaction submission</t>
+  </si>
+  <si>
+    <t>0.14s</t>
+  </si>
+  <si>
+    <t>TC-SEL-16</t>
+  </si>
+  <si>
+    <t>Verify delete income transaction adjusts total calculations</t>
+  </si>
+  <si>
+    <t>Removing an income transaction successfully reduces total balance</t>
+  </si>
+  <si>
     <t>0.20s</t>
   </si>
   <si>
-    <t>TC-SEL-07</t>
-  </si>
-  <si>
-    <t>Validate login password length boundaries</t>
-  </si>
-  <si>
-    <t>0.29s</t>
-  </si>
-  <si>
-    <t>TC-SEL-08</t>
-  </si>
-  <si>
-    <t>Validate wrong password credential error boundary</t>
-  </si>
-  <si>
-    <t>Error message: "Invalid email or password credential." displays</t>
-  </si>
-  <si>
-    <t>0.30s</t>
-  </si>
-  <si>
-    <t>TC-SEL-09</t>
-  </si>
-  <si>
-    <t>Verify successful authentication for Admin Manager role</t>
-  </si>
-  <si>
-    <t>Login succeeds and redirects to dashboard with active sidebar</t>
-  </si>
-  <si>
-    <t>TC-SEL-10</t>
-  </si>
-  <si>
-    <t>Verify Remember Me session storage persistence behavior</t>
-  </si>
-  <si>
-    <t>Session remains cached in localStorage when remember check is checked</t>
-  </si>
-  <si>
-    <t>0.43s</t>
-  </si>
-  <si>
-    <t>TC-SEL-11</t>
-  </si>
-  <si>
-    <t>Verify dashboard panels load initial default budgeting summary cards</t>
-  </si>
-  <si>
-    <t>Total Balance, Total Income, and Total Expenses load correctly</t>
-  </si>
-  <si>
-    <t>0.27s</t>
-  </si>
-  <si>
-    <t>TC-SEL-12</t>
-  </si>
-  <si>
-    <t>Verify dashboard net balance math matches initial static transactions</t>
-  </si>
-  <si>
-    <t>Balance equals total income minus total expenses</t>
-  </si>
-  <si>
-    <t>0.06s</t>
-  </si>
-  <si>
-    <t>TC-SEL-13</t>
-  </si>
-  <si>
-    <t>Verify dashboard search bar resolves real-time query list matches</t>
-  </si>
-  <si>
-    <t>Typing transaction names filters matching rows dynamically</t>
-  </si>
-  <si>
-    <t>0.16s</t>
-  </si>
-  <si>
-    <t>TC-SEL-14</t>
-  </si>
-  <si>
-    <t>Verify add income inflow category transaction form submission flow</t>
-  </si>
-  <si>
-    <t>Inflow transaction added and net balance increases accordingly</t>
-  </si>
-  <si>
-    <t>0.57s</t>
-  </si>
-  <si>
-    <t>TC-SEL-15</t>
-  </si>
-  <si>
-    <t>Validate income forms empty constraints boundaries</t>
-  </si>
-  <si>
-    <t>Missing required inputs prevent transaction submission</t>
-  </si>
-  <si>
-    <t>0.14s</t>
-  </si>
-  <si>
-    <t>TC-SEL-16</t>
-  </si>
-  <si>
-    <t>Verify delete income transaction adjusts total calculations</t>
-  </si>
-  <si>
-    <t>Removing an income transaction successfully reduces total balance</t>
-  </si>
-  <si>
-    <t>0.23s</t>
-  </si>
-  <si>
     <t>TC-SEL-17</t>
   </si>
   <si>
@@ -289,6 +289,9 @@
     <t>Outflow transaction decreases net balance</t>
   </si>
   <si>
+    <t>0.54s</t>
+  </si>
+  <si>
     <t>TC-SEL-18</t>
   </si>
   <si>
@@ -298,7 +301,7 @@
     <t>Negative or text values in amount are rejected</t>
   </si>
   <si>
-    <t>0.08s</t>
+    <t>0.07s</t>
   </si>
   <si>
     <t>TC-SEL-19</t>
@@ -310,7 +313,7 @@
     <t>Deleting an expense successfully restores balance amount</t>
   </si>
   <si>
-    <t>0.21s</t>
+    <t>0.25s</t>
   </si>
   <si>
     <t>TC-SEL-20</t>
@@ -322,7 +325,7 @@
     <t>Category caps limits are saved and progress bars render</t>
   </si>
   <si>
-    <t>0.39s</t>
+    <t>0.38s</t>
   </si>
   <si>
     <t>TC-SEL-21</t>
@@ -334,7 +337,7 @@
     <t>Budget Cap overflow modal popup loads when transaction exceeds cap</t>
   </si>
   <si>
-    <t>0.81s</t>
+    <t>0.80s</t>
   </si>
   <si>
     <t>TC-SEL-22</t>
@@ -346,9 +349,6 @@
     <t>Updating limit increases budget cap and progress decreases</t>
   </si>
   <si>
-    <t>0.31s</t>
-  </si>
-  <si>
     <t>TC-SEL-23</t>
   </si>
   <si>
@@ -358,75 +358,75 @@
     <t>Monthly Balance Trend line container is visible on page</t>
   </si>
   <si>
+    <t>0.10s</t>
+  </si>
+  <si>
+    <t>TC-SEL-24</t>
+  </si>
+  <si>
+    <t>Verify category distribution breakdown list aggregates metrics</t>
+  </si>
+  <si>
+    <t>Analytics categories breakdown table loads and sums values</t>
+  </si>
+  <si>
+    <t>TC-SEL-25</t>
+  </si>
+  <si>
+    <t>Verify raw data export reports CSV simulation download trigger</t>
+  </si>
+  <si>
+    <t>Clicking export initializes simulated raw CSV download</t>
+  </si>
+  <si>
+    <t>TC-SEL-26</t>
+  </si>
+  <si>
+    <t>Verify user profile metadata fields update successfully</t>
+  </si>
+  <si>
+    <t>Display name successfully updates and synchronizes with sidebar user block</t>
+  </si>
+  <si>
+    <t>0.40s</t>
+  </si>
+  <si>
+    <t>TC-SEL-27</t>
+  </si>
+  <si>
+    <t>Verify preferred default currency synchronization on profile updates</t>
+  </si>
+  <si>
+    <t>Changing currency symbol on profile alters dashboard symbols</t>
+  </si>
+  <si>
+    <t>0.44s</t>
+  </si>
+  <si>
+    <t>TC-SEL-28</t>
+  </si>
+  <si>
+    <t>Verify profile assigned application role is readonly configuration</t>
+  </si>
+  <si>
+    <t>Application role text box contains "readonly" property attribute</t>
+  </si>
+  <si>
+    <t>0.11s</t>
+  </si>
+  <si>
+    <t>TC-SEL-29</t>
+  </si>
+  <si>
+    <t>Verify successful user logout redirects to authentication login view</t>
+  </si>
+  <si>
+    <t>Session clears and client redirects to login view immediately</t>
+  </si>
+  <si>
     <t>0.09s</t>
   </si>
   <si>
-    <t>TC-SEL-24</t>
-  </si>
-  <si>
-    <t>Verify category distribution breakdown list aggregates metrics</t>
-  </si>
-  <si>
-    <t>Analytics categories breakdown table loads and sums values</t>
-  </si>
-  <si>
-    <t>0.11s</t>
-  </si>
-  <si>
-    <t>TC-SEL-25</t>
-  </si>
-  <si>
-    <t>Verify raw data export reports CSV simulation download trigger</t>
-  </si>
-  <si>
-    <t>Clicking export initializes simulated raw CSV download</t>
-  </si>
-  <si>
-    <t>0.10s</t>
-  </si>
-  <si>
-    <t>TC-SEL-26</t>
-  </si>
-  <si>
-    <t>Verify user profile metadata fields update successfully</t>
-  </si>
-  <si>
-    <t>Display name successfully updates and synchronizes with sidebar user block</t>
-  </si>
-  <si>
-    <t>0.41s</t>
-  </si>
-  <si>
-    <t>TC-SEL-27</t>
-  </si>
-  <si>
-    <t>Verify preferred default currency synchronization on profile updates</t>
-  </si>
-  <si>
-    <t>Changing currency symbol on profile alters dashboard symbols</t>
-  </si>
-  <si>
-    <t>0.40s</t>
-  </si>
-  <si>
-    <t>TC-SEL-28</t>
-  </si>
-  <si>
-    <t>Verify profile assigned application role is readonly configuration</t>
-  </si>
-  <si>
-    <t>Application role text box contains "readonly" property attribute</t>
-  </si>
-  <si>
-    <t>TC-SEL-29</t>
-  </si>
-  <si>
-    <t>Verify successful user logout redirects to authentication login view</t>
-  </si>
-  <si>
-    <t>Session clears and client redirects to login view immediately</t>
-  </si>
-  <si>
     <t>TC-SEL-30</t>
   </si>
   <si>
@@ -436,7 +436,7 @@
     <t>Inactivity trigger automatically destroys token and redirects to login view</t>
   </si>
   <si>
-    <t>0.47s</t>
+    <t>0.22s</t>
   </si>
   <si>
     <t>Failure Message</t>
@@ -463,7 +463,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>6/18/2026, 5:58:14 AM</t>
+    <t>6/18/2026, 6:11:52 AM</t>
   </si>
   <si>
     <t>LoginPage</t>
@@ -493,6 +493,9 @@
     <t>Confirm register password</t>
   </si>
   <si>
+    <t>6/18/2026, 6:11:53 AM</t>
+  </si>
+  <si>
     <t>Click Sign Up Button</t>
   </si>
   <si>
@@ -502,9 +505,6 @@
     <t>Text found: "All fields are required for registration."</t>
   </si>
   <si>
-    <t>6/18/2026, 5:58:15 AM</t>
-  </si>
-  <si>
     <t>Enter register name: Sarah Connor</t>
   </si>
   <si>
@@ -526,7 +526,7 @@
     <t>Text found: "Passwords do not match."</t>
   </si>
   <si>
-    <t>6/18/2026, 5:58:16 AM</t>
+    <t>6/18/2026, 6:11:54 AM</t>
   </si>
   <si>
     <t>Entered: 12345</t>
@@ -550,12 +550,12 @@
     <t>Entered: SmartBudgetPass123!</t>
   </si>
   <si>
+    <t>6/18/2026, 6:11:55 AM</t>
+  </si>
+  <si>
     <t>Text found: "Email address already registered."</t>
   </si>
   <si>
-    <t>6/18/2026, 5:58:17 AM</t>
-  </si>
-  <si>
     <t>Entered: SarahPass123!</t>
   </si>
   <si>
@@ -568,6 +568,9 @@
     <t xml:space="preserve">Enter login email: </t>
   </si>
   <si>
+    <t>6/18/2026, 6:11:56 AM</t>
+  </si>
+  <si>
     <t>Enter login password</t>
   </si>
   <si>
@@ -589,15 +592,15 @@
     <t>Entered: 123</t>
   </si>
   <si>
-    <t>6/18/2026, 5:58:18 AM</t>
-  </si>
-  <si>
     <t>Enter login email: admin@budget.com</t>
   </si>
   <si>
     <t>Text found: "Invalid email or password credential."</t>
   </si>
   <si>
+    <t>6/18/2026, 6:11:57 AM</t>
+  </si>
+  <si>
     <t>Check Remember Me option</t>
   </si>
   <si>
@@ -607,9 +610,6 @@
     <t>Text found: "$3,410.00"</t>
   </si>
   <si>
-    <t>6/18/2026, 5:58:19 AM</t>
-  </si>
-  <si>
     <t>Read total income statistic</t>
   </si>
   <si>
@@ -640,6 +640,9 @@
     <t>Entered: Salary</t>
   </si>
   <si>
+    <t>6/18/2026, 6:11:58 AM</t>
+  </si>
+  <si>
     <t>Enter income amount: 2500</t>
   </si>
   <si>
@@ -661,9 +664,6 @@
     <t>Click submit button on empty form</t>
   </si>
   <si>
-    <t>6/18/2026, 5:58:20 AM</t>
-  </si>
-  <si>
     <t>Navigate to tab: nav-dashboard</t>
   </si>
   <si>
@@ -682,6 +682,9 @@
     <t>Entered: Food</t>
   </si>
   <si>
+    <t>6/18/2026, 6:11:59 AM</t>
+  </si>
+  <si>
     <t>Enter expense amount: 120</t>
   </si>
   <si>
@@ -704,9 +707,6 @@
   </si>
   <si>
     <t>Text found: "$1,990.00"</t>
-  </si>
-  <si>
-    <t>6/18/2026, 5:58:21 AM</t>
   </si>
   <si>
     <t>Navigate to tab: nav-budget</t>
@@ -739,6 +739,9 @@
 $0.00 / $1500.00 (0%)"</t>
   </si>
   <si>
+    <t>6/18/2026, 6:12:00 AM</t>
+  </si>
+  <si>
     <t>Select budget segment: Shopping</t>
   </si>
   <si>
@@ -760,9 +763,6 @@
     <t>Entered: 250</t>
   </si>
   <si>
-    <t>6/18/2026, 5:58:22 AM</t>
-  </si>
-  <si>
     <t>Enter expense description: Designer sneakers</t>
   </si>
   <si>
@@ -776,6 +776,9 @@
   </si>
   <si>
     <t>Entered: 1000</t>
+  </si>
+  <si>
+    <t>6/18/2026, 6:12:01 AM</t>
   </si>
   <si>
     <t>Check updated Food cap</t>
@@ -1613,21 +1616,21 @@
         <v>28</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
@@ -1636,21 +1639,21 @@
         <v>28</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>27</v>
@@ -1659,7 +1662,7 @@
         <v>28</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1797,21 +1800,21 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -1820,21 +1823,21 @@
         <v>28</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>27</v>
@@ -1843,21 +1846,21 @@
         <v>28</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>27</v>
@@ -1866,21 +1869,21 @@
         <v>28</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>27</v>
@@ -1889,21 +1892,21 @@
         <v>28</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>27</v>
@@ -1912,7 +1915,7 @@
         <v>28</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1958,21 +1961,21 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>121</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -1981,21 +1984,21 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>125</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>27</v>
@@ -2004,21 +2007,21 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>129</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
@@ -2027,21 +2030,21 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>133</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>27</v>
@@ -2050,21 +2053,21 @@
         <v>28</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>136</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>27</v>
@@ -2073,7 +2076,7 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2273,13 +2276,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>153</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>28</v>
@@ -2290,24 +2293,24 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>153</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>24</v>
@@ -2324,7 +2327,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>153</v>
@@ -2341,7 +2344,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>153</v>
@@ -2358,7 +2361,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>153</v>
@@ -2375,7 +2378,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>153</v>
@@ -2392,13 +2395,13 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>153</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>28</v>
@@ -2409,13 +2412,13 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>153</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
@@ -2426,7 +2429,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
@@ -2443,7 +2446,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>153</v>
@@ -2460,7 +2463,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>153</v>
@@ -2517,7 +2520,7 @@
         <v>153</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>28</v>
@@ -2534,7 +2537,7 @@
         <v>153</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>28</v>
@@ -2613,7 +2616,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>153</v>
@@ -2630,13 +2633,13 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>153</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>28</v>
@@ -2647,24 +2650,24 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>153</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
@@ -2681,7 +2684,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>153</v>
@@ -2698,7 +2701,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>153</v>
@@ -2715,7 +2718,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>153</v>
@@ -2732,7 +2735,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>153</v>
@@ -2749,13 +2752,13 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>153</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>28</v>
@@ -2766,7 +2769,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>181</v>
@@ -2783,7 +2786,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>24</v>
@@ -2800,7 +2803,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>150</v>
@@ -2817,13 +2820,13 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>150</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>28</v>
@@ -2834,13 +2837,13 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>150</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>28</v>
@@ -2851,24 +2854,24 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>150</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>24</v>
@@ -2885,47 +2888,47 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>150</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>150</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>150</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>28</v>
@@ -2936,13 +2939,13 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>150</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>28</v>
@@ -2953,7 +2956,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>24</v>
@@ -2970,7 +2973,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>150</v>
@@ -2987,13 +2990,13 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>150</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>28</v>
@@ -3004,13 +3007,13 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>150</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>28</v>
@@ -3021,13 +3024,13 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>150</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>28</v>
@@ -3038,7 +3041,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>24</v>
@@ -3055,7 +3058,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>150</v>
@@ -3072,13 +3075,13 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>150</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>28</v>
@@ -3089,13 +3092,13 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>150</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>28</v>
@@ -3106,7 +3109,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>24</v>
@@ -3123,7 +3126,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>181</v>
@@ -3140,7 +3143,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>150</v>
@@ -3157,13 +3160,13 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>150</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>28</v>
@@ -3174,13 +3177,13 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>150</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>28</v>
@@ -3191,13 +3194,13 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>150</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>28</v>
@@ -3208,13 +3211,13 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>28</v>
@@ -3225,30 +3228,30 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>28</v>
@@ -3259,24 +3262,24 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E65" s="3" t="s">
         <v>197</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>181</v>
@@ -3293,7 +3296,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>181</v>
@@ -3310,7 +3313,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>24</v>
@@ -3327,7 +3330,7 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>181</v>
@@ -3344,7 +3347,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>181</v>
@@ -3361,7 +3364,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>24</v>
@@ -3378,24 +3381,24 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>197</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>181</v>
@@ -3412,7 +3415,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>181</v>
@@ -3429,47 +3432,47 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>28</v>
@@ -3480,24 +3483,24 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>24</v>
@@ -3514,7 +3517,7 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>181</v>
@@ -3531,13 +3534,13 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>28</v>
@@ -3548,7 +3551,7 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>24</v>
@@ -3565,7 +3568,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>181</v>
@@ -3582,24 +3585,24 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>181</v>
@@ -3616,13 +3619,13 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>28</v>
@@ -3633,7 +3636,7 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>24</v>
@@ -3650,13 +3653,13 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>28</v>
@@ -3667,7 +3670,7 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>181</v>
@@ -3684,7 +3687,7 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>181</v>
@@ -3701,47 +3704,47 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>28</v>
@@ -3752,24 +3755,24 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>24</v>
@@ -3786,7 +3789,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>181</v>
@@ -3803,13 +3806,13 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D97" s="6" t="s">
         <v>28</v>
@@ -3820,7 +3823,7 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>181</v>
@@ -3837,30 +3840,30 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>28</v>
@@ -3871,30 +3874,30 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D101" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D102" s="6" t="s">
         <v>28</v>
@@ -3905,7 +3908,7 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>181</v>
@@ -3922,7 +3925,7 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>181</v>
@@ -3939,7 +3942,7 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>181</v>
@@ -3956,7 +3959,7 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>181</v>
@@ -3973,7 +3976,7 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>181</v>
@@ -3990,13 +3993,13 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D108" s="6" t="s">
         <v>28</v>
@@ -4007,7 +4010,7 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>181</v>
@@ -4024,41 +4027,41 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>181</v>
@@ -4075,7 +4078,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>181</v>
@@ -4092,41 +4095,41 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>181</v>
@@ -4143,13 +4146,13 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>28</v>
@@ -4160,7 +4163,7 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>181</v>
@@ -4177,13 +4180,13 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D119" s="6" t="s">
         <v>28</v>
@@ -4194,7 +4197,7 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>181</v>
@@ -4211,7 +4214,7 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>181</v>
@@ -4228,7 +4231,7 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>181</v>
@@ -4245,7 +4248,7 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>181</v>
@@ -4262,30 +4265,30 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D125" s="6" t="s">
         <v>28</v>
@@ -4296,13 +4299,13 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>28</v>
@@ -4313,7 +4316,7 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>24</v>
@@ -4330,13 +4333,13 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D128" s="6" t="s">
         <v>28</v>
@@ -4347,24 +4350,24 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D129" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>24</v>
@@ -4381,13 +4384,13 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D131" s="6" t="s">
         <v>28</v>
@@ -4398,13 +4401,13 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>28</v>
@@ -4415,13 +4418,13 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D133" s="6" t="s">
         <v>28</v>
@@ -4432,47 +4435,47 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
-        <v>3</v>
+        <v>251</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
-        <v>3</v>
+        <v>251</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D135" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
-        <v>3</v>
+        <v>251</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>28</v>
@@ -4483,30 +4486,30 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
-        <v>3</v>
+        <v>251</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D137" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
-        <v>3</v>
+        <v>251</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D138" s="6" t="s">
         <v>28</v>
@@ -4517,13 +4520,13 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
-        <v>3</v>
+        <v>251</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D139" s="6" t="s">
         <v>28</v>
@@ -4534,19 +4537,19 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
-        <v>3</v>
+        <v>251</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
@@ -4557,13 +4560,13 @@
         <v>181</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D141" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -4574,7 +4577,7 @@
         <v>181</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D142" s="6" t="s">
         <v>28</v>
@@ -4608,13 +4611,13 @@
         <v>181</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D144" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -4625,7 +4628,7 @@
         <v>24</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D145" s="6" t="s">
         <v>28</v>
@@ -4642,7 +4645,7 @@
         <v>181</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D146" s="6" t="s">
         <v>28</v>
@@ -4659,7 +4662,7 @@
         <v>24</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D147" s="6" t="s">
         <v>28</v>
@@ -4693,7 +4696,7 @@
         <v>24</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D149" s="6" t="s">
         <v>28</v>

--- a/reports/Selenium_Report.xlsx
+++ b/reports/Selenium_Report.xlsx
@@ -24,7 +24,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>18/6/2026, 12:06:19 pm</t>
+    <t>18/6/2026, 12:08:55 pm</t>
   </si>
   <si>
     <t>Test Suite / Scope</t>
@@ -96,1522 +96,1522 @@
     <t>PASS</t>
   </si>
   <si>
+    <t>0.10s</t>
+  </si>
+  <si>
+    <t>TC-SEL-002</t>
+  </si>
+  <si>
+    <t>Verify Login Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Login Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>0.30s</t>
+  </si>
+  <si>
+    <t>TC-SEL-003</t>
+  </si>
+  <si>
+    <t>Verify Login Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Login Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>0.26s</t>
+  </si>
+  <si>
+    <t>TC-SEL-004</t>
+  </si>
+  <si>
+    <t>Verify Login Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Login Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>0.39s</t>
+  </si>
+  <si>
+    <t>TC-SEL-005</t>
+  </si>
+  <si>
+    <t>Verify Login Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Login Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>0.22s</t>
+  </si>
+  <si>
+    <t>TC-SEL-006</t>
+  </si>
+  <si>
+    <t>Verify Login Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Login Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>0.27s</t>
+  </si>
+  <si>
+    <t>TC-SEL-007</t>
+  </si>
+  <si>
+    <t>Verify Login Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Login Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>0.34s</t>
+  </si>
+  <si>
+    <t>TC-SEL-008</t>
+  </si>
+  <si>
+    <t>Verify Login Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Login Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-009</t>
+  </si>
+  <si>
+    <t>Verify Login Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Login Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-010</t>
+  </si>
+  <si>
+    <t>Verify Login Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Login Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>0.35s</t>
+  </si>
+  <si>
+    <t>TC-SEL-011</t>
+  </si>
+  <si>
+    <t>Registration Screen</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-012</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>0.46s</t>
+  </si>
+  <si>
+    <t>TC-SEL-013</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>0.48s</t>
+  </si>
+  <si>
+    <t>TC-SEL-014</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>0.38s</t>
+  </si>
+  <si>
+    <t>TC-SEL-015</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>0.19s</t>
+  </si>
+  <si>
+    <t>TC-SEL-016</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>0.14s</t>
+  </si>
+  <si>
+    <t>TC-SEL-017</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>0.37s</t>
+  </si>
+  <si>
+    <t>TC-SEL-018</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-019</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>0.28s</t>
+  </si>
+  <si>
+    <t>TC-SEL-020</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>0.17s</t>
+  </si>
+  <si>
+    <t>TC-SEL-021</t>
+  </si>
+  <si>
+    <t>Forgot Password Screen</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>0.24s</t>
+  </si>
+  <si>
+    <t>TC-SEL-022</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>0.41s</t>
+  </si>
+  <si>
+    <t>TC-SEL-023</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-024</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-025</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>0.45s</t>
+  </si>
+  <si>
+    <t>TC-SEL-026</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>0.43s</t>
+  </si>
+  <si>
+    <t>TC-SEL-027</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-028</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-029</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>0.40s</t>
+  </si>
+  <si>
+    <t>TC-SEL-030</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>0.42s</t>
+  </si>
+  <si>
+    <t>TC-SEL-031</t>
+  </si>
+  <si>
+    <t>OTP Verification Screen</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>0.33s</t>
+  </si>
+  <si>
+    <t>TC-SEL-032</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>0.11s</t>
+  </si>
+  <si>
+    <t>TC-SEL-033</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 3 without validation errors</t>
+  </si>
+  <si>
     <t>0.31s</t>
   </si>
   <si>
-    <t>TC-SEL-002</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 2 without validation errors</t>
+    <t>TC-SEL-034</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-035</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-036</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-037</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>0.29s</t>
+  </si>
+  <si>
+    <t>TC-SEL-038</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-039</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-040</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-041</t>
+  </si>
+  <si>
+    <t>Multi-Factor Auth Screen</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-042</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-043</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-044</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-045</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-046</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-047</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>0.21s</t>
+  </si>
+  <si>
+    <t>TC-SEL-048</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>0.20s</t>
+  </si>
+  <si>
+    <t>TC-SEL-049</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>0.23s</t>
+  </si>
+  <si>
+    <t>TC-SEL-050</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>0.18s</t>
+  </si>
+  <si>
+    <t>TC-SEL-051</t>
+  </si>
+  <si>
+    <t>Host Dashboard Screen</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>0.12s</t>
+  </si>
+  <si>
+    <t>TC-SEL-052</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-053</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>0.50s</t>
+  </si>
+  <si>
+    <t>TC-SEL-054</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-055</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-056</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-057</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-058</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>0.36s</t>
+  </si>
+  <si>
+    <t>TC-SEL-059</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-060</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-061</t>
+  </si>
+  <si>
+    <t>Guard Dashboard Screen</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-062</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-063</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-064</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-065</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-066</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-067</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-068</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-069</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-070</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-071</t>
+  </si>
+  <si>
+    <t>Admin Dashboard Screen</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-072</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-073</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-074</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-075</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-076</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-077</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>0.44s</t>
+  </si>
+  <si>
+    <t>TC-SEL-078</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-079</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-080</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-081</t>
+  </si>
+  <si>
+    <t>Visitor Logs Screen</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-082</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-083</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>0.47s</t>
+  </si>
+  <si>
+    <t>TC-SEL-084</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-085</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-086</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-087</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-088</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-089</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-090</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-091</t>
+  </si>
+  <si>
+    <t>Scan QR Screen</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-092</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-093</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-094</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-095</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-096</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-097</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-098</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-099</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-100</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-101</t>
+  </si>
+  <si>
+    <t>Face Verify Screen</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-102</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>0.13s</t>
+  </si>
+  <si>
+    <t>TC-SEL-103</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 3 without validation errors</t>
   </si>
   <si>
     <t>0.15s</t>
   </si>
   <si>
-    <t>TC-SEL-003</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 3 without validation errors</t>
+    <t>TC-SEL-104</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-105</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-106</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-107</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-108</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-109</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-110</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 10 without validation errors</t>
   </si>
   <si>
     <t>0.49s</t>
   </si>
   <si>
-    <t>TC-SEL-004</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-005</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>0.23s</t>
-  </si>
-  <si>
-    <t>TC-SEL-006</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>0.28s</t>
-  </si>
-  <si>
-    <t>TC-SEL-007</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>0.38s</t>
-  </si>
-  <si>
-    <t>TC-SEL-008</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>0.41s</t>
-  </si>
-  <si>
-    <t>TC-SEL-009</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>0.36s</t>
-  </si>
-  <si>
-    <t>TC-SEL-010</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>0.35s</t>
-  </si>
-  <si>
-    <t>TC-SEL-011</t>
-  </si>
-  <si>
-    <t>Registration Screen</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>0.17s</t>
-  </si>
-  <si>
-    <t>TC-SEL-012</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-013</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>0.14s</t>
-  </si>
-  <si>
-    <t>TC-SEL-014</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>0.22s</t>
-  </si>
-  <si>
-    <t>TC-SEL-015</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>0.37s</t>
-  </si>
-  <si>
-    <t>TC-SEL-016</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>0.20s</t>
-  </si>
-  <si>
-    <t>TC-SEL-017</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-018</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>0.19s</t>
-  </si>
-  <si>
-    <t>TC-SEL-019</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 9 without validation errors</t>
+    <t>TC-SEL-111</t>
+  </si>
+  <si>
+    <t>Profile Screen</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-112</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-113</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-114</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-115</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-116</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-117</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-118</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 8 without validation errors</t>
   </si>
   <si>
     <t>0.16s</t>
   </si>
   <si>
-    <t>TC-SEL-020</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>0.45s</t>
-  </si>
-  <si>
-    <t>TC-SEL-021</t>
-  </si>
-  <si>
-    <t>Forgot Password Screen</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-022</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>0.44s</t>
-  </si>
-  <si>
-    <t>TC-SEL-023</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-024</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-025</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>0.48s</t>
-  </si>
-  <si>
-    <t>TC-SEL-026</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>0.29s</t>
-  </si>
-  <si>
-    <t>TC-SEL-027</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>0.34s</t>
-  </si>
-  <si>
-    <t>TC-SEL-028</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>0.39s</t>
-  </si>
-  <si>
-    <t>TC-SEL-029</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>0.30s</t>
-  </si>
-  <si>
-    <t>TC-SEL-030</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-031</t>
-  </si>
-  <si>
-    <t>OTP Verification Screen</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>0.47s</t>
-  </si>
-  <si>
-    <t>TC-SEL-032</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-033</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-034</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>0.50s</t>
-  </si>
-  <si>
-    <t>TC-SEL-035</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-036</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-037</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>0.46s</t>
-  </si>
-  <si>
-    <t>TC-SEL-038</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>0.18s</t>
-  </si>
-  <si>
-    <t>TC-SEL-039</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>0.43s</t>
-  </si>
-  <si>
-    <t>TC-SEL-040</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>0.42s</t>
-  </si>
-  <si>
-    <t>TC-SEL-041</t>
-  </si>
-  <si>
-    <t>Multi-Factor Auth Screen</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-042</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>0.12s</t>
-  </si>
-  <si>
-    <t>TC-SEL-043</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>0.13s</t>
-  </si>
-  <si>
-    <t>TC-SEL-044</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-045</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 5 without validation errors</t>
+    <t>TC-SEL-119</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-120</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-121</t>
+  </si>
+  <si>
+    <t>Settings Screen</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-122</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-123</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-124</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-125</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-126</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-127</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-128</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-129</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-130</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-131</t>
+  </si>
+  <si>
+    <t>Pass Preview Screen</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-132</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-133</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-134</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-135</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-136</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-137</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-138</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-139</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-140</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-141</t>
+  </si>
+  <si>
+    <t>Active Visitor Details Screen</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-142</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-143</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-144</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-145</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-146</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-147</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-148</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-149</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEL-150</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 10 without validation errors</t>
   </si>
   <si>
     <t>0.32s</t>
   </si>
   <si>
-    <t>TC-SEL-046</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-047</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-048</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-049</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-050</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-051</t>
-  </si>
-  <si>
-    <t>Host Dashboard Screen</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>0.11s</t>
-  </si>
-  <si>
-    <t>TC-SEL-052</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>0.24s</t>
-  </si>
-  <si>
-    <t>TC-SEL-053</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-054</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>0.26s</t>
-  </si>
-  <si>
-    <t>TC-SEL-055</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-056</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-057</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-058</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-059</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-060</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-061</t>
-  </si>
-  <si>
-    <t>Guard Dashboard Screen</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-062</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-063</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-064</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-065</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-066</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-067</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-068</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-069</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-070</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-071</t>
-  </si>
-  <si>
-    <t>Admin Dashboard Screen</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-072</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-073</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-074</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-075</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>0.40s</t>
-  </si>
-  <si>
-    <t>TC-SEL-076</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>0.33s</t>
-  </si>
-  <si>
-    <t>TC-SEL-077</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-078</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-079</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-080</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-081</t>
-  </si>
-  <si>
-    <t>Visitor Logs Screen</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-082</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-083</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-084</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-085</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-086</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-087</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-088</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-089</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-090</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-091</t>
-  </si>
-  <si>
-    <t>Scan QR Screen</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-092</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>0.21s</t>
-  </si>
-  <si>
-    <t>TC-SEL-093</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-094</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-095</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-096</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-097</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-098</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-099</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-100</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-101</t>
-  </si>
-  <si>
-    <t>Face Verify Screen</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-102</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-103</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-104</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-105</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 5 without validation errors</t>
+    <t>TC-SEL-151</t>
+  </si>
+  <si>
+    <t>Upcoming Visit Details Screen</t>
+  </si>
+  <si>
+    <t>Verify Upcoming Visit Details Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Upcoming Visit Details Screen action 1 without validation errors</t>
   </si>
   <si>
     <t>0.25s</t>
-  </si>
-  <si>
-    <t>TC-SEL-106</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-107</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-108</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-109</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-110</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-111</t>
-  </si>
-  <si>
-    <t>Profile Screen</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-112</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-113</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-114</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-115</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-116</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-117</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-118</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-119</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-120</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-121</t>
-  </si>
-  <si>
-    <t>Settings Screen</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-122</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-123</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-124</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-125</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-126</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-127</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-128</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>0.10s</t>
-  </si>
-  <si>
-    <t>TC-SEL-129</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-130</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-131</t>
-  </si>
-  <si>
-    <t>Pass Preview Screen</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-132</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-133</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-134</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-135</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-136</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-137</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-138</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-139</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-140</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>0.27s</t>
-  </si>
-  <si>
-    <t>TC-SEL-141</t>
-  </si>
-  <si>
-    <t>Active Visitor Details Screen</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-142</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-143</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-144</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-145</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-146</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-147</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-148</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-149</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-150</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-151</t>
-  </si>
-  <si>
-    <t>Upcoming Visit Details Screen</t>
-  </si>
-  <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 1 without validation errors</t>
   </si>
   <si>
     <t>TC-SEL-152</t>
@@ -3652,21 +3652,21 @@
         <v>26</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>25</v>
@@ -3675,21 +3675,21 @@
         <v>26</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>25</v>
@@ -3698,21 +3698,21 @@
         <v>26</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>25</v>
@@ -3721,21 +3721,21 @@
         <v>26</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>25</v>
@@ -3744,7 +3744,7 @@
         <v>26</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -3767,45 +3767,45 @@
         <v>26</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="E12" s="3" t="s">
         <v>25</v>
       </c>
@@ -3813,145 +3813,145 @@
         <v>26</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="E13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -3959,7 +3959,7 @@
         <v>90</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>91</v>
@@ -3974,76 +3974,76 @@
         <v>26</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -4051,7 +4051,7 @@
         <v>106</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>107</v>
@@ -4074,7 +4074,7 @@
         <v>110</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>111</v>
@@ -4089,7 +4089,7 @@
         <v>26</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>27</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -4097,7 +4097,7 @@
         <v>113</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>114</v>
@@ -4112,7 +4112,7 @@
         <v>26</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -4120,7 +4120,7 @@
         <v>116</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>117</v>
@@ -4143,7 +4143,7 @@
         <v>120</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>121</v>
@@ -4166,7 +4166,7 @@
         <v>124</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>125</v>
@@ -4181,22 +4181,22 @@
         <v>26</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>130</v>
-      </c>
       <c r="E29" s="3" t="s">
         <v>25</v>
       </c>
@@ -4204,99 +4204,99 @@
         <v>26</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>131</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C30" s="3" t="s">
+      <c r="E30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C31" s="3" t="s">
+      <c r="E31" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="D32" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="E32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C33" s="3" t="s">
+      <c r="D33" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="E33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -4304,7 +4304,7 @@
         <v>147</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>148</v>
@@ -4319,21 +4319,21 @@
         <v>26</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>58</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>25</v>
@@ -4342,7 +4342,7 @@
         <v>26</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>153</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -4350,7 +4350,7 @@
         <v>154</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>155</v>
@@ -4365,7 +4365,7 @@
         <v>26</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -4373,7 +4373,7 @@
         <v>157</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>158</v>
@@ -4396,7 +4396,7 @@
         <v>160</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>161</v>
@@ -4419,7 +4419,7 @@
         <v>164</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>165</v>
@@ -4434,22 +4434,22 @@
         <v>26</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C40" s="3" t="s">
+      <c r="D40" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="E40" s="3" t="s">
         <v>25</v>
       </c>
@@ -4457,22 +4457,22 @@
         <v>26</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="E41" s="3" t="s">
         <v>25</v>
       </c>
@@ -4480,22 +4480,22 @@
         <v>26</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>175</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>179</v>
-      </c>
       <c r="E42" s="3" t="s">
         <v>25</v>
       </c>
@@ -4503,21 +4503,21 @@
         <v>26</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>25</v>
@@ -4526,21 +4526,21 @@
         <v>26</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>183</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>25</v>
@@ -4549,21 +4549,21 @@
         <v>26</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>25</v>
@@ -4572,21 +4572,21 @@
         <v>26</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>25</v>
@@ -4595,21 +4595,21 @@
         <v>26</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>194</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>25</v>
@@ -4618,21 +4618,21 @@
         <v>26</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>183</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>25</v>
@@ -4641,21 +4641,21 @@
         <v>26</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>25</v>
@@ -4664,21 +4664,21 @@
         <v>26</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>27</v>
+        <v>199</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>25</v>
@@ -4687,68 +4687,68 @@
         <v>26</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>123</v>
+        <v>203</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="D52" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="E52" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="E53" s="3" t="s">
         <v>25</v>
       </c>
@@ -4756,45 +4756,45 @@
         <v>26</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>218</v>
+        <v>96</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>224</v>
-      </c>
       <c r="E55" s="3" t="s">
         <v>25</v>
       </c>
@@ -4802,21 +4802,21 @@
         <v>26</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>225</v>
+        <v>123</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>25</v>
@@ -4825,21 +4825,21 @@
         <v>26</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>25</v>
@@ -4848,21 +4848,21 @@
         <v>26</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>218</v>
+        <v>69</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>25</v>
@@ -4871,45 +4871,45 @@
         <v>26</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>218</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="3" t="s">
         <v>235</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>240</v>
-      </c>
       <c r="E60" s="3" t="s">
         <v>25</v>
       </c>
@@ -4917,22 +4917,22 @@
         <v>26</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>131</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D61" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B61" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>243</v>
-      </c>
       <c r="E61" s="3" t="s">
         <v>25</v>
       </c>
@@ -4940,22 +4940,22 @@
         <v>26</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>27</v>
+        <v>235</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="D62" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>247</v>
-      </c>
       <c r="E62" s="3" t="s">
         <v>25</v>
       </c>
@@ -4963,22 +4963,22 @@
         <v>26</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>123</v>
+        <v>203</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="E63" s="3" t="s">
         <v>25</v>
       </c>
@@ -4986,22 +4986,22 @@
         <v>26</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>187</v>
+        <v>96</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D64" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="B64" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>253</v>
-      </c>
       <c r="E64" s="3" t="s">
         <v>25</v>
       </c>
@@ -5009,22 +5009,22 @@
         <v>26</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D65" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>256</v>
-      </c>
       <c r="E65" s="3" t="s">
         <v>25</v>
       </c>
@@ -5032,22 +5032,22 @@
         <v>26</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>131</v>
+        <v>199</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D66" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>259</v>
-      </c>
       <c r="E66" s="3" t="s">
         <v>25</v>
       </c>
@@ -5055,22 +5055,22 @@
         <v>26</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>74</v>
+        <v>109</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D67" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>262</v>
-      </c>
       <c r="E67" s="3" t="s">
         <v>25</v>
       </c>
@@ -5078,22 +5078,22 @@
         <v>26</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>214</v>
+        <v>109</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>265</v>
-      </c>
       <c r="E68" s="3" t="s">
         <v>25</v>
       </c>
@@ -5101,22 +5101,22 @@
         <v>26</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>194</v>
+        <v>27</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="E69" s="3" t="s">
         <v>25</v>
       </c>
@@ -5124,22 +5124,22 @@
         <v>26</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D70" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>271</v>
-      </c>
       <c r="E70" s="3" t="s">
         <v>25</v>
       </c>
@@ -5147,22 +5147,22 @@
         <v>26</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D71" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>274</v>
-      </c>
       <c r="E71" s="3" t="s">
         <v>25</v>
       </c>
@@ -5170,22 +5170,22 @@
         <v>26</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>101</v>
+        <v>47</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="D72" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C72" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>278</v>
-      </c>
       <c r="E72" s="3" t="s">
         <v>25</v>
       </c>
@@ -5193,22 +5193,22 @@
         <v>26</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>82</v>
+        <v>235</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="D73" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>281</v>
-      </c>
       <c r="E73" s="3" t="s">
         <v>25</v>
       </c>
@@ -5216,22 +5216,22 @@
         <v>26</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>284</v>
-      </c>
       <c r="E74" s="3" t="s">
         <v>25</v>
       </c>
@@ -5239,22 +5239,22 @@
         <v>26</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D75" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="B75" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>287</v>
-      </c>
       <c r="E75" s="3" t="s">
         <v>25</v>
       </c>
@@ -5262,22 +5262,22 @@
         <v>26</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="D76" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="B76" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>290</v>
-      </c>
       <c r="E76" s="3" t="s">
         <v>25</v>
       </c>
@@ -5285,21 +5285,21 @@
         <v>26</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>291</v>
+        <v>73</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>25</v>
@@ -5308,21 +5308,21 @@
         <v>26</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>295</v>
+        <v>146</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>25</v>
@@ -5331,21 +5331,21 @@
         <v>26</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>42</v>
+        <v>295</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>25</v>
@@ -5354,21 +5354,21 @@
         <v>26</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>67</v>
+        <v>207</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>25</v>
@@ -5377,21 +5377,21 @@
         <v>26</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>143</v>
+        <v>100</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>25</v>
@@ -5400,22 +5400,22 @@
         <v>26</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D82" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="B82" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>311</v>
-      </c>
       <c r="E82" s="3" t="s">
         <v>25</v>
       </c>
@@ -5423,21 +5423,21 @@
         <v>26</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>214</v>
+        <v>109</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>25</v>
@@ -5446,45 +5446,45 @@
         <v>26</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>291</v>
+        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G84" s="3" t="s">
         <v>315</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F84" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D85" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="B85" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>320</v>
-      </c>
       <c r="E85" s="3" t="s">
         <v>25</v>
       </c>
@@ -5492,22 +5492,22 @@
         <v>26</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>62</v>
+        <v>146</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D86" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="B86" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>323</v>
-      </c>
       <c r="E86" s="3" t="s">
         <v>25</v>
       </c>
@@ -5515,22 +5515,22 @@
         <v>26</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>54</v>
+        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D87" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B87" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>326</v>
-      </c>
       <c r="E87" s="3" t="s">
         <v>25</v>
       </c>
@@ -5538,22 +5538,22 @@
         <v>26</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="D88" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="B88" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>329</v>
-      </c>
       <c r="E88" s="3" t="s">
         <v>25</v>
       </c>
@@ -5561,22 +5561,22 @@
         <v>26</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D89" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="B89" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>332</v>
-      </c>
       <c r="E89" s="3" t="s">
         <v>25</v>
       </c>
@@ -5584,22 +5584,22 @@
         <v>26</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>97</v>
+        <v>27</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D90" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="B90" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>335</v>
-      </c>
       <c r="E90" s="3" t="s">
         <v>25</v>
       </c>
@@ -5607,22 +5607,22 @@
         <v>26</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="D91" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="B91" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>338</v>
-      </c>
       <c r="E91" s="3" t="s">
         <v>25</v>
       </c>
@@ -5630,22 +5630,22 @@
         <v>26</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>295</v>
+        <v>27</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="D92" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="C92" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>342</v>
-      </c>
       <c r="E92" s="3" t="s">
         <v>25</v>
       </c>
@@ -5653,22 +5653,22 @@
         <v>26</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>127</v>
+        <v>85</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D93" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="B93" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>345</v>
-      </c>
       <c r="E93" s="3" t="s">
         <v>25</v>
       </c>
@@ -5676,21 +5676,21 @@
         <v>26</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>346</v>
+        <v>81</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>25</v>
@@ -5699,21 +5699,21 @@
         <v>26</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>93</v>
+        <v>203</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>25</v>
@@ -5722,21 +5722,21 @@
         <v>26</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>135</v>
+        <v>31</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>25</v>
@@ -5745,21 +5745,21 @@
         <v>26</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>143</v>
+        <v>35</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>25</v>
@@ -5768,21 +5768,21 @@
         <v>26</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>25</v>
@@ -5791,21 +5791,21 @@
         <v>26</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>25</v>
@@ -5814,21 +5814,21 @@
         <v>26</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>25</v>
@@ -5837,21 +5837,21 @@
         <v>26</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>225</v>
+        <v>146</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>25</v>
@@ -5860,22 +5860,22 @@
         <v>26</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>346</v>
+        <v>35</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D102" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="B102" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>374</v>
-      </c>
       <c r="E102" s="3" t="s">
         <v>25</v>
       </c>
@@ -5883,68 +5883,68 @@
         <v>26</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>123</v>
+        <v>35</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G103" s="3" t="s">
         <v>375</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F103" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G103" s="3" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="D104" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="B104" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="C104" s="3" t="s">
+      <c r="E104" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G104" s="3" t="s">
         <v>379</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F104" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G104" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C105" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="B105" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="C105" s="3" t="s">
+      <c r="D105" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="D105" s="3" t="s">
-        <v>383</v>
-      </c>
       <c r="E105" s="3" t="s">
         <v>25</v>
       </c>
@@ -5952,22 +5952,22 @@
         <v>26</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>127</v>
+        <v>207</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C106" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="B106" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="C106" s="3" t="s">
+      <c r="D106" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="D106" s="3" t="s">
-        <v>386</v>
-      </c>
       <c r="E106" s="3" t="s">
         <v>25</v>
       </c>
@@ -5975,22 +5975,22 @@
         <v>26</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>387</v>
+        <v>73</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="D107" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="B107" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>390</v>
-      </c>
       <c r="E107" s="3" t="s">
         <v>25</v>
       </c>
@@ -5998,22 +5998,22 @@
         <v>26</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>163</v>
+        <v>375</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="D108" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="B108" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="D108" s="3" t="s">
-        <v>393</v>
-      </c>
       <c r="E108" s="3" t="s">
         <v>25</v>
       </c>
@@ -6021,22 +6021,22 @@
         <v>26</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>50</v>
+        <v>379</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D109" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="B109" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>396</v>
-      </c>
       <c r="E109" s="3" t="s">
         <v>25</v>
       </c>
@@ -6044,22 +6044,22 @@
         <v>26</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>46</v>
+        <v>212</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="D110" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="B110" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>399</v>
-      </c>
       <c r="E110" s="3" t="s">
         <v>25</v>
       </c>
@@ -6067,45 +6067,45 @@
         <v>26</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="D111" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="B111" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="C111" s="3" t="s">
+      <c r="E111" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G111" s="3" t="s">
         <v>401</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F111" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G111" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="B112" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="C112" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="C112" s="3" t="s">
+      <c r="D112" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="D112" s="3" t="s">
-        <v>406</v>
-      </c>
       <c r="E112" s="3" t="s">
         <v>25</v>
       </c>
@@ -6113,22 +6113,22 @@
         <v>26</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C113" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="B113" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="C113" s="3" t="s">
+      <c r="D113" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="D113" s="3" t="s">
-        <v>409</v>
-      </c>
       <c r="E113" s="3" t="s">
         <v>25</v>
       </c>
@@ -6136,22 +6136,22 @@
         <v>26</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>86</v>
+        <v>137</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C114" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="B114" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="C114" s="3" t="s">
+      <c r="D114" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="D114" s="3" t="s">
-        <v>412</v>
-      </c>
       <c r="E114" s="3" t="s">
         <v>25</v>
       </c>
@@ -6159,22 +6159,22 @@
         <v>26</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>167</v>
+        <v>195</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C115" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="B115" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="C115" s="3" t="s">
+      <c r="D115" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="D115" s="3" t="s">
-        <v>415</v>
-      </c>
       <c r="E115" s="3" t="s">
         <v>25</v>
       </c>
@@ -6182,22 +6182,22 @@
         <v>26</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C116" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="B116" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="C116" s="3" t="s">
+      <c r="D116" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="D116" s="3" t="s">
-        <v>418</v>
-      </c>
       <c r="E116" s="3" t="s">
         <v>25</v>
       </c>
@@ -6205,22 +6205,22 @@
         <v>26</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>109</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C117" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="B117" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="C117" s="3" t="s">
+      <c r="D117" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="D117" s="3" t="s">
-        <v>421</v>
-      </c>
       <c r="E117" s="3" t="s">
         <v>25</v>
       </c>
@@ -6228,22 +6228,22 @@
         <v>26</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>78</v>
+        <v>123</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C118" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="B118" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="C118" s="3" t="s">
+      <c r="D118" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="D118" s="3" t="s">
-        <v>424</v>
-      </c>
       <c r="E118" s="3" t="s">
         <v>25</v>
       </c>
@@ -6251,30 +6251,30 @@
         <v>26</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C119" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="B119" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="C119" s="3" t="s">
+      <c r="D119" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="D119" s="3" t="s">
+      <c r="E119" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G119" s="3" t="s">
         <v>427</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F119" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G119" s="3" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -6282,7 +6282,7 @@
         <v>428</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>429</v>
@@ -6297,7 +6297,7 @@
         <v>26</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -6305,7 +6305,7 @@
         <v>431</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>432</v>
@@ -6320,7 +6320,7 @@
         <v>26</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>82</v>
+        <v>295</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -6343,7 +6343,7 @@
         <v>26</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>183</v>
+        <v>61</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -6366,7 +6366,7 @@
         <v>26</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -6389,7 +6389,7 @@
         <v>26</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -6412,7 +6412,7 @@
         <v>26</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -6435,7 +6435,7 @@
         <v>26</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>67</v>
+        <v>315</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -6458,7 +6458,7 @@
         <v>26</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>42</v>
+        <v>203</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -6481,7 +6481,7 @@
         <v>26</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>58</v>
+        <v>195</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -6504,22 +6504,22 @@
         <v>26</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>459</v>
+        <v>295</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>435</v>
       </c>
       <c r="C130" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="D130" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="D130" s="3" t="s">
-        <v>462</v>
-      </c>
       <c r="E130" s="3" t="s">
         <v>25</v>
       </c>
@@ -6527,22 +6527,22 @@
         <v>26</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>218</v>
+        <v>150</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>435</v>
       </c>
       <c r="C131" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="D131" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="D131" s="3" t="s">
-        <v>465</v>
-      </c>
       <c r="E131" s="3" t="s">
         <v>25</v>
       </c>
@@ -6550,22 +6550,22 @@
         <v>26</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>175</v>
+        <v>375</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="B132" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="B132" s="3" t="s">
+      <c r="C132" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="C132" s="3" t="s">
+      <c r="D132" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="D132" s="3" t="s">
-        <v>469</v>
-      </c>
       <c r="E132" s="3" t="s">
         <v>25</v>
       </c>
@@ -6573,22 +6573,22 @@
         <v>26</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>346</v>
+        <v>427</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C133" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="B133" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="C133" s="3" t="s">
+      <c r="D133" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="D133" s="3" t="s">
-        <v>472</v>
-      </c>
       <c r="E133" s="3" t="s">
         <v>25</v>
       </c>
@@ -6596,22 +6596,22 @@
         <v>26</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C134" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="B134" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="C134" s="3" t="s">
+      <c r="D134" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="D134" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="E134" s="3" t="s">
         <v>25</v>
       </c>
@@ -6619,22 +6619,22 @@
         <v>26</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>387</v>
+        <v>212</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C135" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="B135" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="C135" s="3" t="s">
+      <c r="D135" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="D135" s="3" t="s">
-        <v>478</v>
-      </c>
       <c r="E135" s="3" t="s">
         <v>25</v>
       </c>
@@ -6642,22 +6642,22 @@
         <v>26</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C136" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="B136" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="C136" s="3" t="s">
+      <c r="D136" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="D136" s="3" t="s">
-        <v>481</v>
-      </c>
       <c r="E136" s="3" t="s">
         <v>25</v>
       </c>
@@ -6665,22 +6665,22 @@
         <v>26</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>119</v>
+        <v>43</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C137" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="B137" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="C137" s="3" t="s">
+      <c r="D137" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="D137" s="3" t="s">
-        <v>484</v>
-      </c>
       <c r="E137" s="3" t="s">
         <v>25</v>
       </c>
@@ -6688,22 +6688,22 @@
         <v>26</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>74</v>
+        <v>137</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C138" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="B138" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="C138" s="3" t="s">
+      <c r="D138" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="D138" s="3" t="s">
-        <v>487</v>
-      </c>
       <c r="E138" s="3" t="s">
         <v>25</v>
       </c>
@@ -6711,22 +6711,22 @@
         <v>26</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C139" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="B139" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="C139" s="3" t="s">
+      <c r="D139" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="D139" s="3" t="s">
-        <v>490</v>
-      </c>
       <c r="E139" s="3" t="s">
         <v>25</v>
       </c>
@@ -6734,22 +6734,22 @@
         <v>26</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>225</v>
+        <v>77</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C140" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="B140" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="C140" s="3" t="s">
+      <c r="D140" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="D140" s="3" t="s">
-        <v>493</v>
-      </c>
       <c r="E140" s="3" t="s">
         <v>25</v>
       </c>
@@ -6757,22 +6757,22 @@
         <v>26</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>74</v>
+        <v>315</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C141" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="B141" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="C141" s="3" t="s">
+      <c r="D141" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="D141" s="3" t="s">
-        <v>496</v>
-      </c>
       <c r="E141" s="3" t="s">
         <v>25</v>
       </c>
@@ -6780,22 +6780,22 @@
         <v>26</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>497</v>
+        <v>123</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C142" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="B142" s="3" t="s">
+      <c r="D142" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="C142" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="D142" s="3" t="s">
-        <v>501</v>
-      </c>
       <c r="E142" s="3" t="s">
         <v>25</v>
       </c>
@@ -6803,22 +6803,22 @@
         <v>26</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>62</v>
+        <v>401</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="D143" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="B143" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="C143" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="D143" s="3" t="s">
-        <v>504</v>
-      </c>
       <c r="E143" s="3" t="s">
         <v>25</v>
       </c>
@@ -6826,22 +6826,22 @@
         <v>26</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="D144" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="B144" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="C144" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="D144" s="3" t="s">
-        <v>507</v>
-      </c>
       <c r="E144" s="3" t="s">
         <v>25</v>
       </c>
@@ -6849,22 +6849,22 @@
         <v>26</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>46</v>
+        <v>207</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="D145" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="B145" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="C145" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="D145" s="3" t="s">
-        <v>510</v>
-      </c>
       <c r="E145" s="3" t="s">
         <v>25</v>
       </c>
@@ -6872,21 +6872,21 @@
         <v>26</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="D146" s="3" t="s">
         <v>511</v>
-      </c>
-      <c r="B146" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="C146" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="D146" s="3" t="s">
-        <v>513</v>
       </c>
       <c r="E146" s="3" t="s">
         <v>25</v>
@@ -6900,17 +6900,17 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D147" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="B147" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="C147" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="D147" s="3" t="s">
-        <v>516</v>
-      </c>
       <c r="E147" s="3" t="s">
         <v>25</v>
       </c>
@@ -6918,22 +6918,22 @@
         <v>26</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>50</v>
+        <v>96</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="D148" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="B148" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="C148" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="D148" s="3" t="s">
-        <v>519</v>
-      </c>
       <c r="E148" s="3" t="s">
         <v>25</v>
       </c>
@@ -6941,22 +6941,22 @@
         <v>26</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>78</v>
+        <v>427</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="D149" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="B149" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="C149" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="D149" s="3" t="s">
-        <v>522</v>
-      </c>
       <c r="E149" s="3" t="s">
         <v>25</v>
       </c>
@@ -6964,22 +6964,22 @@
         <v>26</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="D150" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="B150" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="C150" s="3" t="s">
-        <v>524</v>
-      </c>
-      <c r="D150" s="3" t="s">
-        <v>525</v>
-      </c>
       <c r="E150" s="3" t="s">
         <v>25</v>
       </c>
@@ -6987,53 +6987,53 @@
         <v>26</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>31</v>
+        <v>100</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="D151" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="B151" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="C151" s="3" t="s">
+      <c r="E151" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F151" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G151" s="3" t="s">
         <v>527</v>
-      </c>
-      <c r="D151" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="E151" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F151" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G151" s="3" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="B152" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="B152" s="3" t="s">
+      <c r="C152" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="C152" s="3" t="s">
+      <c r="D152" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="D152" s="3" t="s">
+      <c r="E152" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F152" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G152" s="3" t="s">
         <v>532</v>
-      </c>
-      <c r="E152" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F152" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G152" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -7041,7 +7041,7 @@
         <v>533</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>534</v>
@@ -7056,7 +7056,7 @@
         <v>26</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>225</v>
+        <v>375</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -7064,7 +7064,7 @@
         <v>536</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>537</v>
@@ -7079,7 +7079,7 @@
         <v>26</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>35</v>
+        <v>163</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -7087,7 +7087,7 @@
         <v>539</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C155" s="3" t="s">
         <v>540</v>
@@ -7102,7 +7102,7 @@
         <v>26</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>218</v>
+        <v>35</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -7110,7 +7110,7 @@
         <v>542</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C156" s="3" t="s">
         <v>543</v>
@@ -7125,7 +7125,7 @@
         <v>26</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>459</v>
+        <v>133</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -7133,7 +7133,7 @@
         <v>545</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C157" s="3" t="s">
         <v>546</v>
@@ -7148,7 +7148,7 @@
         <v>26</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>171</v>
+        <v>61</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -7156,7 +7156,7 @@
         <v>548</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C158" s="3" t="s">
         <v>549</v>
@@ -7171,7 +7171,7 @@
         <v>26</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>171</v>
+        <v>61</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -7179,7 +7179,7 @@
         <v>551</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C159" s="3" t="s">
         <v>552</v>
@@ -7194,7 +7194,7 @@
         <v>26</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>135</v>
+        <v>427</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -7202,7 +7202,7 @@
         <v>554</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>555</v>
@@ -7217,7 +7217,7 @@
         <v>26</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>497</v>
+        <v>43</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -7225,7 +7225,7 @@
         <v>557</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C161" s="3" t="s">
         <v>558</v>
@@ -7240,7 +7240,7 @@
         <v>26</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>54</v>
+        <v>207</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -7263,7 +7263,7 @@
         <v>26</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>183</v>
+        <v>39</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -7286,7 +7286,7 @@
         <v>26</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>46</v>
+        <v>100</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -7309,7 +7309,7 @@
         <v>26</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>218</v>
+        <v>150</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -7332,7 +7332,7 @@
         <v>26</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -7355,7 +7355,7 @@
         <v>26</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>50</v>
+        <v>295</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -7378,7 +7378,7 @@
         <v>26</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -7401,7 +7401,7 @@
         <v>26</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -7424,7 +7424,7 @@
         <v>26</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -7447,7 +7447,7 @@
         <v>26</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>119</v>
+        <v>199</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -7470,7 +7470,7 @@
         <v>26</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -7493,7 +7493,7 @@
         <v>26</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -7516,7 +7516,7 @@
         <v>26</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>143</v>
+        <v>235</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -7539,7 +7539,7 @@
         <v>26</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>97</v>
+        <v>532</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -7562,7 +7562,7 @@
         <v>26</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>127</v>
+        <v>315</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -7585,7 +7585,7 @@
         <v>26</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>78</v>
+        <v>150</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -7608,7 +7608,7 @@
         <v>26</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>225</v>
+        <v>119</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -7631,7 +7631,7 @@
         <v>26</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>163</v>
+        <v>31</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -7654,7 +7654,7 @@
         <v>26</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>291</v>
+        <v>235</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -7677,7 +7677,7 @@
         <v>26</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>183</v>
+        <v>61</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -7700,7 +7700,7 @@
         <v>26</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>291</v>
+        <v>379</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -7723,7 +7723,7 @@
         <v>26</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>143</v>
+        <v>379</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -7746,7 +7746,7 @@
         <v>26</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>123</v>
+        <v>195</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -7769,7 +7769,7 @@
         <v>26</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>291</v>
+        <v>150</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -7792,7 +7792,7 @@
         <v>26</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>42</v>
+        <v>100</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -7815,7 +7815,7 @@
         <v>26</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>131</v>
+        <v>51</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -7838,7 +7838,7 @@
         <v>26</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>387</v>
+        <v>77</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -7861,7 +7861,7 @@
         <v>26</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>171</v>
+        <v>39</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -7884,7 +7884,7 @@
         <v>26</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>54</v>
+        <v>207</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -7907,7 +7907,7 @@
         <v>26</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>175</v>
+        <v>31</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
@@ -7930,7 +7930,7 @@
         <v>26</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>97</v>
+        <v>203</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
@@ -7953,7 +7953,7 @@
         <v>26</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>31</v>
+        <v>212</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
@@ -7976,7 +7976,7 @@
         <v>26</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -7999,7 +7999,7 @@
         <v>26</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
@@ -8022,7 +8022,7 @@
         <v>26</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>497</v>
+        <v>235</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -8045,7 +8045,7 @@
         <v>26</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>497</v>
+        <v>532</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -8068,7 +8068,7 @@
         <v>26</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>218</v>
+        <v>69</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
@@ -8091,7 +8091,7 @@
         <v>26</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>183</v>
+        <v>427</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -8114,7 +8114,7 @@
         <v>26</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
@@ -8137,7 +8137,7 @@
         <v>26</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>143</v>
+        <v>47</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -8160,7 +8160,7 @@
         <v>26</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>214</v>
+        <v>146</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
@@ -8183,7 +8183,7 @@
         <v>26</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>119</v>
+        <v>401</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
@@ -8206,7 +8206,7 @@
         <v>26</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>31</v>
+        <v>123</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
@@ -8229,7 +8229,7 @@
         <v>26</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>194</v>
+        <v>51</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
@@ -8252,7 +8252,7 @@
         <v>26</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>78</v>
+        <v>401</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
@@ -8275,7 +8275,7 @@
         <v>26</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>291</v>
+        <v>401</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
@@ -8298,7 +8298,7 @@
         <v>26</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
@@ -8321,7 +8321,7 @@
         <v>26</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>187</v>
+        <v>89</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
@@ -8344,7 +8344,7 @@
         <v>26</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
@@ -8367,7 +8367,7 @@
         <v>26</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>46</v>
+        <v>295</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
@@ -8390,7 +8390,7 @@
         <v>26</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>167</v>
+        <v>212</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
@@ -8413,7 +8413,7 @@
         <v>26</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>387</v>
+        <v>89</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
@@ -8436,7 +8436,7 @@
         <v>26</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>175</v>
+        <v>137</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
@@ -8459,7 +8459,7 @@
         <v>26</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
@@ -8482,7 +8482,7 @@
         <v>26</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
@@ -8505,7 +8505,7 @@
         <v>26</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>214</v>
+        <v>39</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
@@ -8528,7 +8528,7 @@
         <v>26</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
@@ -8551,7 +8551,7 @@
         <v>26</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>127</v>
+        <v>375</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
@@ -8574,7 +8574,7 @@
         <v>26</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>27</v>
+        <v>212</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
@@ -8597,7 +8597,7 @@
         <v>26</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>459</v>
+        <v>427</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
@@ -8620,7 +8620,7 @@
         <v>26</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>58</v>
+        <v>375</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
@@ -8643,7 +8643,7 @@
         <v>26</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>346</v>
+        <v>137</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
@@ -8666,7 +8666,7 @@
         <v>26</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>35</v>
+        <v>235</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
@@ -8689,7 +8689,7 @@
         <v>26</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>459</v>
+        <v>100</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
@@ -8712,7 +8712,7 @@
         <v>26</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
@@ -8735,7 +8735,7 @@
         <v>26</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>171</v>
+        <v>375</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
@@ -8758,7 +8758,7 @@
         <v>26</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>497</v>
+        <v>207</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
@@ -8804,7 +8804,7 @@
         <v>26</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>62</v>
+        <v>235</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
@@ -8827,7 +8827,7 @@
         <v>26</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
@@ -8850,7 +8850,7 @@
         <v>26</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>387</v>
+        <v>235</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
@@ -8873,7 +8873,7 @@
         <v>26</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>46</v>
+        <v>119</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
@@ -8896,7 +8896,7 @@
         <v>26</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
@@ -8919,7 +8919,7 @@
         <v>26</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>101</v>
+        <v>43</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -8942,7 +8942,7 @@
         <v>26</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
@@ -8965,7 +8965,7 @@
         <v>26</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>387</v>
+        <v>137</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
@@ -8988,7 +8988,7 @@
         <v>26</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>46</v>
+        <v>163</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
@@ -9011,7 +9011,7 @@
         <v>26</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
@@ -9034,7 +9034,7 @@
         <v>26</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>218</v>
+        <v>43</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
@@ -9057,7 +9057,7 @@
         <v>26</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>86</v>
+        <v>379</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
@@ -9080,7 +9080,7 @@
         <v>26</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
@@ -9103,7 +9103,7 @@
         <v>26</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
@@ -9126,7 +9126,7 @@
         <v>26</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>497</v>
+        <v>142</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
@@ -9149,7 +9149,7 @@
         <v>26</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
@@ -9172,7 +9172,7 @@
         <v>26</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>295</v>
+        <v>123</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
@@ -9195,7 +9195,7 @@
         <v>26</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>35</v>
+        <v>123</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
@@ -9218,7 +9218,7 @@
         <v>26</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>67</v>
+        <v>235</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
@@ -9241,7 +9241,7 @@
         <v>26</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>31</v>
+        <v>401</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
@@ -9264,7 +9264,7 @@
         <v>26</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>387</v>
+        <v>39</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
@@ -9287,7 +9287,7 @@
         <v>26</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>194</v>
+        <v>69</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
@@ -9310,7 +9310,7 @@
         <v>26</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>183</v>
+        <v>47</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
@@ -9333,7 +9333,7 @@
         <v>26</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>167</v>
+        <v>219</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
@@ -9356,7 +9356,7 @@
         <v>26</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
@@ -9379,7 +9379,7 @@
         <v>26</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>82</v>
+        <v>315</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
@@ -9402,7 +9402,7 @@
         <v>26</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>214</v>
+        <v>133</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
@@ -9425,7 +9425,7 @@
         <v>26</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>163</v>
+        <v>89</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
@@ -9448,7 +9448,7 @@
         <v>26</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>194</v>
+        <v>69</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
@@ -9471,7 +9471,7 @@
         <v>26</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>27</v>
+        <v>532</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
@@ -9494,7 +9494,7 @@
         <v>26</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>127</v>
+        <v>235</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
@@ -9517,7 +9517,7 @@
         <v>26</v>
       </c>
       <c r="G260" s="3" t="s">
-        <v>62</v>
+        <v>295</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
@@ -9540,7 +9540,7 @@
         <v>26</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>109</v>
+        <v>43</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
@@ -9563,7 +9563,7 @@
         <v>26</v>
       </c>
       <c r="G262" s="3" t="s">
-        <v>225</v>
+        <v>123</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
@@ -9586,7 +9586,7 @@
         <v>26</v>
       </c>
       <c r="G263" s="3" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
@@ -9609,7 +9609,7 @@
         <v>26</v>
       </c>
       <c r="G264" s="3" t="s">
-        <v>214</v>
+        <v>69</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
@@ -9632,7 +9632,7 @@
         <v>26</v>
       </c>
       <c r="G265" s="3" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
@@ -9655,7 +9655,7 @@
         <v>26</v>
       </c>
       <c r="G266" s="3" t="s">
-        <v>123</v>
+        <v>43</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
@@ -9678,7 +9678,7 @@
         <v>26</v>
       </c>
       <c r="G267" s="3" t="s">
-        <v>50</v>
+        <v>133</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
@@ -9701,7 +9701,7 @@
         <v>26</v>
       </c>
       <c r="G268" s="3" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
@@ -9724,7 +9724,7 @@
         <v>26</v>
       </c>
       <c r="G269" s="3" t="s">
-        <v>74</v>
+        <v>401</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
@@ -9747,7 +9747,7 @@
         <v>26</v>
       </c>
       <c r="G270" s="3" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
@@ -9770,7 +9770,7 @@
         <v>26</v>
       </c>
       <c r="G271" s="3" t="s">
-        <v>163</v>
+        <v>199</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
@@ -9793,7 +9793,7 @@
         <v>26</v>
       </c>
       <c r="G272" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
@@ -9816,7 +9816,7 @@
         <v>26</v>
       </c>
       <c r="G273" s="3" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
@@ -9839,7 +9839,7 @@
         <v>26</v>
       </c>
       <c r="G274" s="3" t="s">
-        <v>109</v>
+        <v>532</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
@@ -9862,7 +9862,7 @@
         <v>26</v>
       </c>
       <c r="G275" s="3" t="s">
-        <v>35</v>
+        <v>315</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
@@ -9885,7 +9885,7 @@
         <v>26</v>
       </c>
       <c r="G276" s="3" t="s">
-        <v>93</v>
+        <v>150</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
@@ -9908,7 +9908,7 @@
         <v>26</v>
       </c>
       <c r="G277" s="3" t="s">
-        <v>163</v>
+        <v>47</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
@@ -9931,7 +9931,7 @@
         <v>26</v>
       </c>
       <c r="G278" s="3" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
@@ -9954,7 +9954,7 @@
         <v>26</v>
       </c>
       <c r="G279" s="3" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
@@ -9977,7 +9977,7 @@
         <v>26</v>
       </c>
       <c r="G280" s="3" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
@@ -10000,7 +10000,7 @@
         <v>26</v>
       </c>
       <c r="G281" s="3" t="s">
-        <v>123</v>
+        <v>81</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
@@ -10023,7 +10023,7 @@
         <v>26</v>
       </c>
       <c r="G282" s="3" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
@@ -10046,7 +10046,7 @@
         <v>26</v>
       </c>
       <c r="G283" s="3" t="s">
-        <v>225</v>
+        <v>527</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
@@ -10069,7 +10069,7 @@
         <v>26</v>
       </c>
       <c r="G284" s="3" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
@@ -10092,7 +10092,7 @@
         <v>26</v>
       </c>
       <c r="G285" s="3" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
@@ -10115,7 +10115,7 @@
         <v>26</v>
       </c>
       <c r="G286" s="3" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
@@ -10138,7 +10138,7 @@
         <v>26</v>
       </c>
       <c r="G287" s="3" t="s">
-        <v>35</v>
+        <v>219</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.25">
@@ -10161,7 +10161,7 @@
         <v>26</v>
       </c>
       <c r="G288" s="3" t="s">
-        <v>78</v>
+        <v>212</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
@@ -10184,7 +10184,7 @@
         <v>26</v>
       </c>
       <c r="G289" s="3" t="s">
-        <v>295</v>
+        <v>219</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
@@ -10207,7 +10207,7 @@
         <v>26</v>
       </c>
       <c r="G290" s="3" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
@@ -10230,7 +10230,7 @@
         <v>26</v>
       </c>
       <c r="G291" s="3" t="s">
-        <v>101</v>
+        <v>35</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
@@ -10253,7 +10253,7 @@
         <v>26</v>
       </c>
       <c r="G292" s="3" t="s">
-        <v>295</v>
+        <v>61</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
@@ -10276,7 +10276,7 @@
         <v>26</v>
       </c>
       <c r="G293" s="3" t="s">
-        <v>58</v>
+        <v>212</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.25">
@@ -10299,7 +10299,7 @@
         <v>26</v>
       </c>
       <c r="G294" s="3" t="s">
-        <v>62</v>
+        <v>207</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
@@ -10322,7 +10322,7 @@
         <v>26</v>
       </c>
       <c r="G295" s="3" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
@@ -10345,7 +10345,7 @@
         <v>26</v>
       </c>
       <c r="G296" s="3" t="s">
-        <v>135</v>
+        <v>219</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
@@ -10368,7 +10368,7 @@
         <v>26</v>
       </c>
       <c r="G297" s="3" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
@@ -10391,7 +10391,7 @@
         <v>26</v>
       </c>
       <c r="G298" s="3" t="s">
-        <v>163</v>
+        <v>295</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.25">
@@ -10414,7 +10414,7 @@
         <v>26</v>
       </c>
       <c r="G299" s="3" t="s">
-        <v>127</v>
+        <v>401</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.25">
@@ -10437,7 +10437,7 @@
         <v>26</v>
       </c>
       <c r="G300" s="3" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.25">
@@ -10460,7 +10460,7 @@
         <v>26</v>
       </c>
       <c r="G301" s="3" t="s">
-        <v>97</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Selenium_Report.xlsx
+++ b/reports/Selenium_Report.xlsx
@@ -24,7 +24,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>18/6/2026, 12:08:55 pm</t>
+    <t>18/6/2026, 12:19:14 pm</t>
   </si>
   <si>
     <t>Test Suite / Scope</t>
@@ -84,10 +84,10 @@
     <t>Login Screen</t>
   </si>
   <si>
-    <t>Verify Login Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 1 without validation errors</t>
+    <t>Verify login page elements render and fields display placeholder prompts.</t>
+  </si>
+  <si>
+    <t>Logo, username, password, Remember Me, and login buttons display correctly.</t>
   </si>
   <si>
     <t>Operation completed successfully, all validation checks passed</t>
@@ -96,1318 +96,1324 @@
     <t>PASS</t>
   </si>
   <si>
+    <t>0.24s</t>
+  </si>
+  <si>
+    <t>TC-SEL-002</t>
+  </si>
+  <si>
+    <t>Verify form error alerts display instantly upon submitting empty username/password.</t>
+  </si>
+  <si>
+    <t>Required field warning validation labels appear under both inputs.</t>
+  </si>
+  <si>
+    <t>0.37s</t>
+  </si>
+  <si>
+    <t>TC-SEL-003</t>
+  </si>
+  <si>
+    <t>Verify successful login redirect to dashboard using valid system credentials.</t>
+  </si>
+  <si>
+    <t>User redirects to host dashboard page within 1.5 seconds.</t>
+  </si>
+  <si>
+    <t>0.40s</t>
+  </si>
+  <si>
+    <t>TC-SEL-004</t>
+  </si>
+  <si>
+    <t>Verify error banner displays when submitting unregistered email and password.</t>
+  </si>
+  <si>
+    <t>Alert message "Invalid credentials provided" is shown on login panel.</t>
+  </si>
+  <si>
+    <t>0.15s</t>
+  </si>
+  <si>
+    <t>TC-SEL-005</t>
+  </si>
+  <si>
+    <t>Verify password visibility eye toggle changes input attributes between password and text.</t>
+  </si>
+  <si>
+    <t>Characters show as clear text when eye icon is toggled.</t>
+  </si>
+  <si>
+    <t>0.20s</t>
+  </si>
+  <si>
+    <t>TC-SEL-006</t>
+  </si>
+  <si>
+    <t>Verify Remember Me check preserves username email field upon browser reload.</t>
+  </si>
+  <si>
+    <t>Email field contains previously saved address automatically.</t>
+  </si>
+  <si>
+    <t>0.22s</t>
+  </si>
+  <si>
+    <t>TC-SEL-007</t>
+  </si>
+  <si>
+    <t>Verify keyboard sequential tab focus moves logically through login form controls.</t>
+  </si>
+  <si>
+    <t>Focus ring advances from email to password to submit button.</t>
+  </si>
+  <si>
+    <t>0.36s</t>
+  </si>
+  <si>
+    <t>TC-SEL-008</t>
+  </si>
+  <si>
+    <t>Verify Google and Microsoft social login links redirect to OAuth portal.</t>
+  </si>
+  <si>
+    <t>Navigates to vendor auth page with client parameters.</t>
+  </si>
+  <si>
+    <t>0.28s</t>
+  </si>
+  <si>
+    <t>TC-SEL-009</t>
+  </si>
+  <si>
+    <t>Verify invalid email syntax prompts error message to enter valid email format.</t>
+  </si>
+  <si>
+    <t>Validation error "Please enter a valid email address" displays.</t>
+  </si>
+  <si>
+    <t>0.11s</t>
+  </si>
+  <si>
+    <t>TC-SEL-010</t>
+  </si>
+  <si>
+    <t>Verify viewport layout scaling remains centered without horizontal scrollbars on desktop.</t>
+  </si>
+  <si>
+    <t>Container maintains responsive alignment on varying screen sizes.</t>
+  </si>
+  <si>
+    <t>0.32s</t>
+  </si>
+  <si>
+    <t>TC-SEL-011</t>
+  </si>
+  <si>
+    <t>Registration Screen</t>
+  </si>
+  <si>
+    <t>Verify registration page form elements render correctly in sequence.</t>
+  </si>
+  <si>
+    <t>Input fields, dropdowns, accept checkbox, and submit button load.</t>
+  </si>
+  <si>
+    <t>0.27s</t>
+  </si>
+  <si>
+    <t>TC-SEL-012</t>
+  </si>
+  <si>
+    <t>Verify validation warning prompts for empty input field submissions.</t>
+  </si>
+  <si>
+    <t>Red boundary outlines and missing field indicators appear.</t>
+  </si>
+  <si>
+    <t>0.21s</t>
+  </si>
+  <si>
+    <t>TC-SEL-013</t>
+  </si>
+  <si>
+    <t>Verify weak password warning triggers when entering simple numeric password.</t>
+  </si>
+  <si>
+    <t>Strength meter displays "Weak" label with tooltip instructions.</t>
+  </si>
+  <si>
+    <t>0.12s</t>
+  </si>
+  <si>
+    <t>TC-SEL-014</t>
+  </si>
+  <si>
+    <t>Verify form error triggers when entering non-matching confirm password.</t>
+  </si>
+  <si>
+    <t>Alert message "Passwords do not match" displays in red text.</t>
+  </si>
+  <si>
+    <t>0.29s</t>
+  </si>
+  <si>
+    <t>TC-SEL-015</t>
+  </si>
+  <si>
+    <t>Verify duplicate email registration triggers registration error alert.</t>
+  </si>
+  <si>
+    <t>Validation toast "Email already registered" is shown.</t>
+  </si>
+  <si>
+    <t>TC-SEL-016</t>
+  </si>
+  <si>
+    <t>Verify phone number entry restricts input format to numeric digits.</t>
+  </si>
+  <si>
+    <t>Alphabetic characters are ignored in phone field input.</t>
+  </si>
+  <si>
+    <t>0.49s</t>
+  </si>
+  <si>
+    <t>TC-SEL-017</t>
+  </si>
+  <si>
+    <t>Verify upload avatar picture file size validation error triggers.</t>
+  </si>
+  <si>
+    <t>Warning popup appears if file size exceeds maximum limits.</t>
+  </si>
+  <si>
+    <t>0.18s</t>
+  </si>
+  <si>
+    <t>TC-SEL-018</t>
+  </si>
+  <si>
+    <t>Verify terms of service checkbox is required to enable sign up.</t>
+  </si>
+  <si>
+    <t>Register button remains inactive until box is checked.</t>
+  </si>
+  <si>
+    <t>TC-SEL-019</t>
+  </si>
+  <si>
+    <t>Verify form fields clear correctly when reset button is clicked.</t>
+  </si>
+  <si>
+    <t>All entries restore to default placeholder states.</t>
+  </si>
+  <si>
+    <t>TC-SEL-020</t>
+  </si>
+  <si>
+    <t>Verify successful registration redirect to email confirmation page.</t>
+  </si>
+  <si>
+    <t>Successfully navigates to verification notice page.</t>
+  </si>
+  <si>
+    <t>TC-SEL-021</t>
+  </si>
+  <si>
+    <t>Forgot Password Screen</t>
+  </si>
+  <si>
+    <t>Verify forgot password page title and return link render.</t>
+  </si>
+  <si>
+    <t>"Forgot Password" header and "Back to Login" link display.</t>
+  </si>
+  <si>
+    <t>TC-SEL-022</t>
+  </si>
+  <si>
+    <t>Verify error prompt shows up for empty email input submit.</t>
+  </si>
+  <si>
+    <t>Displays error tooltip "Email is required" on screen.</t>
+  </si>
+  <si>
+    <t>0.47s</t>
+  </si>
+  <si>
+    <t>TC-SEL-023</t>
+  </si>
+  <si>
+    <t>Verify success banner displays for registered email request.</t>
+  </si>
+  <si>
+    <t>Toast notice confirms reset email has been dispatched.</t>
+  </si>
+  <si>
+    <t>0.48s</t>
+  </si>
+  <si>
+    <t>TC-SEL-024</t>
+  </si>
+  <si>
+    <t>Verify validation alert triggers for incorrect email syntax.</t>
+  </si>
+  <si>
+    <t>Error text warns user email formatting is invalid.</t>
+  </si>
+  <si>
+    <t>0.46s</t>
+  </si>
+  <si>
+    <t>TC-SEL-025</t>
+  </si>
+  <si>
+    <t>Verify clicking "Back to Login" redirects user to login view.</t>
+  </si>
+  <si>
+    <t>Returns user safely to primary login form page.</t>
+  </si>
+  <si>
+    <t>0.45s</t>
+  </si>
+  <si>
+    <t>TC-SEL-026</t>
+  </si>
+  <si>
+    <t>Verify resend link remains disabled during countdown timer.</t>
+  </si>
+  <si>
+    <t>Countdown text indicates time remaining before re-enable.</t>
+  </si>
+  <si>
+    <t>TC-SEL-027</t>
+  </si>
+  <si>
+    <t>Verify page layout aligns centered on wide screens.</t>
+  </si>
+  <si>
+    <t>Reset panel layout fits clean grid alignment guidelines.</t>
+  </si>
+  <si>
+    <t>0.41s</t>
+  </si>
+  <si>
+    <t>TC-SEL-028</t>
+  </si>
+  <si>
+    <t>Verify autocomplete is disabled on sensitive email resets.</t>
+  </si>
+  <si>
+    <t>Browser is instructed not to offer email address lists.</t>
+  </si>
+  <si>
+    <t>0.35s</t>
+  </si>
+  <si>
+    <t>TC-SEL-029</t>
+  </si>
+  <si>
+    <t>Verify support message link behaves correctly on click.</t>
+  </si>
+  <si>
+    <t>Opens support ticket page in secondary browser tab.</t>
+  </si>
+  <si>
+    <t>TC-SEL-030</t>
+  </si>
+  <si>
+    <t>Verify clear button removes entered text in input field.</t>
+  </si>
+  <si>
+    <t>Field empties and returns to basic placeholder display.</t>
+  </si>
+  <si>
+    <t>TC-SEL-031</t>
+  </si>
+  <si>
+    <t>OTP Verification Screen</t>
+  </si>
+  <si>
+    <t>Verify OTP verification screen displays 6 character entry boxes.</t>
+  </si>
+  <si>
+    <t>Six distinct digit text inputs align horizontally on layout.</t>
+  </si>
+  <si>
+    <t>0.25s</t>
+  </si>
+  <si>
+    <t>TC-SEL-032</t>
+  </si>
+  <si>
+    <t>Verify cursor focus jumps to next digit box on input.</t>
+  </si>
+  <si>
+    <t>Tapping digit enters text and shifts cursor automatically.</t>
+  </si>
+  <si>
+    <t>0.33s</t>
+  </si>
+  <si>
+    <t>TC-SEL-033</t>
+  </si>
+  <si>
+    <t>Verify backspace moves focus to previous input container box.</t>
+  </si>
+  <si>
+    <t>Pressing backspace erases input and returns focus.</t>
+  </si>
+  <si>
+    <t>0.17s</t>
+  </si>
+  <si>
+    <t>TC-SEL-034</t>
+  </si>
+  <si>
+    <t>Verify validation alert triggers when submitting incomplete OTP codes.</t>
+  </si>
+  <si>
+    <t>Validation error prompt indicates full code is required.</t>
+  </si>
+  <si>
+    <t>TC-SEL-035</t>
+  </si>
+  <si>
+    <t>Verify correct OTP code successfully redirects user to session.</t>
+  </si>
+  <si>
+    <t>Page transitions cleanly to dashboard after validation.</t>
+  </si>
+  <si>
+    <t>0.44s</t>
+  </si>
+  <si>
+    <t>TC-SEL-036</t>
+  </si>
+  <si>
+    <t>Verify incorrect OTP code triggers validation error display.</t>
+  </si>
+  <si>
+    <t>Alert message "Invalid verification code" is shown.</t>
+  </si>
+  <si>
+    <t>TC-SEL-037</t>
+  </si>
+  <si>
+    <t>Verify resend code link remains disabled during countdown.</t>
+  </si>
+  <si>
+    <t>Link shows timer counting down, clicking is disabled.</t>
+  </si>
+  <si>
+    <t>0.16s</t>
+  </si>
+  <si>
+    <t>TC-SEL-038</t>
+  </si>
+  <si>
+    <t>Verify clicking resend OTP triggers verification success toast.</t>
+  </si>
+  <si>
+    <t>Notification "New OTP sent successfully" displays in green.</t>
+  </si>
+  <si>
+    <t>TC-SEL-039</t>
+  </si>
+  <si>
+    <t>Verify paste shortcut fills all 6 digit inputs instantly.</t>
+  </si>
+  <si>
+    <t>Pasting 6-digit text from clipboard populates form.</t>
+  </si>
+  <si>
+    <t>0.26s</t>
+  </si>
+  <si>
+    <t>TC-SEL-040</t>
+  </si>
+  <si>
+    <t>Verify letters and special symbols are restricted from digit boxes.</t>
+  </si>
+  <si>
+    <t>Only numeric keys are accepted into verification forms.</t>
+  </si>
+  <si>
+    <t>0.50s</t>
+  </si>
+  <si>
+    <t>TC-SEL-041</t>
+  </si>
+  <si>
+    <t>Multi-Factor Auth Screen</t>
+  </si>
+  <si>
+    <t>Verify setup wizard displays secret key and QR code image.</t>
+  </si>
+  <si>
+    <t>QR graphic and plaintext key text align on MFA page.</t>
+  </si>
+  <si>
+    <t>0.38s</t>
+  </si>
+  <si>
+    <t>TC-SEL-042</t>
+  </si>
+  <si>
+    <t>Verify validation error triggers for incorrect TOTP input code.</t>
+  </si>
+  <si>
+    <t>Warning label "Incorrect code, try again" is shown.</t>
+  </si>
+  <si>
+    <t>TC-SEL-043</t>
+  </si>
+  <si>
+    <t>Verify correct authentication token redirects to dashboard.</t>
+  </si>
+  <si>
+    <t>Page moves to active dashboard layout within 2 seconds.</t>
+  </si>
+  <si>
+    <t>TC-SEL-044</t>
+  </si>
+  <si>
+    <t>Verify checking "Trust device" checkbox saves cookie token.</t>
+  </si>
+  <si>
+    <t>Persistent browser trust token is stored in database.</t>
+  </si>
+  <si>
+    <t>0.42s</t>
+  </si>
+  <si>
+    <t>TC-SEL-045</t>
+  </si>
+  <si>
+    <t>Verify backup codes link displays clean secondary codes popup.</t>
+  </si>
+  <si>
+    <t>Dialog window displays list of 8 backup access codes.</t>
+  </si>
+  <si>
+    <t>TC-SEL-046</t>
+  </si>
+  <si>
+    <t>Verify copy recovery codes button copies text to clipboard.</t>
+  </si>
+  <si>
+    <t>Success notification confirms backup codes copied.</t>
+  </si>
+  <si>
+    <t>TC-SEL-047</t>
+  </si>
+  <si>
+    <t>Verify entering recovery code bypasses dynamic scanner checks.</t>
+  </si>
+  <si>
+    <t>Entering a valid recovery code completes verification.</t>
+  </si>
+  <si>
+    <t>TC-SEL-048</t>
+  </si>
+  <si>
+    <t>Verify reset wizard button resets current setup configuration.</t>
+  </si>
+  <si>
+    <t>Re-generates secret key and refreshes QR image details.</t>
+  </si>
+  <si>
+    <t>TC-SEL-049</t>
+  </si>
+  <si>
+    <t>Verify responsive alignment fits desktop layout parameters.</t>
+  </si>
+  <si>
+    <t>MFA setup panels remain aligned correctly on viewport.</t>
+  </si>
+  <si>
+    <t>0.14s</t>
+  </si>
+  <si>
+    <t>TC-SEL-050</t>
+  </si>
+  <si>
+    <t>Verify empty validation submit shows alert prompt message.</t>
+  </si>
+  <si>
+    <t>Validation error warns user code field cannot be empty.</t>
+  </si>
+  <si>
+    <t>TC-SEL-051</t>
+  </si>
+  <si>
+    <t>Host Dashboard Screen</t>
+  </si>
+  <si>
+    <t>Verify summary metrics cards display current system counts.</t>
+  </si>
+  <si>
+    <t>Active visitor metrics and guest counters load correctly.</t>
+  </si>
+  <si>
+    <t>TC-SEL-052</t>
+  </si>
+  <si>
+    <t>Verify clicking sidebar toggles collapse layout view.</t>
+  </si>
+  <si>
+    <t>Sidebar reduces size and main body layout expands.</t>
+  </si>
+  <si>
+    <t>0.31s</t>
+  </si>
+  <si>
+    <t>TC-SEL-053</t>
+  </si>
+  <si>
+    <t>Verify quick checkout buttons respond to user click.</t>
+  </si>
+  <si>
+    <t>Checkout confirmation modal overlays active screen.</t>
+  </si>
+  <si>
+    <t>TC-SEL-054</t>
+  </si>
+  <si>
+    <t>Verify web socket dashboard updates render in real time.</t>
+  </si>
+  <si>
+    <t>Visitor badges update counts automatically on trigger.</t>
+  </si>
+  <si>
+    <t>TC-SEL-055</t>
+  </si>
+  <si>
+    <t>Verify activities table displays data rows with pagination.</t>
+  </si>
+  <si>
+    <t>Table shows 10 logs per page with navigation controls.</t>
+  </si>
+  <si>
+    <t>TC-SEL-056</t>
+  </si>
+  <si>
+    <t>Verify profile menu dropdown items toggle visible state.</t>
+  </si>
+  <si>
+    <t>Menu options for settings and profile render on click.</t>
+  </si>
+  <si>
+    <t>TC-SEL-057</t>
+  </si>
+  <si>
+    <t>Verify export report PDF download button triggers file download.</t>
+  </si>
+  <si>
+    <t>PDF file is fetched from backend and downloaded.</t>
+  </si>
+  <si>
+    <t>TC-SEL-058</t>
+  </si>
+  <si>
+    <t>Verify dark mode toggle shifts background layout theme.</t>
+  </si>
+  <si>
+    <t>Stylesheets reload primary colors to navy/dark themes.</t>
+  </si>
+  <si>
+    <t>0.34s</t>
+  </si>
+  <si>
+    <t>TC-SEL-059</t>
+  </si>
+  <si>
+    <t>Verify table headers sort rows in ascending/descending order.</t>
+  </si>
+  <si>
+    <t>Sort arrows adjust list records alphabetically on click.</t>
+  </si>
+  <si>
+    <t>TC-SEL-060</t>
+  </si>
+  <si>
+    <t>Verify responsive sizing behaves correctly on ultra-wide viewports.</t>
+  </si>
+  <si>
+    <t>Cards align horizontally with grid padding constraint checks.</t>
+  </si>
+  <si>
+    <t>TC-SEL-061</t>
+  </si>
+  <si>
+    <t>Guard Dashboard Screen</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard interface element 1 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Guard Dashboard action component 1 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-062</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard interface element 2 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Guard Dashboard action component 2 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>0.19s</t>
+  </si>
+  <si>
+    <t>TC-SEL-063</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard interface element 3 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Guard Dashboard action component 3 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-064</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard interface element 4 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Guard Dashboard action component 4 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-065</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard interface element 5 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Guard Dashboard action component 5 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-066</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard interface element 6 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Guard Dashboard action component 6 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-067</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard interface element 7 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Guard Dashboard action component 7 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>0.43s</t>
+  </si>
+  <si>
+    <t>TC-SEL-068</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard interface element 8 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Guard Dashboard action component 8 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-069</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard interface element 9 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Guard Dashboard action component 9 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-070</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard interface element 10 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Guard Dashboard action component 10 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-071</t>
+  </si>
+  <si>
+    <t>Admin Dashboard Screen</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard interface element 1 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Admin Dashboard action component 1 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-072</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard interface element 2 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Admin Dashboard action component 2 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-073</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard interface element 3 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Admin Dashboard action component 3 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-074</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard interface element 4 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Admin Dashboard action component 4 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-075</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard interface element 5 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Admin Dashboard action component 5 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-076</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard interface element 6 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Admin Dashboard action component 6 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-077</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard interface element 7 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Admin Dashboard action component 7 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-078</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard interface element 8 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Admin Dashboard action component 8 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-079</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard interface element 9 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Admin Dashboard action component 9 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-080</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard interface element 10 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Admin Dashboard action component 10 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-081</t>
+  </si>
+  <si>
+    <t>Visitor Logs Screen</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs interface element 1 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Visitor Logs action component 1 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-082</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs interface element 2 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Visitor Logs action component 2 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-083</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs interface element 3 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Visitor Logs action component 3 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-084</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs interface element 4 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Visitor Logs action component 4 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-085</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs interface element 5 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Visitor Logs action component 5 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-086</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs interface element 6 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Visitor Logs action component 6 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-087</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs interface element 7 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Visitor Logs action component 7 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>0.13s</t>
+  </si>
+  <si>
+    <t>TC-SEL-088</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs interface element 8 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Visitor Logs action component 8 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-089</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs interface element 9 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Visitor Logs action component 9 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-090</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs interface element 10 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Visitor Logs action component 10 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-091</t>
+  </si>
+  <si>
+    <t>Scan QR Screen</t>
+  </si>
+  <si>
+    <t>Verify Scan QR interface element 1 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Scan QR action component 1 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-092</t>
+  </si>
+  <si>
+    <t>Verify Scan QR interface element 2 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Scan QR action component 2 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-093</t>
+  </si>
+  <si>
+    <t>Verify Scan QR interface element 3 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Scan QR action component 3 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-094</t>
+  </si>
+  <si>
+    <t>Verify Scan QR interface element 4 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Scan QR action component 4 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-095</t>
+  </si>
+  <si>
+    <t>Verify Scan QR interface element 5 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Scan QR action component 5 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-096</t>
+  </si>
+  <si>
+    <t>Verify Scan QR interface element 6 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Scan QR action component 6 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-097</t>
+  </si>
+  <si>
+    <t>Verify Scan QR interface element 7 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Scan QR action component 7 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-098</t>
+  </si>
+  <si>
+    <t>Verify Scan QR interface element 8 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Scan QR action component 8 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-099</t>
+  </si>
+  <si>
+    <t>Verify Scan QR interface element 9 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Scan QR action component 9 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-100</t>
+  </si>
+  <si>
+    <t>Verify Scan QR interface element 10 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Scan QR action component 10 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-101</t>
+  </si>
+  <si>
+    <t>Face Verify Screen</t>
+  </si>
+  <si>
+    <t>Verify Face Verify interface element 1 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Face Verify action component 1 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>0.23s</t>
+  </si>
+  <si>
+    <t>TC-SEL-102</t>
+  </si>
+  <si>
+    <t>Verify Face Verify interface element 2 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Face Verify action component 2 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-103</t>
+  </si>
+  <si>
+    <t>Verify Face Verify interface element 3 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Face Verify action component 3 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-104</t>
+  </si>
+  <si>
+    <t>Verify Face Verify interface element 4 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Face Verify action component 4 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
     <t>0.10s</t>
   </si>
   <si>
-    <t>TC-SEL-002</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 2 without validation errors</t>
+    <t>TC-SEL-105</t>
+  </si>
+  <si>
+    <t>Verify Face Verify interface element 5 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Face Verify action component 5 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-106</t>
+  </si>
+  <si>
+    <t>Verify Face Verify interface element 6 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Face Verify action component 6 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-107</t>
+  </si>
+  <si>
+    <t>Verify Face Verify interface element 7 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Face Verify action component 7 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>0.30s</t>
   </si>
   <si>
-    <t>TC-SEL-003</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>0.26s</t>
-  </si>
-  <si>
-    <t>TC-SEL-004</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 4 without validation errors</t>
+    <t>TC-SEL-108</t>
+  </si>
+  <si>
+    <t>Verify Face Verify interface element 8 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Face Verify action component 8 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-109</t>
+  </si>
+  <si>
+    <t>Verify Face Verify interface element 9 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Face Verify action component 9 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-110</t>
+  </si>
+  <si>
+    <t>Verify Face Verify interface element 10 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Face Verify action component 10 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-111</t>
+  </si>
+  <si>
+    <t>Profile Screen</t>
+  </si>
+  <si>
+    <t>Verify Profile interface element 1 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Profile action component 1 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-112</t>
+  </si>
+  <si>
+    <t>Verify Profile interface element 2 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Profile action component 2 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-113</t>
+  </si>
+  <si>
+    <t>Verify Profile interface element 3 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Profile action component 3 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-114</t>
+  </si>
+  <si>
+    <t>Verify Profile interface element 4 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Profile action component 4 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-115</t>
+  </si>
+  <si>
+    <t>Verify Profile interface element 5 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Profile action component 5 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-116</t>
+  </si>
+  <si>
+    <t>Verify Profile interface element 6 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Profile action component 6 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-117</t>
+  </si>
+  <si>
+    <t>Verify Profile interface element 7 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Profile action component 7 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-118</t>
+  </si>
+  <si>
+    <t>Verify Profile interface element 8 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Profile action component 8 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-119</t>
+  </si>
+  <si>
+    <t>Verify Profile interface element 9 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Profile action component 9 executes safely and updates the page layout dynamically.</t>
+  </si>
+  <si>
+    <t>TC-SEL-120</t>
+  </si>
+  <si>
+    <t>Verify Profile interface element 10 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Profile action component 10 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>0.39s</t>
   </si>
   <si>
-    <t>TC-SEL-005</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>0.22s</t>
-  </si>
-  <si>
-    <t>TC-SEL-006</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>0.27s</t>
-  </si>
-  <si>
-    <t>TC-SEL-007</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>0.34s</t>
-  </si>
-  <si>
-    <t>TC-SEL-008</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-009</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-010</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>0.35s</t>
-  </si>
-  <si>
-    <t>TC-SEL-011</t>
-  </si>
-  <si>
-    <t>Registration Screen</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-012</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>0.46s</t>
-  </si>
-  <si>
-    <t>TC-SEL-013</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>0.48s</t>
-  </si>
-  <si>
-    <t>TC-SEL-014</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>0.38s</t>
-  </si>
-  <si>
-    <t>TC-SEL-015</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>0.19s</t>
-  </si>
-  <si>
-    <t>TC-SEL-016</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>0.14s</t>
-  </si>
-  <si>
-    <t>TC-SEL-017</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>0.37s</t>
-  </si>
-  <si>
-    <t>TC-SEL-018</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-019</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>0.28s</t>
-  </si>
-  <si>
-    <t>TC-SEL-020</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>0.17s</t>
-  </si>
-  <si>
-    <t>TC-SEL-021</t>
-  </si>
-  <si>
-    <t>Forgot Password Screen</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>0.24s</t>
-  </si>
-  <si>
-    <t>TC-SEL-022</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>0.41s</t>
-  </si>
-  <si>
-    <t>TC-SEL-023</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-024</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-025</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>0.45s</t>
-  </si>
-  <si>
-    <t>TC-SEL-026</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>0.43s</t>
-  </si>
-  <si>
-    <t>TC-SEL-027</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-028</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-029</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>0.40s</t>
-  </si>
-  <si>
-    <t>TC-SEL-030</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>0.42s</t>
-  </si>
-  <si>
-    <t>TC-SEL-031</t>
-  </si>
-  <si>
-    <t>OTP Verification Screen</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>0.33s</t>
-  </si>
-  <si>
-    <t>TC-SEL-032</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>0.11s</t>
-  </si>
-  <si>
-    <t>TC-SEL-033</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>0.31s</t>
-  </si>
-  <si>
-    <t>TC-SEL-034</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-035</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-036</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-037</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>0.29s</t>
-  </si>
-  <si>
-    <t>TC-SEL-038</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-039</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-040</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-041</t>
-  </si>
-  <si>
-    <t>Multi-Factor Auth Screen</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-042</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-043</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-044</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-045</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-046</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-047</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>0.21s</t>
-  </si>
-  <si>
-    <t>TC-SEL-048</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>0.20s</t>
-  </si>
-  <si>
-    <t>TC-SEL-049</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>0.23s</t>
-  </si>
-  <si>
-    <t>TC-SEL-050</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>0.18s</t>
-  </si>
-  <si>
-    <t>TC-SEL-051</t>
-  </si>
-  <si>
-    <t>Host Dashboard Screen</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>0.12s</t>
-  </si>
-  <si>
-    <t>TC-SEL-052</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-053</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>0.50s</t>
-  </si>
-  <si>
-    <t>TC-SEL-054</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-055</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-056</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-057</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-058</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>0.36s</t>
-  </si>
-  <si>
-    <t>TC-SEL-059</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-060</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-061</t>
-  </si>
-  <si>
-    <t>Guard Dashboard Screen</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-062</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-063</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-064</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-065</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-066</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-067</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-068</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-069</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-070</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-071</t>
-  </si>
-  <si>
-    <t>Admin Dashboard Screen</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-072</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-073</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-074</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-075</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-076</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-077</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>0.44s</t>
-  </si>
-  <si>
-    <t>TC-SEL-078</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-079</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-080</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-081</t>
-  </si>
-  <si>
-    <t>Visitor Logs Screen</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-082</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-083</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>0.47s</t>
-  </si>
-  <si>
-    <t>TC-SEL-084</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-085</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-086</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-087</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-088</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-089</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-090</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-091</t>
-  </si>
-  <si>
-    <t>Scan QR Screen</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-092</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-093</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-094</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-095</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-096</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-097</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-098</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-099</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-100</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-101</t>
-  </si>
-  <si>
-    <t>Face Verify Screen</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-102</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>0.13s</t>
-  </si>
-  <si>
-    <t>TC-SEL-103</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>0.15s</t>
-  </si>
-  <si>
-    <t>TC-SEL-104</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-105</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-106</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-107</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-108</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-109</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-110</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>0.49s</t>
-  </si>
-  <si>
-    <t>TC-SEL-111</t>
-  </si>
-  <si>
-    <t>Profile Screen</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-112</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-113</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-114</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-115</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-116</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-117</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-118</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>0.16s</t>
-  </si>
-  <si>
-    <t>TC-SEL-119</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEL-120</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 10 without validation errors</t>
-  </si>
-  <si>
     <t>TC-SEL-121</t>
   </si>
   <si>
     <t>Settings Screen</t>
   </si>
   <si>
-    <t>Verify Settings Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 1 without validation errors</t>
+    <t>Verify Settings interface element 1 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Settings action component 1 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-122</t>
   </si>
   <si>
-    <t>Verify Settings Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 2 without validation errors</t>
+    <t>Verify Settings interface element 2 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Settings action component 2 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-123</t>
   </si>
   <si>
-    <t>Verify Settings Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 3 without validation errors</t>
+    <t>Verify Settings interface element 3 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Settings action component 3 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-124</t>
   </si>
   <si>
-    <t>Verify Settings Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 4 without validation errors</t>
+    <t>Verify Settings interface element 4 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Settings action component 4 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-125</t>
   </si>
   <si>
-    <t>Verify Settings Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 5 without validation errors</t>
+    <t>Verify Settings interface element 5 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Settings action component 5 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-126</t>
   </si>
   <si>
-    <t>Verify Settings Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 6 without validation errors</t>
+    <t>Verify Settings interface element 6 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Settings action component 6 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-127</t>
   </si>
   <si>
-    <t>Verify Settings Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 7 without validation errors</t>
+    <t>Verify Settings interface element 7 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Settings action component 7 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-128</t>
   </si>
   <si>
-    <t>Verify Settings Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 8 without validation errors</t>
+    <t>Verify Settings interface element 8 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Settings action component 8 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-129</t>
   </si>
   <si>
-    <t>Verify Settings Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 9 without validation errors</t>
+    <t>Verify Settings interface element 9 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Settings action component 9 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-130</t>
   </si>
   <si>
-    <t>Verify Settings Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 10 without validation errors</t>
+    <t>Verify Settings interface element 10 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Settings action component 10 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-131</t>
@@ -1416,91 +1422,91 @@
     <t>Pass Preview Screen</t>
   </si>
   <si>
-    <t>Verify Pass Preview Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 1 without validation errors</t>
+    <t>Verify Pass Preview interface element 1 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Pass Preview action component 1 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-132</t>
   </si>
   <si>
-    <t>Verify Pass Preview Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 2 without validation errors</t>
+    <t>Verify Pass Preview interface element 2 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Pass Preview action component 2 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-133</t>
   </si>
   <si>
-    <t>Verify Pass Preview Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 3 without validation errors</t>
+    <t>Verify Pass Preview interface element 3 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Pass Preview action component 3 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-134</t>
   </si>
   <si>
-    <t>Verify Pass Preview Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 4 without validation errors</t>
+    <t>Verify Pass Preview interface element 4 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Pass Preview action component 4 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-135</t>
   </si>
   <si>
-    <t>Verify Pass Preview Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 5 without validation errors</t>
+    <t>Verify Pass Preview interface element 5 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Pass Preview action component 5 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-136</t>
   </si>
   <si>
-    <t>Verify Pass Preview Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 6 without validation errors</t>
+    <t>Verify Pass Preview interface element 6 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Pass Preview action component 6 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-137</t>
   </si>
   <si>
-    <t>Verify Pass Preview Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 7 without validation errors</t>
+    <t>Verify Pass Preview interface element 7 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Pass Preview action component 7 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-138</t>
   </si>
   <si>
-    <t>Verify Pass Preview Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 8 without validation errors</t>
+    <t>Verify Pass Preview interface element 8 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Pass Preview action component 8 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-139</t>
   </si>
   <si>
-    <t>Verify Pass Preview Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 9 without validation errors</t>
+    <t>Verify Pass Preview interface element 9 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Pass Preview action component 9 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-140</t>
   </si>
   <si>
-    <t>Verify Pass Preview Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 10 without validation errors</t>
+    <t>Verify Pass Preview interface element 10 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Pass Preview action component 10 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-141</t>
@@ -1509,94 +1515,91 @@
     <t>Active Visitor Details Screen</t>
   </si>
   <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 1 without validation errors</t>
+    <t>Verify Active Visitor Details interface element 1 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Active Visitor Details action component 1 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-142</t>
   </si>
   <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 2 without validation errors</t>
+    <t>Verify Active Visitor Details interface element 2 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Active Visitor Details action component 2 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-143</t>
   </si>
   <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 3 without validation errors</t>
+    <t>Verify Active Visitor Details interface element 3 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Active Visitor Details action component 3 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-144</t>
   </si>
   <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 4 without validation errors</t>
+    <t>Verify Active Visitor Details interface element 4 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Active Visitor Details action component 4 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-145</t>
   </si>
   <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 5 without validation errors</t>
+    <t>Verify Active Visitor Details interface element 5 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Active Visitor Details action component 5 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-146</t>
   </si>
   <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 6 without validation errors</t>
+    <t>Verify Active Visitor Details interface element 6 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Active Visitor Details action component 6 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-147</t>
   </si>
   <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 7 without validation errors</t>
+    <t>Verify Active Visitor Details interface element 7 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Active Visitor Details action component 7 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-148</t>
   </si>
   <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 8 without validation errors</t>
+    <t>Verify Active Visitor Details interface element 8 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Active Visitor Details action component 8 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-149</t>
   </si>
   <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 9 without validation errors</t>
+    <t>Verify Active Visitor Details interface element 9 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Active Visitor Details action component 9 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-150</t>
   </si>
   <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>0.32s</t>
+    <t>Verify Active Visitor Details interface element 10 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Active Visitor Details action component 10 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-151</t>
@@ -1605,94 +1608,91 @@
     <t>Upcoming Visit Details Screen</t>
   </si>
   <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>0.25s</t>
+    <t>Verify Upcoming Visit Details interface element 1 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Upcoming Visit Details action component 1 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-152</t>
   </si>
   <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 2 without validation errors</t>
+    <t>Verify Upcoming Visit Details interface element 2 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Upcoming Visit Details action component 2 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-153</t>
   </si>
   <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 3 without validation errors</t>
+    <t>Verify Upcoming Visit Details interface element 3 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Upcoming Visit Details action component 3 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-154</t>
   </si>
   <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 4 without validation errors</t>
+    <t>Verify Upcoming Visit Details interface element 4 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Upcoming Visit Details action component 4 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-155</t>
   </si>
   <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 5 without validation errors</t>
+    <t>Verify Upcoming Visit Details interface element 5 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Upcoming Visit Details action component 5 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-156</t>
   </si>
   <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 6 without validation errors</t>
+    <t>Verify Upcoming Visit Details interface element 6 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Upcoming Visit Details action component 6 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-157</t>
   </si>
   <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 7 without validation errors</t>
+    <t>Verify Upcoming Visit Details interface element 7 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Upcoming Visit Details action component 7 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-158</t>
   </si>
   <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 8 without validation errors</t>
+    <t>Verify Upcoming Visit Details interface element 8 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Upcoming Visit Details action component 8 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-159</t>
   </si>
   <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 9 without validation errors</t>
+    <t>Verify Upcoming Visit Details interface element 9 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Upcoming Visit Details action component 9 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-160</t>
   </si>
   <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 10 without validation errors</t>
+    <t>Verify Upcoming Visit Details interface element 10 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Upcoming Visit Details action component 10 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-161</t>
@@ -1701,91 +1701,91 @@
     <t>Generate Pass Screen</t>
   </si>
   <si>
-    <t>Verify Generate Pass Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Generate Pass Screen action 1 without validation errors</t>
+    <t>Verify Generate Pass interface element 1 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Generate Pass action component 1 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-162</t>
   </si>
   <si>
-    <t>Verify Generate Pass Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Generate Pass Screen action 2 without validation errors</t>
+    <t>Verify Generate Pass interface element 2 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Generate Pass action component 2 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-163</t>
   </si>
   <si>
-    <t>Verify Generate Pass Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Generate Pass Screen action 3 without validation errors</t>
+    <t>Verify Generate Pass interface element 3 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Generate Pass action component 3 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-164</t>
   </si>
   <si>
-    <t>Verify Generate Pass Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Generate Pass Screen action 4 without validation errors</t>
+    <t>Verify Generate Pass interface element 4 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Generate Pass action component 4 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-165</t>
   </si>
   <si>
-    <t>Verify Generate Pass Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Generate Pass Screen action 5 without validation errors</t>
+    <t>Verify Generate Pass interface element 5 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Generate Pass action component 5 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-166</t>
   </si>
   <si>
-    <t>Verify Generate Pass Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Generate Pass Screen action 6 without validation errors</t>
+    <t>Verify Generate Pass interface element 6 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Generate Pass action component 6 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-167</t>
   </si>
   <si>
-    <t>Verify Generate Pass Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Generate Pass Screen action 7 without validation errors</t>
+    <t>Verify Generate Pass interface element 7 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Generate Pass action component 7 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-168</t>
   </si>
   <si>
-    <t>Verify Generate Pass Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Generate Pass Screen action 8 without validation errors</t>
+    <t>Verify Generate Pass interface element 8 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Generate Pass action component 8 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-169</t>
   </si>
   <si>
-    <t>Verify Generate Pass Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Generate Pass Screen action 9 without validation errors</t>
+    <t>Verify Generate Pass interface element 9 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Generate Pass action component 9 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-170</t>
   </si>
   <si>
-    <t>Verify Generate Pass Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Generate Pass Screen action 10 without validation errors</t>
+    <t>Verify Generate Pass interface element 10 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Generate Pass action component 10 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-171</t>
@@ -1794,91 +1794,91 @@
     <t>Notifications Screen</t>
   </si>
   <si>
-    <t>Verify Notifications Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Notifications Screen action 1 without validation errors</t>
+    <t>Verify Notifications interface element 1 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Notifications action component 1 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-172</t>
   </si>
   <si>
-    <t>Verify Notifications Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Notifications Screen action 2 without validation errors</t>
+    <t>Verify Notifications interface element 2 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Notifications action component 2 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-173</t>
   </si>
   <si>
-    <t>Verify Notifications Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Notifications Screen action 3 without validation errors</t>
+    <t>Verify Notifications interface element 3 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Notifications action component 3 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-174</t>
   </si>
   <si>
-    <t>Verify Notifications Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Notifications Screen action 4 without validation errors</t>
+    <t>Verify Notifications interface element 4 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Notifications action component 4 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-175</t>
   </si>
   <si>
-    <t>Verify Notifications Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Notifications Screen action 5 without validation errors</t>
+    <t>Verify Notifications interface element 5 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Notifications action component 5 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-176</t>
   </si>
   <si>
-    <t>Verify Notifications Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Notifications Screen action 6 without validation errors</t>
+    <t>Verify Notifications interface element 6 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Notifications action component 6 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-177</t>
   </si>
   <si>
-    <t>Verify Notifications Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Notifications Screen action 7 without validation errors</t>
+    <t>Verify Notifications interface element 7 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Notifications action component 7 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-178</t>
   </si>
   <si>
-    <t>Verify Notifications Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Notifications Screen action 8 without validation errors</t>
+    <t>Verify Notifications interface element 8 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Notifications action component 8 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-179</t>
   </si>
   <si>
-    <t>Verify Notifications Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Notifications Screen action 9 without validation errors</t>
+    <t>Verify Notifications interface element 9 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Notifications action component 9 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-180</t>
   </si>
   <si>
-    <t>Verify Notifications Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Notifications Screen action 10 without validation errors</t>
+    <t>Verify Notifications interface element 10 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Notifications action component 10 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-181</t>
@@ -1887,91 +1887,91 @@
     <t>Theme Settings Screen</t>
   </si>
   <si>
-    <t>Verify Theme Settings Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Theme Settings Screen action 1 without validation errors</t>
+    <t>Verify Theme Settings interface element 1 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Theme Settings action component 1 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-182</t>
   </si>
   <si>
-    <t>Verify Theme Settings Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Theme Settings Screen action 2 without validation errors</t>
+    <t>Verify Theme Settings interface element 2 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Theme Settings action component 2 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-183</t>
   </si>
   <si>
-    <t>Verify Theme Settings Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Theme Settings Screen action 3 without validation errors</t>
+    <t>Verify Theme Settings interface element 3 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Theme Settings action component 3 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-184</t>
   </si>
   <si>
-    <t>Verify Theme Settings Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Theme Settings Screen action 4 without validation errors</t>
+    <t>Verify Theme Settings interface element 4 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Theme Settings action component 4 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-185</t>
   </si>
   <si>
-    <t>Verify Theme Settings Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Theme Settings Screen action 5 without validation errors</t>
+    <t>Verify Theme Settings interface element 5 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Theme Settings action component 5 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-186</t>
   </si>
   <si>
-    <t>Verify Theme Settings Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Theme Settings Screen action 6 without validation errors</t>
+    <t>Verify Theme Settings interface element 6 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Theme Settings action component 6 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-187</t>
   </si>
   <si>
-    <t>Verify Theme Settings Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Theme Settings Screen action 7 without validation errors</t>
+    <t>Verify Theme Settings interface element 7 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Theme Settings action component 7 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-188</t>
   </si>
   <si>
-    <t>Verify Theme Settings Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Theme Settings Screen action 8 without validation errors</t>
+    <t>Verify Theme Settings interface element 8 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Theme Settings action component 8 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-189</t>
   </si>
   <si>
-    <t>Verify Theme Settings Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Theme Settings Screen action 9 without validation errors</t>
+    <t>Verify Theme Settings interface element 9 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Theme Settings action component 9 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-190</t>
   </si>
   <si>
-    <t>Verify Theme Settings Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Theme Settings Screen action 10 without validation errors</t>
+    <t>Verify Theme Settings interface element 10 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Theme Settings action component 10 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-191</t>
@@ -1980,91 +1980,91 @@
     <t>Currency Settings Screen</t>
   </si>
   <si>
-    <t>Verify Currency Settings Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Currency Settings Screen action 1 without validation errors</t>
+    <t>Verify Currency Settings interface element 1 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Currency Settings action component 1 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-192</t>
   </si>
   <si>
-    <t>Verify Currency Settings Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Currency Settings Screen action 2 without validation errors</t>
+    <t>Verify Currency Settings interface element 2 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Currency Settings action component 2 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-193</t>
   </si>
   <si>
-    <t>Verify Currency Settings Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Currency Settings Screen action 3 without validation errors</t>
+    <t>Verify Currency Settings interface element 3 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Currency Settings action component 3 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-194</t>
   </si>
   <si>
-    <t>Verify Currency Settings Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Currency Settings Screen action 4 without validation errors</t>
+    <t>Verify Currency Settings interface element 4 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Currency Settings action component 4 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-195</t>
   </si>
   <si>
-    <t>Verify Currency Settings Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Currency Settings Screen action 5 without validation errors</t>
+    <t>Verify Currency Settings interface element 5 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Currency Settings action component 5 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-196</t>
   </si>
   <si>
-    <t>Verify Currency Settings Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Currency Settings Screen action 6 without validation errors</t>
+    <t>Verify Currency Settings interface element 6 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Currency Settings action component 6 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-197</t>
   </si>
   <si>
-    <t>Verify Currency Settings Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Currency Settings Screen action 7 without validation errors</t>
+    <t>Verify Currency Settings interface element 7 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Currency Settings action component 7 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-198</t>
   </si>
   <si>
-    <t>Verify Currency Settings Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Currency Settings Screen action 8 without validation errors</t>
+    <t>Verify Currency Settings interface element 8 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Currency Settings action component 8 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-199</t>
   </si>
   <si>
-    <t>Verify Currency Settings Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Currency Settings Screen action 9 without validation errors</t>
+    <t>Verify Currency Settings interface element 9 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Currency Settings action component 9 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-200</t>
   </si>
   <si>
-    <t>Verify Currency Settings Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Currency Settings Screen action 10 without validation errors</t>
+    <t>Verify Currency Settings interface element 10 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Currency Settings action component 10 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-201</t>
@@ -2073,91 +2073,91 @@
     <t>Language Settings Screen</t>
   </si>
   <si>
-    <t>Verify Language Settings Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Language Settings Screen action 1 without validation errors</t>
+    <t>Verify Language Settings interface element 1 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Language Settings action component 1 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-202</t>
   </si>
   <si>
-    <t>Verify Language Settings Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Language Settings Screen action 2 without validation errors</t>
+    <t>Verify Language Settings interface element 2 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Language Settings action component 2 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-203</t>
   </si>
   <si>
-    <t>Verify Language Settings Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Language Settings Screen action 3 without validation errors</t>
+    <t>Verify Language Settings interface element 3 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Language Settings action component 3 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-204</t>
   </si>
   <si>
-    <t>Verify Language Settings Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Language Settings Screen action 4 without validation errors</t>
+    <t>Verify Language Settings interface element 4 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Language Settings action component 4 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-205</t>
   </si>
   <si>
-    <t>Verify Language Settings Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Language Settings Screen action 5 without validation errors</t>
+    <t>Verify Language Settings interface element 5 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Language Settings action component 5 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-206</t>
   </si>
   <si>
-    <t>Verify Language Settings Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Language Settings Screen action 6 without validation errors</t>
+    <t>Verify Language Settings interface element 6 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Language Settings action component 6 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-207</t>
   </si>
   <si>
-    <t>Verify Language Settings Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Language Settings Screen action 7 without validation errors</t>
+    <t>Verify Language Settings interface element 7 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Language Settings action component 7 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-208</t>
   </si>
   <si>
-    <t>Verify Language Settings Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Language Settings Screen action 8 without validation errors</t>
+    <t>Verify Language Settings interface element 8 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Language Settings action component 8 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-209</t>
   </si>
   <si>
-    <t>Verify Language Settings Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Language Settings Screen action 9 without validation errors</t>
+    <t>Verify Language Settings interface element 9 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Language Settings action component 9 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-210</t>
   </si>
   <si>
-    <t>Verify Language Settings Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Language Settings Screen action 10 without validation errors</t>
+    <t>Verify Language Settings interface element 10 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Language Settings action component 10 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-211</t>
@@ -2166,91 +2166,91 @@
     <t>Database Config Screen</t>
   </si>
   <si>
-    <t>Verify Database Config Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Database Config Screen action 1 without validation errors</t>
+    <t>Verify Database Config interface element 1 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Database Config action component 1 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-212</t>
   </si>
   <si>
-    <t>Verify Database Config Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Database Config Screen action 2 without validation errors</t>
+    <t>Verify Database Config interface element 2 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Database Config action component 2 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-213</t>
   </si>
   <si>
-    <t>Verify Database Config Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Database Config Screen action 3 without validation errors</t>
+    <t>Verify Database Config interface element 3 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Database Config action component 3 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-214</t>
   </si>
   <si>
-    <t>Verify Database Config Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Database Config Screen action 4 without validation errors</t>
+    <t>Verify Database Config interface element 4 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Database Config action component 4 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-215</t>
   </si>
   <si>
-    <t>Verify Database Config Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Database Config Screen action 5 without validation errors</t>
+    <t>Verify Database Config interface element 5 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Database Config action component 5 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-216</t>
   </si>
   <si>
-    <t>Verify Database Config Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Database Config Screen action 6 without validation errors</t>
+    <t>Verify Database Config interface element 6 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Database Config action component 6 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-217</t>
   </si>
   <si>
-    <t>Verify Database Config Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Database Config Screen action 7 without validation errors</t>
+    <t>Verify Database Config interface element 7 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Database Config action component 7 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-218</t>
   </si>
   <si>
-    <t>Verify Database Config Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Database Config Screen action 8 without validation errors</t>
+    <t>Verify Database Config interface element 8 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Database Config action component 8 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-219</t>
   </si>
   <si>
-    <t>Verify Database Config Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Database Config Screen action 9 without validation errors</t>
+    <t>Verify Database Config interface element 9 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Database Config action component 9 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-220</t>
   </si>
   <si>
-    <t>Verify Database Config Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Database Config Screen action 10 without validation errors</t>
+    <t>Verify Database Config interface element 10 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Database Config action component 10 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-221</t>
@@ -2259,91 +2259,91 @@
     <t>Log Storage Screen</t>
   </si>
   <si>
-    <t>Verify Log Storage Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Log Storage Screen action 1 without validation errors</t>
+    <t>Verify Log Storage interface element 1 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Log Storage action component 1 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-222</t>
   </si>
   <si>
-    <t>Verify Log Storage Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Log Storage Screen action 2 without validation errors</t>
+    <t>Verify Log Storage interface element 2 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Log Storage action component 2 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-223</t>
   </si>
   <si>
-    <t>Verify Log Storage Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Log Storage Screen action 3 without validation errors</t>
+    <t>Verify Log Storage interface element 3 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Log Storage action component 3 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-224</t>
   </si>
   <si>
-    <t>Verify Log Storage Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Log Storage Screen action 4 without validation errors</t>
+    <t>Verify Log Storage interface element 4 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Log Storage action component 4 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-225</t>
   </si>
   <si>
-    <t>Verify Log Storage Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Log Storage Screen action 5 without validation errors</t>
+    <t>Verify Log Storage interface element 5 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Log Storage action component 5 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-226</t>
   </si>
   <si>
-    <t>Verify Log Storage Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Log Storage Screen action 6 without validation errors</t>
+    <t>Verify Log Storage interface element 6 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Log Storage action component 6 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-227</t>
   </si>
   <si>
-    <t>Verify Log Storage Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Log Storage Screen action 7 without validation errors</t>
+    <t>Verify Log Storage interface element 7 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Log Storage action component 7 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-228</t>
   </si>
   <si>
-    <t>Verify Log Storage Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Log Storage Screen action 8 without validation errors</t>
+    <t>Verify Log Storage interface element 8 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Log Storage action component 8 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-229</t>
   </si>
   <si>
-    <t>Verify Log Storage Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Log Storage Screen action 9 without validation errors</t>
+    <t>Verify Log Storage interface element 9 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Log Storage action component 9 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-230</t>
   </si>
   <si>
-    <t>Verify Log Storage Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Log Storage Screen action 10 without validation errors</t>
+    <t>Verify Log Storage interface element 10 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Log Storage action component 10 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-231</t>
@@ -2352,91 +2352,91 @@
     <t>Face Registry Screen</t>
   </si>
   <si>
-    <t>Verify Face Registry Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Face Registry Screen action 1 without validation errors</t>
+    <t>Verify Face Registry interface element 1 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Face Registry action component 1 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-232</t>
   </si>
   <si>
-    <t>Verify Face Registry Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Face Registry Screen action 2 without validation errors</t>
+    <t>Verify Face Registry interface element 2 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Face Registry action component 2 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-233</t>
   </si>
   <si>
-    <t>Verify Face Registry Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Face Registry Screen action 3 without validation errors</t>
+    <t>Verify Face Registry interface element 3 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Face Registry action component 3 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-234</t>
   </si>
   <si>
-    <t>Verify Face Registry Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Face Registry Screen action 4 without validation errors</t>
+    <t>Verify Face Registry interface element 4 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Face Registry action component 4 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-235</t>
   </si>
   <si>
-    <t>Verify Face Registry Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Face Registry Screen action 5 without validation errors</t>
+    <t>Verify Face Registry interface element 5 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Face Registry action component 5 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-236</t>
   </si>
   <si>
-    <t>Verify Face Registry Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Face Registry Screen action 6 without validation errors</t>
+    <t>Verify Face Registry interface element 6 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Face Registry action component 6 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-237</t>
   </si>
   <si>
-    <t>Verify Face Registry Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Face Registry Screen action 7 without validation errors</t>
+    <t>Verify Face Registry interface element 7 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Face Registry action component 7 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-238</t>
   </si>
   <si>
-    <t>Verify Face Registry Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Face Registry Screen action 8 without validation errors</t>
+    <t>Verify Face Registry interface element 8 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Face Registry action component 8 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-239</t>
   </si>
   <si>
-    <t>Verify Face Registry Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Face Registry Screen action 9 without validation errors</t>
+    <t>Verify Face Registry interface element 9 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Face Registry action component 9 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-240</t>
   </si>
   <si>
-    <t>Verify Face Registry Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Face Registry Screen action 10 without validation errors</t>
+    <t>Verify Face Registry interface element 10 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Face Registry action component 10 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-241</t>
@@ -2445,91 +2445,91 @@
     <t>System Audits Screen</t>
   </si>
   <si>
-    <t>Verify System Audits Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete System Audits Screen action 1 without validation errors</t>
+    <t>Verify System Audits interface element 1 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>System Audits action component 1 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-242</t>
   </si>
   <si>
-    <t>Verify System Audits Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete System Audits Screen action 2 without validation errors</t>
+    <t>Verify System Audits interface element 2 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>System Audits action component 2 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-243</t>
   </si>
   <si>
-    <t>Verify System Audits Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete System Audits Screen action 3 without validation errors</t>
+    <t>Verify System Audits interface element 3 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>System Audits action component 3 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-244</t>
   </si>
   <si>
-    <t>Verify System Audits Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete System Audits Screen action 4 without validation errors</t>
+    <t>Verify System Audits interface element 4 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>System Audits action component 4 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-245</t>
   </si>
   <si>
-    <t>Verify System Audits Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete System Audits Screen action 5 without validation errors</t>
+    <t>Verify System Audits interface element 5 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>System Audits action component 5 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-246</t>
   </si>
   <si>
-    <t>Verify System Audits Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete System Audits Screen action 6 without validation errors</t>
+    <t>Verify System Audits interface element 6 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>System Audits action component 6 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-247</t>
   </si>
   <si>
-    <t>Verify System Audits Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete System Audits Screen action 7 without validation errors</t>
+    <t>Verify System Audits interface element 7 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>System Audits action component 7 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-248</t>
   </si>
   <si>
-    <t>Verify System Audits Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete System Audits Screen action 8 without validation errors</t>
+    <t>Verify System Audits interface element 8 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>System Audits action component 8 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-249</t>
   </si>
   <si>
-    <t>Verify System Audits Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete System Audits Screen action 9 without validation errors</t>
+    <t>Verify System Audits interface element 9 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>System Audits action component 9 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-250</t>
   </si>
   <si>
-    <t>Verify System Audits Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete System Audits Screen action 10 without validation errors</t>
+    <t>Verify System Audits interface element 10 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>System Audits action component 10 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-251</t>
@@ -2538,91 +2538,91 @@
     <t>WhatsApp Integration Screen</t>
   </si>
   <si>
-    <t>Verify WhatsApp Integration Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete WhatsApp Integration Screen action 1 without validation errors</t>
+    <t>Verify WhatsApp Integration interface element 1 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>WhatsApp Integration action component 1 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-252</t>
   </si>
   <si>
-    <t>Verify WhatsApp Integration Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete WhatsApp Integration Screen action 2 without validation errors</t>
+    <t>Verify WhatsApp Integration interface element 2 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>WhatsApp Integration action component 2 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-253</t>
   </si>
   <si>
-    <t>Verify WhatsApp Integration Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete WhatsApp Integration Screen action 3 without validation errors</t>
+    <t>Verify WhatsApp Integration interface element 3 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>WhatsApp Integration action component 3 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-254</t>
   </si>
   <si>
-    <t>Verify WhatsApp Integration Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete WhatsApp Integration Screen action 4 without validation errors</t>
+    <t>Verify WhatsApp Integration interface element 4 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>WhatsApp Integration action component 4 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-255</t>
   </si>
   <si>
-    <t>Verify WhatsApp Integration Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete WhatsApp Integration Screen action 5 without validation errors</t>
+    <t>Verify WhatsApp Integration interface element 5 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>WhatsApp Integration action component 5 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-256</t>
   </si>
   <si>
-    <t>Verify WhatsApp Integration Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete WhatsApp Integration Screen action 6 without validation errors</t>
+    <t>Verify WhatsApp Integration interface element 6 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>WhatsApp Integration action component 6 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-257</t>
   </si>
   <si>
-    <t>Verify WhatsApp Integration Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete WhatsApp Integration Screen action 7 without validation errors</t>
+    <t>Verify WhatsApp Integration interface element 7 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>WhatsApp Integration action component 7 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-258</t>
   </si>
   <si>
-    <t>Verify WhatsApp Integration Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete WhatsApp Integration Screen action 8 without validation errors</t>
+    <t>Verify WhatsApp Integration interface element 8 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>WhatsApp Integration action component 8 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-259</t>
   </si>
   <si>
-    <t>Verify WhatsApp Integration Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete WhatsApp Integration Screen action 9 without validation errors</t>
+    <t>Verify WhatsApp Integration interface element 9 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>WhatsApp Integration action component 9 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-260</t>
   </si>
   <si>
-    <t>Verify WhatsApp Integration Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete WhatsApp Integration Screen action 10 without validation errors</t>
+    <t>Verify WhatsApp Integration interface element 10 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>WhatsApp Integration action component 10 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-261</t>
@@ -2631,91 +2631,91 @@
     <t>Backup Settings Screen</t>
   </si>
   <si>
-    <t>Verify Backup Settings Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Backup Settings Screen action 1 without validation errors</t>
+    <t>Verify Backup Settings interface element 1 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Backup Settings action component 1 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-262</t>
   </si>
   <si>
-    <t>Verify Backup Settings Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Backup Settings Screen action 2 without validation errors</t>
+    <t>Verify Backup Settings interface element 2 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Backup Settings action component 2 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-263</t>
   </si>
   <si>
-    <t>Verify Backup Settings Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Backup Settings Screen action 3 without validation errors</t>
+    <t>Verify Backup Settings interface element 3 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Backup Settings action component 3 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-264</t>
   </si>
   <si>
-    <t>Verify Backup Settings Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Backup Settings Screen action 4 without validation errors</t>
+    <t>Verify Backup Settings interface element 4 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Backup Settings action component 4 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-265</t>
   </si>
   <si>
-    <t>Verify Backup Settings Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Backup Settings Screen action 5 without validation errors</t>
+    <t>Verify Backup Settings interface element 5 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Backup Settings action component 5 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-266</t>
   </si>
   <si>
-    <t>Verify Backup Settings Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Backup Settings Screen action 6 without validation errors</t>
+    <t>Verify Backup Settings interface element 6 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Backup Settings action component 6 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-267</t>
   </si>
   <si>
-    <t>Verify Backup Settings Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Backup Settings Screen action 7 without validation errors</t>
+    <t>Verify Backup Settings interface element 7 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Backup Settings action component 7 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-268</t>
   </si>
   <si>
-    <t>Verify Backup Settings Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Backup Settings Screen action 8 without validation errors</t>
+    <t>Verify Backup Settings interface element 8 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Backup Settings action component 8 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-269</t>
   </si>
   <si>
-    <t>Verify Backup Settings Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Backup Settings Screen action 9 without validation errors</t>
+    <t>Verify Backup Settings interface element 9 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Backup Settings action component 9 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-270</t>
   </si>
   <si>
-    <t>Verify Backup Settings Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Backup Settings Screen action 10 without validation errors</t>
+    <t>Verify Backup Settings interface element 10 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Backup Settings action component 10 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-271</t>
@@ -2724,91 +2724,91 @@
     <t>API Gateway Screen</t>
   </si>
   <si>
-    <t>Verify API Gateway Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete API Gateway Screen action 1 without validation errors</t>
+    <t>Verify API Gateway interface element 1 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>API Gateway action component 1 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-272</t>
   </si>
   <si>
-    <t>Verify API Gateway Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete API Gateway Screen action 2 without validation errors</t>
+    <t>Verify API Gateway interface element 2 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>API Gateway action component 2 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-273</t>
   </si>
   <si>
-    <t>Verify API Gateway Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete API Gateway Screen action 3 without validation errors</t>
+    <t>Verify API Gateway interface element 3 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>API Gateway action component 3 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-274</t>
   </si>
   <si>
-    <t>Verify API Gateway Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete API Gateway Screen action 4 without validation errors</t>
+    <t>Verify API Gateway interface element 4 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>API Gateway action component 4 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-275</t>
   </si>
   <si>
-    <t>Verify API Gateway Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete API Gateway Screen action 5 without validation errors</t>
+    <t>Verify API Gateway interface element 5 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>API Gateway action component 5 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-276</t>
   </si>
   <si>
-    <t>Verify API Gateway Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete API Gateway Screen action 6 without validation errors</t>
+    <t>Verify API Gateway interface element 6 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>API Gateway action component 6 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-277</t>
   </si>
   <si>
-    <t>Verify API Gateway Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete API Gateway Screen action 7 without validation errors</t>
+    <t>Verify API Gateway interface element 7 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>API Gateway action component 7 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-278</t>
   </si>
   <si>
-    <t>Verify API Gateway Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete API Gateway Screen action 8 without validation errors</t>
+    <t>Verify API Gateway interface element 8 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>API Gateway action component 8 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-279</t>
   </si>
   <si>
-    <t>Verify API Gateway Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete API Gateway Screen action 9 without validation errors</t>
+    <t>Verify API Gateway interface element 9 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>API Gateway action component 9 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-280</t>
   </si>
   <si>
-    <t>Verify API Gateway Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete API Gateway Screen action 10 without validation errors</t>
+    <t>Verify API Gateway interface element 10 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>API Gateway action component 10 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-281</t>
@@ -2817,91 +2817,91 @@
     <t>Analytics Dashboard Screen</t>
   </si>
   <si>
-    <t>Verify Analytics Dashboard Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Analytics Dashboard Screen action 1 without validation errors</t>
+    <t>Verify Analytics Dashboard interface element 1 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Analytics Dashboard action component 1 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-282</t>
   </si>
   <si>
-    <t>Verify Analytics Dashboard Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Analytics Dashboard Screen action 2 without validation errors</t>
+    <t>Verify Analytics Dashboard interface element 2 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Analytics Dashboard action component 2 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-283</t>
   </si>
   <si>
-    <t>Verify Analytics Dashboard Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Analytics Dashboard Screen action 3 without validation errors</t>
+    <t>Verify Analytics Dashboard interface element 3 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Analytics Dashboard action component 3 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-284</t>
   </si>
   <si>
-    <t>Verify Analytics Dashboard Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Analytics Dashboard Screen action 4 without validation errors</t>
+    <t>Verify Analytics Dashboard interface element 4 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Analytics Dashboard action component 4 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-285</t>
   </si>
   <si>
-    <t>Verify Analytics Dashboard Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Analytics Dashboard Screen action 5 without validation errors</t>
+    <t>Verify Analytics Dashboard interface element 5 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Analytics Dashboard action component 5 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-286</t>
   </si>
   <si>
-    <t>Verify Analytics Dashboard Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Analytics Dashboard Screen action 6 without validation errors</t>
+    <t>Verify Analytics Dashboard interface element 6 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Analytics Dashboard action component 6 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-287</t>
   </si>
   <si>
-    <t>Verify Analytics Dashboard Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Analytics Dashboard Screen action 7 without validation errors</t>
+    <t>Verify Analytics Dashboard interface element 7 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Analytics Dashboard action component 7 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-288</t>
   </si>
   <si>
-    <t>Verify Analytics Dashboard Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Analytics Dashboard Screen action 8 without validation errors</t>
+    <t>Verify Analytics Dashboard interface element 8 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Analytics Dashboard action component 8 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-289</t>
   </si>
   <si>
-    <t>Verify Analytics Dashboard Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Analytics Dashboard Screen action 9 without validation errors</t>
+    <t>Verify Analytics Dashboard interface element 9 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Analytics Dashboard action component 9 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-290</t>
   </si>
   <si>
-    <t>Verify Analytics Dashboard Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Analytics Dashboard Screen action 10 without validation errors</t>
+    <t>Verify Analytics Dashboard interface element 10 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Analytics Dashboard action component 10 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-291</t>
@@ -2910,91 +2910,91 @@
     <t>Logout Screen</t>
   </si>
   <si>
-    <t>Verify Logout Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Logout Screen action 1 without validation errors</t>
+    <t>Verify Logout interface element 1 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Logout action component 1 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-292</t>
   </si>
   <si>
-    <t>Verify Logout Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Logout Screen action 2 without validation errors</t>
+    <t>Verify Logout interface element 2 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Logout action component 2 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-293</t>
   </si>
   <si>
-    <t>Verify Logout Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Logout Screen action 3 without validation errors</t>
+    <t>Verify Logout interface element 3 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Logout action component 3 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-294</t>
   </si>
   <si>
-    <t>Verify Logout Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Logout Screen action 4 without validation errors</t>
+    <t>Verify Logout interface element 4 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Logout action component 4 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-295</t>
   </si>
   <si>
-    <t>Verify Logout Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Logout Screen action 5 without validation errors</t>
+    <t>Verify Logout interface element 5 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Logout action component 5 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-296</t>
   </si>
   <si>
-    <t>Verify Logout Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Logout Screen action 6 without validation errors</t>
+    <t>Verify Logout interface element 6 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Logout action component 6 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-297</t>
   </si>
   <si>
-    <t>Verify Logout Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Logout Screen action 7 without validation errors</t>
+    <t>Verify Logout interface element 7 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Logout action component 7 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-298</t>
   </si>
   <si>
-    <t>Verify Logout Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Logout Screen action 8 without validation errors</t>
+    <t>Verify Logout interface element 8 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Logout action component 8 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-299</t>
   </si>
   <si>
-    <t>Verify Logout Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Logout Screen action 9 without validation errors</t>
+    <t>Verify Logout interface element 9 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Logout action component 9 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>TC-SEL-300</t>
   </si>
   <si>
-    <t>Verify Logout Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Logout Screen action 10 without validation errors</t>
+    <t>Verify Logout interface element 10 displays and interacts correctly under web environment.</t>
+  </si>
+  <si>
+    <t>Logout action component 10 executes safely and updates the page layout dynamically.</t>
   </si>
   <si>
     <t>Failed Test ID</t>
@@ -3744,21 +3744,21 @@
         <v>26</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>25</v>
@@ -3767,21 +3767,21 @@
         <v>26</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>25</v>
@@ -3790,21 +3790,21 @@
         <v>26</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>25</v>
@@ -3813,21 +3813,21 @@
         <v>26</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>25</v>
@@ -3836,21 +3836,21 @@
         <v>26</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
@@ -3859,21 +3859,21 @@
         <v>26</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>25</v>
@@ -3882,21 +3882,21 @@
         <v>26</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>25</v>
@@ -3905,21 +3905,21 @@
         <v>26</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
@@ -3928,21 +3928,21 @@
         <v>26</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
@@ -3951,21 +3951,21 @@
         <v>26</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>25</v>
@@ -3974,21 +3974,21 @@
         <v>26</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
@@ -3997,21 +3997,21 @@
         <v>26</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
@@ -4020,7 +4020,7 @@
         <v>26</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>100</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -4043,53 +4043,53 @@
         <v>26</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>102</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>102</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -4112,21 +4112,21 @@
         <v>26</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>47</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>102</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>25</v>
@@ -4135,21 +4135,21 @@
         <v>26</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>102</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>25</v>
@@ -4158,7 +4158,7 @@
         <v>26</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>123</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -4181,21 +4181,21 @@
         <v>26</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>102</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>25</v>
@@ -4204,21 +4204,21 @@
         <v>26</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>51</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>102</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>25</v>
@@ -4227,21 +4227,21 @@
         <v>26</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>133</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>102</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>25</v>
@@ -4250,7 +4250,7 @@
         <v>26</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>137</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -4342,7 +4342,7 @@
         <v>26</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -4365,21 +4365,21 @@
         <v>26</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>81</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>139</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>25</v>
@@ -4388,21 +4388,21 @@
         <v>26</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>35</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>139</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>25</v>
@@ -4411,21 +4411,21 @@
         <v>26</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>139</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>25</v>
@@ -4434,21 +4434,21 @@
         <v>26</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>139</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>25</v>
@@ -4457,21 +4457,21 @@
         <v>26</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>139</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>25</v>
@@ -4480,21 +4480,21 @@
         <v>26</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>35</v>
+        <v>175</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>25</v>
@@ -4503,21 +4503,21 @@
         <v>26</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>85</v>
+        <v>180</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="C43" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>25</v>
@@ -4526,21 +4526,21 @@
         <v>26</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>119</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>25</v>
@@ -4549,21 +4549,21 @@
         <v>26</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>150</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>25</v>
@@ -4572,21 +4572,21 @@
         <v>26</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>133</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>25</v>
@@ -4595,21 +4595,21 @@
         <v>26</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>25</v>
@@ -4618,21 +4618,21 @@
         <v>26</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>51</v>
+        <v>112</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>25</v>
@@ -4641,21 +4641,21 @@
         <v>26</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>195</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>25</v>
@@ -4664,21 +4664,21 @@
         <v>26</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>199</v>
+        <v>91</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>25</v>
@@ -4687,21 +4687,21 @@
         <v>26</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>25</v>
@@ -4710,21 +4710,21 @@
         <v>26</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>207</v>
+        <v>146</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>25</v>
@@ -4733,21 +4733,21 @@
         <v>26</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>212</v>
+        <v>171</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>25</v>
@@ -4756,21 +4756,21 @@
         <v>26</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>96</v>
+        <v>217</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>25</v>
@@ -4779,21 +4779,21 @@
         <v>26</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>219</v>
+        <v>51</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>25</v>
@@ -4802,21 +4802,21 @@
         <v>26</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>25</v>
@@ -4825,21 +4825,21 @@
         <v>26</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>85</v>
+        <v>175</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>25</v>
@@ -4848,21 +4848,21 @@
         <v>26</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>25</v>
@@ -4871,21 +4871,21 @@
         <v>26</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>89</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>25</v>
@@ -4894,21 +4894,21 @@
         <v>26</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>25</v>
@@ -4917,21 +4917,21 @@
         <v>26</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>43</v>
+        <v>217</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>25</v>
@@ -4940,21 +4940,21 @@
         <v>26</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>235</v>
+        <v>164</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>25</v>
@@ -4963,21 +4963,21 @@
         <v>26</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>203</v>
+        <v>39</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>25</v>
@@ -4986,21 +4986,21 @@
         <v>26</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>96</v>
+        <v>250</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>25</v>
@@ -5009,21 +5009,21 @@
         <v>26</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>25</v>
@@ -5032,21 +5032,21 @@
         <v>26</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>25</v>
@@ -5055,21 +5055,21 @@
         <v>26</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>25</v>
@@ -5078,21 +5078,21 @@
         <v>26</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>109</v>
+        <v>164</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>25</v>
@@ -5101,21 +5101,21 @@
         <v>26</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>27</v>
+        <v>266</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>25</v>
@@ -5124,21 +5124,21 @@
         <v>26</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>123</v>
+        <v>180</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>25</v>
@@ -5147,21 +5147,21 @@
         <v>26</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>25</v>
@@ -5170,21 +5170,21 @@
         <v>26</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>47</v>
+        <v>131</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>25</v>
@@ -5193,21 +5193,21 @@
         <v>26</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>235</v>
+        <v>164</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>274</v>
-      </c>
       <c r="C73" s="3" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>25</v>
@@ -5216,21 +5216,21 @@
         <v>26</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>25</v>
@@ -5239,21 +5239,21 @@
         <v>26</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>81</v>
+        <v>266</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>25</v>
@@ -5262,21 +5262,21 @@
         <v>26</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>25</v>
@@ -5285,21 +5285,21 @@
         <v>26</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>25</v>
@@ -5313,16 +5313,16 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>25</v>
@@ -5331,21 +5331,21 @@
         <v>26</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>295</v>
+        <v>31</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>25</v>
@@ -5354,21 +5354,21 @@
         <v>26</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>207</v>
+        <v>250</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>25</v>
@@ -5377,21 +5377,21 @@
         <v>26</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>100</v>
+        <v>171</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>25</v>
@@ -5400,21 +5400,21 @@
         <v>26</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>25</v>
@@ -5423,21 +5423,21 @@
         <v>26</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>25</v>
@@ -5446,21 +5446,21 @@
         <v>26</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>199</v>
+        <v>120</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>25</v>
@@ -5469,21 +5469,21 @@
         <v>26</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>315</v>
+        <v>55</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>25</v>
@@ -5492,21 +5492,21 @@
         <v>26</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>146</v>
+        <v>43</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>25</v>
@@ -5515,21 +5515,21 @@
         <v>26</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>199</v>
+        <v>47</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>25</v>
@@ -5538,21 +5538,21 @@
         <v>26</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>25</v>
@@ -5561,21 +5561,21 @@
         <v>26</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>81</v>
+        <v>329</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>25</v>
@@ -5584,21 +5584,21 @@
         <v>26</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>27</v>
+        <v>190</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>25</v>
@@ -5607,21 +5607,21 @@
         <v>26</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>47</v>
+        <v>127</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>25</v>
@@ -5630,21 +5630,21 @@
         <v>26</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>27</v>
+        <v>120</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>25</v>
@@ -5653,21 +5653,21 @@
         <v>26</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>25</v>
@@ -5676,21 +5676,21 @@
         <v>26</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>25</v>
@@ -5699,21 +5699,21 @@
         <v>26</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>203</v>
+        <v>266</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>25</v>
@@ -5722,21 +5722,21 @@
         <v>26</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>25</v>
@@ -5745,21 +5745,21 @@
         <v>26</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>35</v>
+        <v>171</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>25</v>
@@ -5768,21 +5768,21 @@
         <v>26</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>25</v>
@@ -5791,21 +5791,21 @@
         <v>26</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>25</v>
@@ -5814,21 +5814,21 @@
         <v>26</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>61</v>
+        <v>180</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>25</v>
@@ -5837,21 +5837,21 @@
         <v>26</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>25</v>
@@ -5860,21 +5860,21 @@
         <v>26</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>25</v>
@@ -5883,44 +5883,44 @@
         <v>26</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>35</v>
+        <v>374</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D103" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G103" s="3" t="s">
         <v>374</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F103" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G103" s="3" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>25</v>
@@ -5929,21 +5929,21 @@
         <v>26</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>379</v>
+        <v>157</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>25</v>
@@ -5952,21 +5952,21 @@
         <v>26</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>207</v>
+        <v>384</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>25</v>
@@ -5975,21 +5975,21 @@
         <v>26</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>73</v>
+        <v>164</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>25</v>
@@ -5998,21 +5998,21 @@
         <v>26</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>375</v>
+        <v>217</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>25</v>
@@ -6021,21 +6021,21 @@
         <v>26</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>25</v>
@@ -6044,21 +6044,21 @@
         <v>26</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>212</v>
+        <v>171</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>25</v>
@@ -6067,21 +6067,21 @@
         <v>26</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>25</v>
@@ -6090,21 +6090,21 @@
         <v>26</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>401</v>
+        <v>236</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>25</v>
@@ -6113,21 +6113,21 @@
         <v>26</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>133</v>
+        <v>250</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>25</v>
@@ -6136,21 +6136,21 @@
         <v>26</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>137</v>
+        <v>164</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>25</v>
@@ -6159,21 +6159,21 @@
         <v>26</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>195</v>
+        <v>384</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>25</v>
@@ -6182,21 +6182,21 @@
         <v>26</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>96</v>
+        <v>150</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>25</v>
@@ -6205,21 +6205,21 @@
         <v>26</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>379</v>
+        <v>27</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E117" s="3" t="s">
         <v>25</v>
@@ -6228,21 +6228,21 @@
         <v>26</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E118" s="3" t="s">
         <v>25</v>
@@ -6251,21 +6251,21 @@
         <v>26</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>25</v>
@@ -6274,21 +6274,21 @@
         <v>26</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>427</v>
+        <v>59</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>25</v>
@@ -6297,21 +6297,21 @@
         <v>26</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>81</v>
+        <v>206</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>25</v>
@@ -6320,21 +6320,21 @@
         <v>26</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>295</v>
+        <v>435</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E122" s="3" t="s">
         <v>25</v>
@@ -6343,21 +6343,21 @@
         <v>26</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>25</v>
@@ -6366,21 +6366,21 @@
         <v>26</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>119</v>
+        <v>171</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>25</v>
@@ -6389,21 +6389,21 @@
         <v>26</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>195</v>
+        <v>55</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>25</v>
@@ -6412,21 +6412,21 @@
         <v>26</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>109</v>
+        <v>236</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>25</v>
@@ -6435,21 +6435,21 @@
         <v>26</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>315</v>
+        <v>164</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>25</v>
@@ -6458,21 +6458,21 @@
         <v>26</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>203</v>
+        <v>112</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>25</v>
@@ -6481,21 +6481,21 @@
         <v>26</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>195</v>
+        <v>91</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>25</v>
@@ -6504,21 +6504,21 @@
         <v>26</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>295</v>
+        <v>43</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E130" s="3" t="s">
         <v>25</v>
@@ -6527,21 +6527,21 @@
         <v>26</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>150</v>
+        <v>72</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>25</v>
@@ -6550,21 +6550,21 @@
         <v>26</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>375</v>
+        <v>236</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>25</v>
@@ -6573,21 +6573,21 @@
         <v>26</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>427</v>
+        <v>127</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>25</v>
@@ -6596,21 +6596,21 @@
         <v>26</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E134" s="3" t="s">
         <v>25</v>
@@ -6619,21 +6619,21 @@
         <v>26</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>212</v>
+        <v>329</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E135" s="3" t="s">
         <v>25</v>
@@ -6642,21 +6642,21 @@
         <v>26</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>25</v>
@@ -6665,21 +6665,21 @@
         <v>26</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E137" s="3" t="s">
         <v>25</v>
@@ -6688,21 +6688,21 @@
         <v>26</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>137</v>
+        <v>35</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E138" s="3" t="s">
         <v>25</v>
@@ -6711,21 +6711,21 @@
         <v>26</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>39</v>
+        <v>157</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E139" s="3" t="s">
         <v>25</v>
@@ -6734,21 +6734,21 @@
         <v>26</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>77</v>
+        <v>435</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>25</v>
@@ -6757,21 +6757,21 @@
         <v>26</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>315</v>
+        <v>142</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>25</v>
@@ -6780,21 +6780,21 @@
         <v>26</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>123</v>
+        <v>435</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E142" s="3" t="s">
         <v>25</v>
@@ -6803,21 +6803,21 @@
         <v>26</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>401</v>
+        <v>266</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E143" s="3" t="s">
         <v>25</v>
@@ -6826,21 +6826,21 @@
         <v>26</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>207</v>
+        <v>80</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>25</v>
@@ -6849,21 +6849,21 @@
         <v>26</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>207</v>
+        <v>59</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>25</v>
@@ -6872,21 +6872,21 @@
         <v>26</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>51</v>
+        <v>435</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E146" s="3" t="s">
         <v>25</v>
@@ -6895,21 +6895,21 @@
         <v>26</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>25</v>
@@ -6918,21 +6918,21 @@
         <v>26</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>96</v>
+        <v>43</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E148" s="3" t="s">
         <v>25</v>
@@ -6941,21 +6941,21 @@
         <v>26</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>427</v>
+        <v>55</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E149" s="3" t="s">
         <v>25</v>
@@ -6964,21 +6964,21 @@
         <v>26</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E150" s="3" t="s">
         <v>25</v>
@@ -6987,21 +6987,21 @@
         <v>26</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E151" s="3" t="s">
         <v>25</v>
@@ -7010,21 +7010,21 @@
         <v>26</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>527</v>
+        <v>35</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E152" s="3" t="s">
         <v>25</v>
@@ -7033,7 +7033,7 @@
         <v>26</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>532</v>
+        <v>120</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -7041,7 +7041,7 @@
         <v>533</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>534</v>
@@ -7056,7 +7056,7 @@
         <v>26</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>375</v>
+        <v>39</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -7064,7 +7064,7 @@
         <v>536</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>537</v>
@@ -7079,7 +7079,7 @@
         <v>26</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -7087,7 +7087,7 @@
         <v>539</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C155" s="3" t="s">
         <v>540</v>
@@ -7102,7 +7102,7 @@
         <v>26</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>35</v>
+        <v>394</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -7110,7 +7110,7 @@
         <v>542</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C156" s="3" t="s">
         <v>543</v>
@@ -7125,7 +7125,7 @@
         <v>26</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>133</v>
+        <v>180</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -7133,7 +7133,7 @@
         <v>545</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C157" s="3" t="s">
         <v>546</v>
@@ -7148,7 +7148,7 @@
         <v>26</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>61</v>
+        <v>164</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -7156,7 +7156,7 @@
         <v>548</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C158" s="3" t="s">
         <v>549</v>
@@ -7171,7 +7171,7 @@
         <v>26</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>61</v>
+        <v>171</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -7179,7 +7179,7 @@
         <v>551</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C159" s="3" t="s">
         <v>552</v>
@@ -7194,7 +7194,7 @@
         <v>26</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>427</v>
+        <v>76</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -7202,7 +7202,7 @@
         <v>554</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>555</v>
@@ -7217,7 +7217,7 @@
         <v>26</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -7225,7 +7225,7 @@
         <v>557</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C161" s="3" t="s">
         <v>558</v>
@@ -7240,7 +7240,7 @@
         <v>26</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>207</v>
+        <v>435</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -7263,7 +7263,7 @@
         <v>26</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>39</v>
+        <v>112</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -7286,7 +7286,7 @@
         <v>26</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -7309,7 +7309,7 @@
         <v>26</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>150</v>
+        <v>91</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -7332,7 +7332,7 @@
         <v>26</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>100</v>
+        <v>266</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -7355,7 +7355,7 @@
         <v>26</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>295</v>
+        <v>250</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -7378,7 +7378,7 @@
         <v>26</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>35</v>
+        <v>329</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -7401,7 +7401,7 @@
         <v>26</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>89</v>
+        <v>206</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -7424,7 +7424,7 @@
         <v>26</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>123</v>
+        <v>217</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -7447,7 +7447,7 @@
         <v>26</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>199</v>
+        <v>39</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -7470,7 +7470,7 @@
         <v>26</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>81</v>
+        <v>217</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -7493,7 +7493,7 @@
         <v>26</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>96</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -7516,7 +7516,7 @@
         <v>26</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>235</v>
+        <v>76</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -7539,7 +7539,7 @@
         <v>26</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>532</v>
+        <v>72</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -7562,7 +7562,7 @@
         <v>26</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>315</v>
+        <v>236</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -7585,7 +7585,7 @@
         <v>26</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>150</v>
+        <v>108</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -7608,7 +7608,7 @@
         <v>26</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -7631,7 +7631,7 @@
         <v>26</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>31</v>
+        <v>236</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -7654,7 +7654,7 @@
         <v>26</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>235</v>
+        <v>68</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -7677,7 +7677,7 @@
         <v>26</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -7700,7 +7700,7 @@
         <v>26</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>379</v>
+        <v>142</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -7723,7 +7723,7 @@
         <v>26</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>379</v>
+        <v>329</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -7746,7 +7746,7 @@
         <v>26</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>195</v>
+        <v>146</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -7769,7 +7769,7 @@
         <v>26</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -7792,7 +7792,7 @@
         <v>26</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>100</v>
+        <v>150</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -7815,7 +7815,7 @@
         <v>26</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -7838,7 +7838,7 @@
         <v>26</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -7861,7 +7861,7 @@
         <v>26</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>39</v>
+        <v>329</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -7884,7 +7884,7 @@
         <v>26</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -7907,7 +7907,7 @@
         <v>26</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
@@ -7930,7 +7930,7 @@
         <v>26</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>203</v>
+        <v>27</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
@@ -7953,7 +7953,7 @@
         <v>26</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>212</v>
+        <v>164</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
@@ -7976,7 +7976,7 @@
         <v>26</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>31</v>
+        <v>394</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -7999,7 +7999,7 @@
         <v>26</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>96</v>
+        <v>266</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
@@ -8022,7 +8022,7 @@
         <v>26</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -8045,7 +8045,7 @@
         <v>26</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>532</v>
+        <v>47</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -8068,7 +8068,7 @@
         <v>26</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
@@ -8091,7 +8091,7 @@
         <v>26</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>427</v>
+        <v>91</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -8114,7 +8114,7 @@
         <v>26</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>96</v>
+        <v>266</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
@@ -8137,7 +8137,7 @@
         <v>26</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>47</v>
+        <v>120</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -8160,7 +8160,7 @@
         <v>26</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
@@ -8183,7 +8183,7 @@
         <v>26</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>401</v>
+        <v>27</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
@@ -8206,7 +8206,7 @@
         <v>26</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>123</v>
+        <v>180</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
@@ -8229,7 +8229,7 @@
         <v>26</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
@@ -8252,7 +8252,7 @@
         <v>26</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>401</v>
+        <v>72</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
@@ -8275,7 +8275,7 @@
         <v>26</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>401</v>
+        <v>76</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
@@ -8298,7 +8298,7 @@
         <v>26</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>109</v>
+        <v>190</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
@@ -8321,7 +8321,7 @@
         <v>26</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>89</v>
+        <v>180</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
@@ -8344,7 +8344,7 @@
         <v>26</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
@@ -8367,7 +8367,7 @@
         <v>26</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>295</v>
+        <v>87</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
@@ -8390,7 +8390,7 @@
         <v>26</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>212</v>
+        <v>59</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
@@ -8413,7 +8413,7 @@
         <v>26</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
@@ -8436,7 +8436,7 @@
         <v>26</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>137</v>
+        <v>250</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
@@ -8459,7 +8459,7 @@
         <v>26</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
@@ -8482,7 +8482,7 @@
         <v>26</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
@@ -8505,7 +8505,7 @@
         <v>26</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
@@ -8528,7 +8528,7 @@
         <v>26</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
@@ -8551,7 +8551,7 @@
         <v>26</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>375</v>
+        <v>91</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
@@ -8574,7 +8574,7 @@
         <v>26</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>212</v>
+        <v>120</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
@@ -8597,7 +8597,7 @@
         <v>26</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>427</v>
+        <v>329</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
@@ -8620,7 +8620,7 @@
         <v>26</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>375</v>
+        <v>217</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
@@ -8643,7 +8643,7 @@
         <v>26</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>137</v>
+        <v>51</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
@@ -8666,7 +8666,7 @@
         <v>26</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>235</v>
+        <v>157</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
@@ -8689,7 +8689,7 @@
         <v>26</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>100</v>
+        <v>374</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
@@ -8712,7 +8712,7 @@
         <v>26</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>146</v>
+        <v>35</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
@@ -8735,7 +8735,7 @@
         <v>26</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>375</v>
+        <v>112</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
@@ -8758,7 +8758,7 @@
         <v>26</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>207</v>
+        <v>51</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
@@ -8781,7 +8781,7 @@
         <v>26</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
@@ -8804,7 +8804,7 @@
         <v>26</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>235</v>
+        <v>146</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
@@ -8827,7 +8827,7 @@
         <v>26</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>142</v>
+        <v>217</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
@@ -8850,7 +8850,7 @@
         <v>26</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>235</v>
+        <v>91</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
@@ -8873,7 +8873,7 @@
         <v>26</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>119</v>
+        <v>180</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
@@ -8896,7 +8896,7 @@
         <v>26</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
@@ -8919,7 +8919,7 @@
         <v>26</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>43</v>
+        <v>87</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -8942,7 +8942,7 @@
         <v>26</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>89</v>
+        <v>146</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
@@ -8965,7 +8965,7 @@
         <v>26</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>137</v>
+        <v>59</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
@@ -8988,7 +8988,7 @@
         <v>26</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>163</v>
+        <v>116</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
@@ -9011,7 +9011,7 @@
         <v>26</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
@@ -9034,7 +9034,7 @@
         <v>26</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>43</v>
+        <v>206</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
@@ -9057,7 +9057,7 @@
         <v>26</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>379</v>
+        <v>59</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
@@ -9080,7 +9080,7 @@
         <v>26</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
@@ -9103,7 +9103,7 @@
         <v>26</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
@@ -9126,7 +9126,7 @@
         <v>26</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>142</v>
+        <v>59</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
@@ -9149,7 +9149,7 @@
         <v>26</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>119</v>
+        <v>31</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
@@ -9172,7 +9172,7 @@
         <v>26</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
@@ -9195,7 +9195,7 @@
         <v>26</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
@@ -9218,7 +9218,7 @@
         <v>26</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>235</v>
+        <v>150</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
@@ -9241,7 +9241,7 @@
         <v>26</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>401</v>
+        <v>39</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
@@ -9264,7 +9264,7 @@
         <v>26</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
@@ -9287,7 +9287,7 @@
         <v>26</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>69</v>
+        <v>171</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
@@ -9310,7 +9310,7 @@
         <v>26</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>47</v>
+        <v>127</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
@@ -9333,7 +9333,7 @@
         <v>26</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
@@ -9356,7 +9356,7 @@
         <v>26</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
@@ -9379,7 +9379,7 @@
         <v>26</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>315</v>
+        <v>190</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
@@ -9402,7 +9402,7 @@
         <v>26</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>133</v>
+        <v>76</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
@@ -9425,7 +9425,7 @@
         <v>26</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
@@ -9448,7 +9448,7 @@
         <v>26</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
@@ -9471,7 +9471,7 @@
         <v>26</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>532</v>
+        <v>131</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
@@ -9494,7 +9494,7 @@
         <v>26</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>235</v>
+        <v>80</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
@@ -9517,7 +9517,7 @@
         <v>26</v>
       </c>
       <c r="G260" s="3" t="s">
-        <v>295</v>
+        <v>80</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
@@ -9540,7 +9540,7 @@
         <v>26</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>43</v>
+        <v>164</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
@@ -9563,7 +9563,7 @@
         <v>26</v>
       </c>
       <c r="G262" s="3" t="s">
-        <v>123</v>
+        <v>59</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
@@ -9586,7 +9586,7 @@
         <v>26</v>
       </c>
       <c r="G263" s="3" t="s">
-        <v>100</v>
+        <v>266</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
@@ -9609,7 +9609,7 @@
         <v>26</v>
       </c>
       <c r="G264" s="3" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
@@ -9632,7 +9632,7 @@
         <v>26</v>
       </c>
       <c r="G265" s="3" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
@@ -9655,7 +9655,7 @@
         <v>26</v>
       </c>
       <c r="G266" s="3" t="s">
-        <v>43</v>
+        <v>112</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
@@ -9678,7 +9678,7 @@
         <v>26</v>
       </c>
       <c r="G267" s="3" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
@@ -9701,7 +9701,7 @@
         <v>26</v>
       </c>
       <c r="G268" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
@@ -9724,7 +9724,7 @@
         <v>26</v>
       </c>
       <c r="G269" s="3" t="s">
-        <v>401</v>
+        <v>35</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
@@ -9747,7 +9747,7 @@
         <v>26</v>
       </c>
       <c r="G270" s="3" t="s">
-        <v>133</v>
+        <v>27</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
@@ -9770,7 +9770,7 @@
         <v>26</v>
       </c>
       <c r="G271" s="3" t="s">
-        <v>199</v>
+        <v>127</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
@@ -9793,7 +9793,7 @@
         <v>26</v>
       </c>
       <c r="G272" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
@@ -9816,7 +9816,7 @@
         <v>26</v>
       </c>
       <c r="G273" s="3" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
@@ -9839,7 +9839,7 @@
         <v>26</v>
       </c>
       <c r="G274" s="3" t="s">
-        <v>532</v>
+        <v>55</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
@@ -9862,7 +9862,7 @@
         <v>26</v>
       </c>
       <c r="G275" s="3" t="s">
-        <v>315</v>
+        <v>112</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
@@ -9885,7 +9885,7 @@
         <v>26</v>
       </c>
       <c r="G276" s="3" t="s">
-        <v>150</v>
+        <v>27</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
@@ -9908,7 +9908,7 @@
         <v>26</v>
       </c>
       <c r="G277" s="3" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
@@ -9931,7 +9931,7 @@
         <v>26</v>
       </c>
       <c r="G278" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
@@ -9954,7 +9954,7 @@
         <v>26</v>
       </c>
       <c r="G279" s="3" t="s">
-        <v>207</v>
+        <v>47</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
@@ -9977,7 +9977,7 @@
         <v>26</v>
       </c>
       <c r="G280" s="3" t="s">
-        <v>123</v>
+        <v>329</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
@@ -10000,7 +10000,7 @@
         <v>26</v>
       </c>
       <c r="G281" s="3" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
@@ -10023,7 +10023,7 @@
         <v>26</v>
       </c>
       <c r="G282" s="3" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
@@ -10046,7 +10046,7 @@
         <v>26</v>
       </c>
       <c r="G283" s="3" t="s">
-        <v>527</v>
+        <v>217</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
@@ -10069,7 +10069,7 @@
         <v>26</v>
       </c>
       <c r="G284" s="3" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
@@ -10092,7 +10092,7 @@
         <v>26</v>
       </c>
       <c r="G285" s="3" t="s">
-        <v>61</v>
+        <v>157</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
@@ -10115,7 +10115,7 @@
         <v>26</v>
       </c>
       <c r="G286" s="3" t="s">
-        <v>119</v>
+        <v>43</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
@@ -10138,7 +10138,7 @@
         <v>26</v>
       </c>
       <c r="G287" s="3" t="s">
-        <v>219</v>
+        <v>39</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.25">
@@ -10161,7 +10161,7 @@
         <v>26</v>
       </c>
       <c r="G288" s="3" t="s">
-        <v>212</v>
+        <v>374</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
@@ -10184,7 +10184,7 @@
         <v>26</v>
       </c>
       <c r="G289" s="3" t="s">
-        <v>219</v>
+        <v>127</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
@@ -10207,7 +10207,7 @@
         <v>26</v>
       </c>
       <c r="G290" s="3" t="s">
-        <v>35</v>
+        <v>266</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
@@ -10230,7 +10230,7 @@
         <v>26</v>
       </c>
       <c r="G291" s="3" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
@@ -10253,7 +10253,7 @@
         <v>26</v>
       </c>
       <c r="G292" s="3" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
@@ -10276,7 +10276,7 @@
         <v>26</v>
       </c>
       <c r="G293" s="3" t="s">
-        <v>212</v>
+        <v>127</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.25">
@@ -10299,7 +10299,7 @@
         <v>26</v>
       </c>
       <c r="G294" s="3" t="s">
-        <v>207</v>
+        <v>87</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
@@ -10322,7 +10322,7 @@
         <v>26</v>
       </c>
       <c r="G295" s="3" t="s">
-        <v>123</v>
+        <v>76</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
@@ -10345,7 +10345,7 @@
         <v>26</v>
       </c>
       <c r="G296" s="3" t="s">
-        <v>219</v>
+        <v>250</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
@@ -10368,7 +10368,7 @@
         <v>26</v>
       </c>
       <c r="G297" s="3" t="s">
-        <v>85</v>
+        <v>266</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
@@ -10391,7 +10391,7 @@
         <v>26</v>
       </c>
       <c r="G298" s="3" t="s">
-        <v>295</v>
+        <v>164</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.25">
@@ -10414,7 +10414,7 @@
         <v>26</v>
       </c>
       <c r="G299" s="3" t="s">
-        <v>401</v>
+        <v>68</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.25">
@@ -10437,7 +10437,7 @@
         <v>26</v>
       </c>
       <c r="G300" s="3" t="s">
-        <v>47</v>
+        <v>116</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.25">
@@ -10460,7 +10460,7 @@
         <v>26</v>
       </c>
       <c r="G301" s="3" t="s">
-        <v>195</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Selenium_Report.xlsx
+++ b/reports/Selenium_Report.xlsx
@@ -24,7 +24,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>18/6/2026, 12:29:47 pm</t>
+    <t>18/6/2026, 1:15:20 pm</t>
   </si>
   <si>
     <t>Test Suite / Scope</t>
